--- a/output/daily_ratings/france_ratings_2026-03-29.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-29.xlsx
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>76.67338598291946</v>
+        <v>75.71695608961932</v>
       </c>
       <c r="T8" t="n">
-        <v>76.67338598291946</v>
+        <v>75.71695608961932</v>
       </c>
     </row>
     <row r="9">
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>73.86047280685412</v>
+        <v>72.81956676022145</v>
       </c>
       <c r="T9" t="n">
-        <v>73.86047280685412</v>
+        <v>72.81956676022145</v>
       </c>
     </row>
     <row r="10">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>62.57121115238971</v>
+        <v>61.19127103721623</v>
       </c>
       <c r="T10" t="n">
-        <v>62.57121115238971</v>
+        <v>61.19127103721623</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>64.67858588176543</v>
+        <v>63.36193350411707</v>
       </c>
       <c r="T11" t="n">
-        <v>64.67858588176543</v>
+        <v>63.36193350411707</v>
       </c>
     </row>
     <row r="12">
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>66.0499052991259</v>
+        <v>64.77443577431302</v>
       </c>
       <c r="T12" t="n">
-        <v>66.0499052991259</v>
+        <v>64.77443577431302</v>
       </c>
     </row>
     <row r="13">
@@ -1368,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>59.55671556298448</v>
+        <v>58.08624546139065</v>
       </c>
       <c r="T13" t="n">
-        <v>59.55671556298448</v>
+        <v>58.08624546139065</v>
       </c>
     </row>
     <row r="14">
@@ -1442,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>58.54171141140753</v>
+        <v>57.04075915804615</v>
       </c>
       <c r="T14" t="n">
-        <v>58.54171141140753</v>
+        <v>57.04075915804615</v>
       </c>
     </row>
     <row r="15">
@@ -1863,7 +1863,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>-2.541280000000015</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
         <v>-5.848210000000009</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
         <v>-5.848210000000009</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -2679,7 +2679,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>10.80370635488746</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>65.59787587861555</v>
+        <v>64.30883120794934</v>
       </c>
       <c r="T33" t="n">
-        <v>65.59787587861555</v>
+        <v>64.30883120794934</v>
       </c>
     </row>
     <row r="34">
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>63.5894620370138</v>
+        <v>62.24010157804597</v>
       </c>
       <c r="T34" t="n">
-        <v>63.5894620370138</v>
+        <v>62.24010157804597</v>
       </c>
     </row>
     <row r="35">
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>60.21619821489585</v>
+        <v>58.76553340203153</v>
       </c>
       <c r="T35" t="n">
-        <v>60.21619821489585</v>
+        <v>58.76553340203153</v>
       </c>
     </row>
     <row r="36">
@@ -2976,10 +2976,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>51.26150463461434</v>
+        <v>49.54191645988792</v>
       </c>
       <c r="T36" t="n">
-        <v>51.26150463461434</v>
+        <v>49.54191645988792</v>
       </c>
     </row>
     <row r="37">
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>49.25309079301257</v>
+        <v>47.47318682998456</v>
       </c>
       <c r="T37" t="n">
-        <v>49.25309079301257</v>
+        <v>47.47318682998456</v>
       </c>
     </row>
     <row r="38">
@@ -3124,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>46.62326687920219</v>
+        <v>44.76438521786806</v>
       </c>
       <c r="T38" t="n">
-        <v>46.62326687920219</v>
+        <v>44.76438521786806</v>
       </c>
     </row>
     <row r="39">
@@ -3270,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>48.43980490932168</v>
+        <v>46.63547670753705</v>
       </c>
       <c r="T40" t="n">
-        <v>48.43980490932168</v>
+        <v>46.63547670753705</v>
       </c>
     </row>
     <row r="41">
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>52.69641088027898</v>
+        <v>51.01991516964209</v>
       </c>
       <c r="T41" t="n">
-        <v>52.69641088027898</v>
+        <v>51.01991516964209</v>
       </c>
     </row>
     <row r="42">
@@ -3418,10 +3418,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>48.97441819109973</v>
+        <v>47.18614525683967</v>
       </c>
       <c r="T42" t="n">
-        <v>48.97441819109973</v>
+        <v>47.18614525683967</v>
       </c>
     </row>
     <row r="43">
@@ -3492,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>46.16906477962127</v>
+        <v>44.29654272350545</v>
       </c>
       <c r="T43" t="n">
-        <v>46.16906477962127</v>
+        <v>44.29654272350545</v>
       </c>
     </row>
     <row r="44">
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>43.90118009603234</v>
+        <v>41.9605499390688</v>
       </c>
       <c r="T44" t="n">
-        <v>43.90118009603234</v>
+        <v>41.9605499390688</v>
       </c>
     </row>
     <row r="45">
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>48.25779322058037</v>
+        <v>46.44799892497626</v>
       </c>
       <c r="T45" t="n">
-        <v>48.25779322058037</v>
+        <v>46.44799892497626</v>
       </c>
     </row>
     <row r="46">
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>40.25833649589222</v>
+        <v>38.20830608542981</v>
       </c>
       <c r="T46" t="n">
-        <v>40.25833649589222</v>
+        <v>38.20830608542981</v>
       </c>
     </row>
     <row r="47">
@@ -3788,10 +3788,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>34.10587777587858</v>
+        <v>31.87107947047142</v>
       </c>
       <c r="T47" t="n">
-        <v>34.10587777587858</v>
+        <v>31.87107947047142</v>
       </c>
     </row>
     <row r="48">
@@ -3931,13 +3931,13 @@
         <v>-5.848210000000009</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S49" t="n">
-        <v>55.4755367173064</v>
+        <v>62.16795569996496</v>
       </c>
       <c r="T49" t="n">
-        <v>55.4755367173064</v>
+        <v>62.16795569996496</v>
       </c>
     </row>
     <row r="50">
@@ -4005,13 +4005,13 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S50" t="n">
-        <v>54.24391187481324</v>
+        <v>60.8993432497746</v>
       </c>
       <c r="T50" t="n">
-        <v>54.24391187481324</v>
+        <v>60.8993432497746</v>
       </c>
     </row>
     <row r="51">
@@ -4079,13 +4079,13 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S51" t="n">
-        <v>53.40874265670244</v>
+        <v>60.03909260237261</v>
       </c>
       <c r="T51" t="n">
-        <v>53.40874265670244</v>
+        <v>60.03909260237261</v>
       </c>
     </row>
     <row r="52">
@@ -4153,13 +4153,13 @@
         <v>-2.541280000000015</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S52" t="n">
-        <v>45.9913335998008</v>
+        <v>52.39892722645178</v>
       </c>
       <c r="T52" t="n">
-        <v>45.9913335998008</v>
+        <v>52.39892722645178</v>
       </c>
     </row>
     <row r="53">
@@ -4227,13 +4227,13 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S53" t="n">
-        <v>46.56035506819386</v>
+        <v>52.98503729367629</v>
       </c>
       <c r="T53" t="n">
-        <v>46.56035506819386</v>
+        <v>52.98503729367629</v>
       </c>
     </row>
     <row r="54">
@@ -4301,13 +4301,13 @@
         <v>2.970269999999999</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S54" t="n">
-        <v>49.33754247263257</v>
+        <v>55.8456279510155</v>
       </c>
       <c r="T54" t="n">
-        <v>49.33754247263257</v>
+        <v>55.8456279510155</v>
       </c>
     </row>
     <row r="55">
@@ -4375,13 +4375,13 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S55" t="n">
-        <v>46.14277045913845</v>
+        <v>52.55491196997528</v>
       </c>
       <c r="T55" t="n">
-        <v>46.14277045913845</v>
+        <v>52.55491196997528</v>
       </c>
     </row>
     <row r="56">
@@ -4449,13 +4449,13 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S56" t="n">
-        <v>44.47243202291685</v>
+        <v>50.8344106751713</v>
       </c>
       <c r="T56" t="n">
-        <v>44.47243202291685</v>
+        <v>50.8344106751713</v>
       </c>
     </row>
     <row r="57">
@@ -4523,7 +4523,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>69.89743269921769</v>
+        <v>68.73751040045033</v>
       </c>
       <c r="T58" t="n">
-        <v>69.89743269921769</v>
+        <v>68.73751040045033</v>
       </c>
     </row>
     <row r="59">
@@ -4672,10 +4672,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>62.77099223240472</v>
+        <v>61.39705185348043</v>
       </c>
       <c r="T59" t="n">
-        <v>62.77099223240472</v>
+        <v>61.39705185348043</v>
       </c>
     </row>
     <row r="60">
@@ -4746,10 +4746,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>65.94932613380479</v>
+        <v>64.67083606037914</v>
       </c>
       <c r="T60" t="n">
-        <v>65.94932613380479</v>
+        <v>64.67083606037914</v>
       </c>
     </row>
     <row r="61">
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>55.63612242759232</v>
+        <v>54.04791082239363</v>
       </c>
       <c r="T61" t="n">
-        <v>55.63612242759232</v>
+        <v>54.04791082239363</v>
       </c>
     </row>
     <row r="62">
@@ -4894,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>51.45390320884022</v>
+        <v>49.74009306224335</v>
       </c>
       <c r="T62" t="n">
-        <v>51.45390320884022</v>
+        <v>49.74009306224335</v>
       </c>
     </row>
     <row r="63">
@@ -5035,7 +5035,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -5103,7 +5103,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -5443,7 +5443,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -5511,7 +5511,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -5579,7 +5579,7 @@
         <v>-1.438970000000012</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>87.258127178846</v>
+        <v>86.61957351004526</v>
       </c>
       <c r="T73" t="n">
-        <v>87.258127178846</v>
+        <v>86.61957351004526</v>
       </c>
     </row>
     <row r="74">
@@ -5728,10 +5728,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>81.30686033444687</v>
+        <v>80.48958087533452</v>
       </c>
       <c r="T74" t="n">
-        <v>81.30686033444687</v>
+        <v>80.48958087533452</v>
       </c>
     </row>
     <row r="75">
@@ -5802,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>78.048517344999</v>
+        <v>77.13338478315717</v>
       </c>
       <c r="T75" t="n">
-        <v>78.048517344999</v>
+        <v>77.13338478315717</v>
       </c>
     </row>
     <row r="76">
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>81.20836225154224</v>
+        <v>80.38812474195564</v>
       </c>
       <c r="T76" t="n">
-        <v>81.20836225154224</v>
+        <v>80.38812474195564</v>
       </c>
     </row>
     <row r="77">
@@ -5950,10 +5950,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>72.98610512282005</v>
+        <v>71.91894045605864</v>
       </c>
       <c r="T77" t="n">
-        <v>72.98610512282005</v>
+        <v>71.91894045605864</v>
       </c>
     </row>
     <row r="78">
@@ -6024,10 +6024,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>78.03999422402194</v>
+        <v>77.12460569961408</v>
       </c>
       <c r="T78" t="n">
-        <v>78.03999422402194</v>
+        <v>77.12460569961408</v>
       </c>
     </row>
     <row r="79">
@@ -6098,10 +6098,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>78.99167319451951</v>
+        <v>78.10486506829787</v>
       </c>
       <c r="T79" t="n">
-        <v>78.99167319451951</v>
+        <v>78.10486506829787</v>
       </c>
     </row>
     <row r="80">
@@ -6172,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>72.89692078625197</v>
+        <v>71.82707777529035</v>
       </c>
       <c r="T80" t="n">
-        <v>72.89692078625197</v>
+        <v>71.82707777529035</v>
       </c>
     </row>
     <row r="81">
@@ -6246,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>74.47684323952356</v>
+        <v>73.45444775468957</v>
       </c>
       <c r="T81" t="n">
-        <v>74.47684323952356</v>
+        <v>73.45444775468957</v>
       </c>
     </row>
     <row r="82">
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>72.41374411806532</v>
+        <v>71.32939056100662</v>
       </c>
       <c r="T82" t="n">
-        <v>72.41374411806532</v>
+        <v>71.32939056100662</v>
       </c>
     </row>
     <row r="83">
@@ -6394,10 +6394,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>59.18337599446452</v>
+        <v>57.70169392553954</v>
       </c>
       <c r="T83" t="n">
-        <v>59.18337599446452</v>
+        <v>57.70169392553954</v>
       </c>
     </row>
     <row r="84">
@@ -6607,13 +6607,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S86" t="n">
-        <v>25.0201871358634</v>
+        <v>28.74658826782138</v>
       </c>
       <c r="T86" t="n">
-        <v>25.0201871358634</v>
+        <v>28.74658826782138</v>
       </c>
     </row>
     <row r="87">
@@ -6681,13 +6681,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S87" t="n">
-        <v>23.28186561349267</v>
+        <v>26.9560622491603</v>
       </c>
       <c r="T87" t="n">
-        <v>23.28186561349267</v>
+        <v>26.9560622491603</v>
       </c>
     </row>
     <row r="88">
@@ -6755,13 +6755,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S88" t="n">
-        <v>22.41270485230731</v>
+        <v>26.06079923982975</v>
       </c>
       <c r="T88" t="n">
-        <v>22.41270485230731</v>
+        <v>26.06079923982975</v>
       </c>
     </row>
     <row r="89">
@@ -6829,13 +6829,13 @@
         <v>-2.541280000000015</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S89" t="n">
-        <v>19.29465145200938</v>
+        <v>22.84910585114404</v>
       </c>
       <c r="T89" t="n">
-        <v>19.29465145200938</v>
+        <v>22.84910585114404</v>
       </c>
     </row>
     <row r="90">
@@ -6903,13 +6903,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S90" t="n">
-        <v>20.79027143142797</v>
+        <v>24.38964162241274</v>
       </c>
       <c r="T90" t="n">
-        <v>20.79027143142797</v>
+        <v>24.38964162241274</v>
       </c>
     </row>
     <row r="91">
@@ -6977,13 +6977,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S91" t="n">
-        <v>20.73232738068228</v>
+        <v>24.32995742179071</v>
       </c>
       <c r="T91" t="n">
-        <v>20.73232738068228</v>
+        <v>24.32995742179071</v>
       </c>
     </row>
     <row r="92">
@@ -7051,13 +7051,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S92" t="n">
-        <v>20.55849522844521</v>
+        <v>24.15090481992459</v>
       </c>
       <c r="T92" t="n">
-        <v>20.55849522844521</v>
+        <v>24.15090481992459</v>
       </c>
     </row>
     <row r="93">
@@ -7125,13 +7125,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S93" t="n">
-        <v>20.52372879799779</v>
+        <v>24.11509429955137</v>
       </c>
       <c r="T93" t="n">
-        <v>20.52372879799779</v>
+        <v>24.11509429955137</v>
       </c>
     </row>
     <row r="94">
@@ -7199,13 +7199,13 @@
         <v>-2.541280000000015</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>9.063867016622922</v>
       </c>
       <c r="S94" t="n">
-        <v>11.78510247536785</v>
+        <v>15.11403345052815</v>
       </c>
       <c r="T94" t="n">
-        <v>11.78510247536785</v>
+        <v>15.11403345052815</v>
       </c>
     </row>
     <row r="95">
@@ -7278,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>72.00081344401215</v>
+        <v>70.90405893720717</v>
       </c>
       <c r="T95" t="n">
-        <v>72.00081344401215</v>
+        <v>70.90405893720717</v>
       </c>
     </row>
     <row r="96">
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>70.71913416758105</v>
+        <v>69.583888840654</v>
       </c>
       <c r="T96" t="n">
-        <v>70.71913416758105</v>
+        <v>69.583888840654</v>
       </c>
     </row>
     <row r="97">
@@ -7426,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>68.38097976002695</v>
+        <v>67.17551602325764</v>
       </c>
       <c r="T97" t="n">
-        <v>68.38097976002695</v>
+        <v>67.17551602325764</v>
       </c>
     </row>
     <row r="98">
@@ -7500,10 +7500,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>63.60945527111908</v>
+        <v>62.26069524003659</v>
       </c>
       <c r="T98" t="n">
-        <v>63.60945527111908</v>
+        <v>62.26069524003659</v>
       </c>
     </row>
     <row r="99">
@@ -7574,10 +7574,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>59.7039745657349</v>
+        <v>58.23792688080211</v>
       </c>
       <c r="T99" t="n">
-        <v>59.7039745657349</v>
+        <v>58.23792688080211</v>
       </c>
     </row>
     <row r="100">
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>62.2930031969792</v>
+        <v>60.90470806463008</v>
       </c>
       <c r="T100" t="n">
-        <v>62.2930031969792</v>
+        <v>60.90470806463008</v>
       </c>
     </row>
     <row r="101">
@@ -7722,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>58.48273816539466</v>
+        <v>56.98001485382392</v>
       </c>
       <c r="T101" t="n">
-        <v>58.48273816539466</v>
+        <v>56.98001485382392</v>
       </c>
     </row>
     <row r="102">
@@ -7796,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>48.58449657076238</v>
+        <v>46.78451368439018</v>
       </c>
       <c r="T102" t="n">
-        <v>48.58449657076238</v>
+        <v>46.78451368439018</v>
       </c>
     </row>
     <row r="103">
@@ -7870,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>46.85240900371505</v>
+        <v>45.00040883641707</v>
       </c>
       <c r="T103" t="n">
-        <v>46.85240900371505</v>
+        <v>45.00040883641707</v>
       </c>
     </row>
     <row r="104">
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>46.49721638689847</v>
+        <v>44.63454923342542</v>
       </c>
       <c r="T104" t="n">
-        <v>46.49721638689847</v>
+        <v>44.63454923342542</v>
       </c>
     </row>
     <row r="105">
@@ -8018,10 +8018,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>45.69707711106171</v>
+        <v>43.81038053189286</v>
       </c>
       <c r="T105" t="n">
-        <v>45.69707711106171</v>
+        <v>43.81038053189286</v>
       </c>
     </row>
     <row r="106">
@@ -8092,10 +8092,10 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>40.96032541986263</v>
+        <v>38.93137682752516</v>
       </c>
       <c r="T106" t="n">
-        <v>40.96032541986263</v>
+        <v>38.93137682752516</v>
       </c>
     </row>
     <row r="107">
@@ -8166,10 +8166,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>48.86468196056535</v>
+        <v>47.0731134767961</v>
       </c>
       <c r="T107" t="n">
-        <v>48.86468196056535</v>
+        <v>47.0731134767961</v>
       </c>
     </row>
     <row r="108">
@@ -8452,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>70.51930312406256</v>
+        <v>69.37805656040467</v>
       </c>
       <c r="T111" t="n">
-        <v>70.51930312406256</v>
+        <v>69.37805656040467</v>
       </c>
     </row>
     <row r="112">
@@ -8526,10 +8526,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>57.6644978904372</v>
+        <v>56.13720155204206</v>
       </c>
       <c r="T112" t="n">
-        <v>57.6644978904372</v>
+        <v>56.13720155204206</v>
       </c>
     </row>
     <row r="113">
@@ -8600,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>61.76207590435195</v>
+        <v>60.35783620045971</v>
       </c>
       <c r="T113" t="n">
-        <v>61.76207590435195</v>
+        <v>60.35783620045971</v>
       </c>
     </row>
     <row r="114">
@@ -8674,10 +8674,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>55.72886367018783</v>
+        <v>54.14343722860401</v>
       </c>
       <c r="T114" t="n">
-        <v>55.72886367018783</v>
+        <v>54.14343722860401</v>
       </c>
     </row>
     <row r="115">
@@ -8748,10 +8748,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>56.22160164849851</v>
+        <v>54.65097289401101</v>
       </c>
       <c r="T115" t="n">
-        <v>56.22160164849851</v>
+        <v>54.65097289401101</v>
       </c>
     </row>
     <row r="116">
@@ -8822,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>59.36291808788365</v>
+        <v>57.88662794699341</v>
       </c>
       <c r="T116" t="n">
-        <v>59.36291808788365</v>
+        <v>57.88662794699341</v>
       </c>
     </row>
     <row r="117">
@@ -8896,10 +8896,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>56.93454588932361</v>
+        <v>55.38532795814837</v>
       </c>
       <c r="T117" t="n">
-        <v>56.93454588932361</v>
+        <v>55.38532795814837</v>
       </c>
     </row>
     <row r="118">
@@ -8970,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>48.77418668552091</v>
+        <v>46.9799004880321</v>
       </c>
       <c r="T118" t="n">
-        <v>48.77418668552091</v>
+        <v>46.9799004880321</v>
       </c>
     </row>
     <row r="119">
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>51.0809002172287</v>
+        <v>49.3558882112282</v>
       </c>
       <c r="T119" t="n">
-        <v>51.0809002172287</v>
+        <v>49.3558882112282</v>
       </c>
     </row>
     <row r="120">
@@ -9118,10 +9118,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>51.13322567051057</v>
+        <v>49.4097850791745</v>
       </c>
       <c r="T120" t="n">
-        <v>51.13322567051057</v>
+        <v>49.4097850791745</v>
       </c>
     </row>
     <row r="121">
@@ -9192,10 +9192,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>41.02554649362181</v>
+        <v>38.99855659146869</v>
       </c>
       <c r="T121" t="n">
-        <v>41.02554649362181</v>
+        <v>38.99855659146869</v>
       </c>
     </row>
     <row r="122">
@@ -9266,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>51.0115670036583</v>
+        <v>49.28447281352555</v>
       </c>
       <c r="T122" t="n">
-        <v>51.0115670036583</v>
+        <v>49.28447281352555</v>
       </c>
     </row>
     <row r="123">
@@ -9340,10 +9340,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>47.92257601755504</v>
+        <v>46.10271462848945</v>
       </c>
       <c r="T123" t="n">
-        <v>47.92257601755504</v>
+        <v>46.10271462848945</v>
       </c>
     </row>
     <row r="124">
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>37.3975953868276</v>
+        <v>35.26165247589049</v>
       </c>
       <c r="T124" t="n">
-        <v>37.3975953868276</v>
+        <v>35.26165247589049</v>
       </c>
     </row>
     <row r="125">
@@ -9488,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>45.45595335601379</v>
+        <v>43.56201545582699</v>
       </c>
       <c r="T125" t="n">
-        <v>45.45595335601379</v>
+        <v>43.56201545582699</v>
       </c>
     </row>
     <row r="126">
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>45.87325480985247</v>
+        <v>43.99184912072013</v>
       </c>
       <c r="T126" t="n">
-        <v>45.87325480985247</v>
+        <v>43.99184912072013</v>
       </c>
     </row>
     <row r="127">
@@ -9638,10 +9638,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>71.2653724379573</v>
+        <v>70.14653149502513</v>
       </c>
       <c r="T127" t="n">
-        <v>71.2653724379573</v>
+        <v>70.14653149502513</v>
       </c>
     </row>
     <row r="128">
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>69.3755072823449</v>
+        <v>68.19991075235026</v>
       </c>
       <c r="T128" t="n">
-        <v>69.3755072823449</v>
+        <v>68.19991075235026</v>
       </c>
     </row>
     <row r="129">
@@ -9786,10 +9786,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>67.70448915601699</v>
+        <v>66.47870935528999</v>
       </c>
       <c r="T129" t="n">
-        <v>67.70448915601699</v>
+        <v>66.47870935528999</v>
       </c>
     </row>
     <row r="130">
@@ -9860,10 +9860,10 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>69.49490056048069</v>
+        <v>68.32288959613965</v>
       </c>
       <c r="T130" t="n">
-        <v>69.49490056048069</v>
+        <v>68.32288959613965</v>
       </c>
     </row>
     <row r="131">
@@ -9934,10 +9934,10 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>69.81320134091391</v>
+        <v>68.65074944357949</v>
       </c>
       <c r="T131" t="n">
-        <v>69.81320134091391</v>
+        <v>68.65074944357949</v>
       </c>
     </row>
     <row r="132">
@@ -10008,10 +10008,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>68.24163696573473</v>
+        <v>67.03198854834443</v>
       </c>
       <c r="T132" t="n">
-        <v>68.24163696573473</v>
+        <v>67.03198854834443</v>
       </c>
     </row>
     <row r="133">
@@ -10082,10 +10082,10 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>65.61571649810713</v>
+        <v>64.32720760896467</v>
       </c>
       <c r="T133" t="n">
-        <v>65.61571649810713</v>
+        <v>64.32720760896467</v>
       </c>
     </row>
     <row r="134">
@@ -10156,10 +10156,10 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>65.19796196652516</v>
+        <v>63.89690725969961</v>
       </c>
       <c r="T134" t="n">
-        <v>65.19796196652516</v>
+        <v>63.89690725969961</v>
       </c>
     </row>
     <row r="135">
@@ -10230,10 +10230,10 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>64.3624529033612</v>
+        <v>63.03630656116949</v>
       </c>
       <c r="T135" t="n">
-        <v>64.3624529033612</v>
+        <v>63.03630656116949</v>
       </c>
     </row>
     <row r="136">
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>66.15286430782487</v>
+        <v>64.88048680201911</v>
       </c>
       <c r="T136" t="n">
-        <v>66.15286430782487</v>
+        <v>64.88048680201911</v>
       </c>
     </row>
     <row r="137">
@@ -10378,10 +10378,10 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>65.31735524466092</v>
+        <v>64.01988610348897</v>
       </c>
       <c r="T137" t="n">
-        <v>65.31735524466092</v>
+        <v>64.01988610348897</v>
       </c>
     </row>
     <row r="138">
@@ -10452,10 +10452,10 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>61.97531899200511</v>
+        <v>60.57748330936847</v>
       </c>
       <c r="T138" t="n">
-        <v>61.97531899200511</v>
+        <v>60.57748330936847</v>
       </c>
     </row>
     <row r="139">
@@ -10526,10 +10526,10 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>58.09613492963156</v>
+        <v>56.5818013221935</v>
       </c>
       <c r="T139" t="n">
-        <v>58.09613492963156</v>
+        <v>56.5818013221935</v>
       </c>
     </row>
     <row r="140">
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>53.13909804582999</v>
+        <v>51.47589691861418</v>
       </c>
       <c r="T140" t="n">
-        <v>53.13909804582999</v>
+        <v>51.47589691861418</v>
       </c>
     </row>
     <row r="141">
@@ -10676,10 +10676,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>52.66307335623635</v>
+        <v>50.9855764679532</v>
       </c>
       <c r="T141" t="n">
-        <v>52.66307335623635</v>
+        <v>50.9855764679532</v>
       </c>
     </row>
     <row r="142">
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>49.97888273059705</v>
+        <v>48.22077542717751</v>
       </c>
       <c r="T142" t="n">
-        <v>49.97888273059705</v>
+        <v>48.22077542717751</v>
       </c>
     </row>
     <row r="143">
@@ -10824,10 +10824,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>48.83880075137888</v>
+        <v>47.04645501468399</v>
       </c>
       <c r="T143" t="n">
-        <v>48.83880075137888</v>
+        <v>47.04645501468399</v>
       </c>
     </row>
     <row r="144">
@@ -10898,10 +10898,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>47.95874939458228</v>
+        <v>46.13997434823439</v>
       </c>
       <c r="T144" t="n">
-        <v>47.95874939458228</v>
+        <v>46.13997434823439</v>
       </c>
     </row>
     <row r="145">
@@ -10972,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>45.70210025847229</v>
+        <v>43.81555453222506</v>
       </c>
       <c r="T145" t="n">
-        <v>45.70210025847229</v>
+        <v>43.81555453222506</v>
       </c>
     </row>
     <row r="146">
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>38.21362618164704</v>
+        <v>36.10218994341273</v>
       </c>
       <c r="T146" t="n">
-        <v>38.21362618164704</v>
+        <v>36.10218994341273</v>
       </c>
     </row>
     <row r="147">
@@ -11122,10 +11122,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>66.38992588630163</v>
+        <v>65.12466770803968</v>
       </c>
       <c r="T147" t="n">
-        <v>66.38992588630163</v>
+        <v>65.12466770803968</v>
       </c>
     </row>
     <row r="148">
@@ -11196,10 +11196,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>67.66943488716043</v>
+        <v>66.44260235227296</v>
       </c>
       <c r="T148" t="n">
-        <v>67.66943488716043</v>
+        <v>66.44260235227296</v>
       </c>
     </row>
     <row r="149">
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>66.28217468115872</v>
+        <v>65.01368056678439</v>
       </c>
       <c r="T149" t="n">
-        <v>66.28217468115872</v>
+        <v>65.01368056678439</v>
       </c>
     </row>
     <row r="150">
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>63.79655670391272</v>
+        <v>62.45341561957195</v>
       </c>
       <c r="T150" t="n">
-        <v>63.79655670391272</v>
+        <v>62.45341561957195</v>
       </c>
     </row>
     <row r="151">
@@ -11418,10 +11418,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>57.30740855116188</v>
+        <v>55.76938826506913</v>
       </c>
       <c r="T151" t="n">
-        <v>57.30740855116188</v>
+        <v>55.76938826506913</v>
       </c>
     </row>
     <row r="152">
@@ -11492,10 +11492,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>52.69847505589895</v>
+        <v>51.0220413356632</v>
       </c>
       <c r="T152" t="n">
-        <v>52.69847505589895</v>
+        <v>51.0220413356632</v>
       </c>
     </row>
     <row r="153">
@@ -11566,10 +11566,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>51.20346364475431</v>
+        <v>49.48213240891933</v>
       </c>
       <c r="T153" t="n">
-        <v>51.20346364475431</v>
+        <v>49.48213240891933</v>
       </c>
     </row>
     <row r="154">
@@ -11712,10 +11712,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>63.70188639660388</v>
+        <v>62.35590221583757</v>
       </c>
       <c r="T155" t="n">
-        <v>63.70188639660388</v>
+        <v>62.35590221583757</v>
       </c>
     </row>
     <row r="156">
@@ -11786,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>65.82810591269083</v>
+        <v>64.54597540767529</v>
       </c>
       <c r="T156" t="n">
-        <v>65.82810591269083</v>
+        <v>64.54597540767529</v>
       </c>
     </row>
     <row r="157">
@@ -11860,10 +11860,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>64.7812391918778</v>
+        <v>63.46766965263304</v>
       </c>
       <c r="T157" t="n">
-        <v>64.7812391918778</v>
+        <v>63.46766965263304</v>
       </c>
     </row>
     <row r="158">
@@ -11934,10 +11934,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>54.08370699490825</v>
+        <v>52.44887394215012</v>
       </c>
       <c r="T158" t="n">
-        <v>54.08370699490825</v>
+        <v>52.44887394215012</v>
       </c>
     </row>
     <row r="159">
@@ -12008,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>53.56027363450172</v>
+        <v>51.90972106462898</v>
       </c>
       <c r="T159" t="n">
-        <v>53.56027363450172</v>
+        <v>51.90972106462898</v>
       </c>
     </row>
     <row r="160">
@@ -12082,10 +12082,10 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>53.5927597089626</v>
+        <v>51.94318274638221</v>
       </c>
       <c r="T160" t="n">
-        <v>53.5927597089626</v>
+        <v>51.94318274638221</v>
       </c>
     </row>
     <row r="161">
@@ -12156,10 +12156,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>42.04473970555826</v>
+        <v>40.04835775916418</v>
       </c>
       <c r="T161" t="n">
-        <v>42.04473970555826</v>
+        <v>40.04835775916418</v>
       </c>
     </row>
     <row r="162">
@@ -12232,10 +12232,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>49.55913569190314</v>
+        <v>47.78842273271603</v>
       </c>
       <c r="T162" t="n">
-        <v>49.55913569190314</v>
+        <v>47.78842273271603</v>
       </c>
     </row>
     <row r="163">
@@ -12306,10 +12306,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>42.67614894489898</v>
+        <v>40.69872919903493</v>
       </c>
       <c r="T163" t="n">
-        <v>42.67614894489898</v>
+        <v>40.69872919903493</v>
       </c>
     </row>
     <row r="164">
@@ -12380,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>34.32105157386439</v>
+        <v>32.09271527194403</v>
       </c>
       <c r="T164" t="n">
-        <v>34.32105157386439</v>
+        <v>32.09271527194403</v>
       </c>
     </row>
     <row r="165">
@@ -12454,10 +12454,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>36.81436647834411</v>
+        <v>34.66090829707436</v>
       </c>
       <c r="T165" t="n">
-        <v>36.81436647834411</v>
+        <v>34.66090829707436</v>
       </c>
     </row>
     <row r="166">
@@ -12528,10 +12528,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>35.58103904088767</v>
+        <v>33.39054212034851</v>
       </c>
       <c r="T166" t="n">
-        <v>35.58103904088767</v>
+        <v>33.39054212034851</v>
       </c>
     </row>
     <row r="167">
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>34.67922635372538</v>
+        <v>32.46164659696996</v>
       </c>
       <c r="T167" t="n">
-        <v>34.67922635372538</v>
+        <v>32.46164659696996</v>
       </c>
     </row>
     <row r="168">
@@ -12676,10 +12676,10 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>30.50167766820809</v>
+        <v>28.15863963342451</v>
       </c>
       <c r="T168" t="n">
-        <v>30.50167766820809</v>
+        <v>28.15863963342451</v>
       </c>
     </row>
     <row r="169">
@@ -12750,10 +12750,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>29.5998649810458</v>
+        <v>27.22974411004597</v>
       </c>
       <c r="T169" t="n">
-        <v>29.5998649810458</v>
+        <v>27.22974411004597</v>
       </c>
     </row>
     <row r="170">
@@ -12824,10 +12824,10 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>20.58173810942291</v>
+        <v>17.94078887626047</v>
       </c>
       <c r="T170" t="n">
-        <v>20.58173810942291</v>
+        <v>17.94078887626047</v>
       </c>
     </row>
     <row r="171">
@@ -13180,10 +13180,10 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>66.90371104828034</v>
+        <v>65.65388263674299</v>
       </c>
       <c r="T175" t="n">
-        <v>66.90371104828034</v>
+        <v>65.65388263674299</v>
       </c>
     </row>
     <row r="176">
@@ -13254,10 +13254,10 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>62.04020917696303</v>
+        <v>60.6443222474059</v>
       </c>
       <c r="T176" t="n">
-        <v>62.04020917696303</v>
+        <v>60.6443222474059</v>
       </c>
     </row>
     <row r="177">
@@ -13328,10 +13328,10 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>54.51355169630472</v>
+        <v>52.89162754781469</v>
       </c>
       <c r="T177" t="n">
-        <v>54.51355169630472</v>
+        <v>52.89162754781469</v>
       </c>
     </row>
     <row r="178">
@@ -13402,10 +13402,10 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>40.63141733428367</v>
+        <v>38.59259112108464</v>
       </c>
       <c r="T178" t="n">
-        <v>40.63141733428367</v>
+        <v>38.59259112108464</v>
       </c>
     </row>
     <row r="179">
@@ -13476,10 +13476,10 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>30.47710797843804</v>
+        <v>28.13333207769472</v>
       </c>
       <c r="T179" t="n">
-        <v>30.47710797843804</v>
+        <v>28.13333207769472</v>
       </c>
     </row>
     <row r="180">
@@ -13550,10 +13550,10 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>33.10475985362534</v>
+        <v>30.83989642149341</v>
       </c>
       <c r="T180" t="n">
-        <v>33.10475985362534</v>
+        <v>30.83989642149341</v>
       </c>
     </row>
     <row r="181">
@@ -13624,10 +13624,10 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>33.36596110633019</v>
+        <v>31.10894195366692</v>
       </c>
       <c r="T181" t="n">
-        <v>33.36596110633019</v>
+        <v>31.10894195366692</v>
       </c>
     </row>
     <row r="182">
@@ -13840,10 +13840,10 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>60.60825584082639</v>
+        <v>59.16936512764104</v>
       </c>
       <c r="T184" t="n">
-        <v>60.60825584082639</v>
+        <v>59.16936512764104</v>
       </c>
     </row>
     <row r="185">
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>55.38272539011666</v>
+        <v>53.78690387815869</v>
       </c>
       <c r="T185" t="n">
-        <v>55.38272539011666</v>
+        <v>53.78690387815869</v>
       </c>
     </row>
     <row r="186">
@@ -13988,10 +13988,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>48.6850843153765</v>
+        <v>46.88812223526654</v>
       </c>
       <c r="T186" t="n">
-        <v>48.6850843153765</v>
+        <v>46.88812223526654</v>
       </c>
     </row>
     <row r="187">
@@ -14062,10 +14062,10 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>46.80837440203685</v>
+        <v>44.95505180723027</v>
       </c>
       <c r="T187" t="n">
-        <v>46.80837440203685</v>
+        <v>44.95505180723027</v>
       </c>
     </row>
     <row r="188">
@@ -14136,10 +14136,10 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>48.81424069342788</v>
+        <v>47.02115738003173</v>
       </c>
       <c r="T188" t="n">
-        <v>48.81424069342788</v>
+        <v>47.02115738003173</v>
       </c>
     </row>
     <row r="189">
@@ -14210,10 +14210,10 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>46.93753078008823</v>
+        <v>45.08808695199546</v>
       </c>
       <c r="T189" t="n">
-        <v>46.93753078008823</v>
+        <v>45.08808695199546</v>
       </c>
     </row>
     <row r="190">
@@ -14284,10 +14284,10 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>30.04714156003138</v>
+        <v>27.690453099669</v>
       </c>
       <c r="T190" t="n">
-        <v>30.04714156003138</v>
+        <v>27.690453099669</v>
       </c>
     </row>
     <row r="191">
@@ -14358,10 +14358,10 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>22.8157448179306</v>
+        <v>20.24188627738519</v>
       </c>
       <c r="T191" t="n">
-        <v>22.8157448179306</v>
+        <v>20.24188627738519</v>
       </c>
     </row>
     <row r="192">
@@ -14784,10 +14784,10 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>60.2353829414904</v>
+        <v>58.7852942757746</v>
       </c>
       <c r="T197" t="n">
-        <v>60.2353829414904</v>
+        <v>58.7852942757746</v>
       </c>
     </row>
     <row r="198">
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>58.6694802893069</v>
+        <v>57.17236513387388</v>
       </c>
       <c r="T198" t="n">
-        <v>58.6694802893069</v>
+        <v>57.17236513387388</v>
       </c>
     </row>
     <row r="199">
@@ -14932,10 +14932,10 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>45.53859634787764</v>
+        <v>43.64714034514573</v>
       </c>
       <c r="T199" t="n">
-        <v>45.53859634787764</v>
+        <v>43.64714034514573</v>
       </c>
     </row>
     <row r="200">
@@ -15006,10 +15006,10 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>46.54174683114275</v>
+        <v>44.68041699610097</v>
       </c>
       <c r="T200" t="n">
-        <v>46.54174683114275</v>
+        <v>44.68041699610097</v>
       </c>
     </row>
     <row r="201">
@@ -15080,10 +15080,10 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>43.72798598655076</v>
+        <v>41.7821545413735</v>
       </c>
       <c r="T201" t="n">
-        <v>43.72798598655076</v>
+        <v>41.7821545413735</v>
       </c>
     </row>
     <row r="202">
@@ -15154,10 +15154,10 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>39.44211451792834</v>
+        <v>37.36757169323624</v>
       </c>
       <c r="T202" t="n">
-        <v>39.44211451792834</v>
+        <v>37.36757169323624</v>
       </c>
     </row>
     <row r="203">
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>38.50419423639767</v>
+        <v>36.40148420832708</v>
       </c>
       <c r="T203" t="n">
-        <v>38.50419423639767</v>
+        <v>36.40148420832708</v>
       </c>
     </row>
     <row r="204">
@@ -15302,10 +15302,10 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>32.68098194201038</v>
+        <v>30.40339180073395</v>
       </c>
       <c r="T204" t="n">
-        <v>32.68098194201038</v>
+        <v>30.40339180073395</v>
       </c>
     </row>
     <row r="205">
@@ -15376,10 +15376,10 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>29.33303075491863</v>
+        <v>26.95489643750584</v>
       </c>
       <c r="T205" t="n">
-        <v>29.33303075491863</v>
+        <v>26.95489643750584</v>
       </c>
     </row>
     <row r="206">
@@ -15450,10 +15450,10 @@
         <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>32.40771240644838</v>
+        <v>30.12191555641759</v>
       </c>
       <c r="T206" t="n">
-        <v>32.40771240644838</v>
+        <v>30.12191555641759</v>
       </c>
     </row>
     <row r="207">
@@ -15524,10 +15524,10 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>31.06606218588683</v>
+        <v>28.73997349509994</v>
       </c>
       <c r="T207" t="n">
-        <v>31.06606218588683</v>
+        <v>28.73997349509994</v>
       </c>
     </row>
     <row r="208">
@@ -15880,10 +15880,10 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>70.3256294664005</v>
+        <v>69.17856658187628</v>
       </c>
       <c r="T212" t="n">
-        <v>70.3256294664005</v>
+        <v>69.17856658187628</v>
       </c>
     </row>
     <row r="213">
@@ -15954,10 +15954,10 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>58.49206527256383</v>
+        <v>56.98962206851367</v>
       </c>
       <c r="T213" t="n">
-        <v>58.49206527256383</v>
+        <v>56.98962206851367</v>
       </c>
     </row>
     <row r="214">
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>57.81777142513244</v>
+        <v>56.29507812913793</v>
       </c>
       <c r="T214" t="n">
-        <v>57.81777142513244</v>
+        <v>56.29507812913793</v>
       </c>
     </row>
     <row r="215">
@@ -16102,10 +16102,10 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>49.84976818512333</v>
+        <v>48.0877833712873</v>
       </c>
       <c r="T215" t="n">
-        <v>49.84976818512333</v>
+        <v>48.0877833712873</v>
       </c>
     </row>
     <row r="216">
@@ -16176,10 +16176,10 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>52.1196955857528</v>
+        <v>50.42588021873116</v>
       </c>
       <c r="T216" t="n">
-        <v>52.1196955857528</v>
+        <v>50.42588021873116</v>
       </c>
     </row>
     <row r="217">
@@ -16250,10 +16250,10 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>45.68048217136731</v>
+        <v>43.79328722037451</v>
       </c>
       <c r="T217" t="n">
-        <v>45.68048217136731</v>
+        <v>43.79328722037451</v>
       </c>
     </row>
     <row r="218">
@@ -16324,10 +16324,10 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>37.47371250840116</v>
+        <v>35.34005551289436</v>
       </c>
       <c r="T218" t="n">
-        <v>37.47371250840116</v>
+        <v>35.34005551289436</v>
       </c>
     </row>
     <row r="219">
@@ -16470,10 +16470,10 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>83.57565950730648</v>
+        <v>82.82651561257558</v>
       </c>
       <c r="T220" t="n">
-        <v>83.57565950730648</v>
+        <v>82.82651561257558</v>
       </c>
     </row>
     <row r="221">
@@ -16544,10 +16544,10 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>71.80330828049688</v>
+        <v>70.70062238675146</v>
       </c>
       <c r="T221" t="n">
-        <v>71.80330828049688</v>
+        <v>70.70062238675146</v>
       </c>
     </row>
     <row r="222">
@@ -16618,10 +16618,10 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>64.23763508883621</v>
+        <v>62.90774027373457</v>
       </c>
       <c r="T222" t="n">
-        <v>64.23763508883621</v>
+        <v>62.90774027373457</v>
       </c>
     </row>
     <row r="223">
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>48.16057955655727</v>
+        <v>46.34786578357365</v>
       </c>
       <c r="T223" t="n">
-        <v>48.16057955655727</v>
+        <v>46.34786578357365</v>
       </c>
     </row>
     <row r="224">
@@ -16978,10 +16978,10 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>55.50429135727116</v>
+        <v>53.91212066019392</v>
       </c>
       <c r="T227" t="n">
-        <v>55.50429135727116</v>
+        <v>53.91212066019392</v>
       </c>
     </row>
     <row r="228">
@@ -17052,10 +17052,10 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>50.95486266964176</v>
+        <v>49.2260655602523</v>
       </c>
       <c r="T228" t="n">
-        <v>50.95486266964176</v>
+        <v>49.2260655602523</v>
       </c>
     </row>
     <row r="229">
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>47.4312066698787</v>
+        <v>45.5965886958213</v>
       </c>
       <c r="T229" t="n">
-        <v>47.4312066698787</v>
+        <v>45.5965886958213</v>
       </c>
     </row>
     <row r="230">
@@ -17200,10 +17200,10 @@
         <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>45.11346766306987</v>
+        <v>43.20924438537568</v>
       </c>
       <c r="T230" t="n">
-        <v>45.11346766306987</v>
+        <v>43.20924438537568</v>
       </c>
     </row>
     <row r="231">
@@ -17274,10 +17274,10 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>38.51249359970783</v>
+        <v>36.41003281441285</v>
       </c>
       <c r="T231" t="n">
-        <v>38.51249359970783</v>
+        <v>36.41003281441285</v>
       </c>
     </row>
     <row r="232">
@@ -17348,10 +17348,10 @@
         <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>24.59801390574346</v>
+        <v>22.0776796751636</v>
       </c>
       <c r="T232" t="n">
-        <v>24.59801390574346</v>
+        <v>22.0776796751636</v>
       </c>
     </row>
     <row r="233">
@@ -17422,10 +17422,10 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>12.1085973462597</v>
+        <v>9.213186530561574</v>
       </c>
       <c r="T233" t="n">
-        <v>12.1085973462597</v>
+        <v>9.213186530561574</v>
       </c>
     </row>
     <row r="234">
@@ -17638,10 +17638,10 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>57.09818426111585</v>
+        <v>55.55388064450398</v>
       </c>
       <c r="T236" t="n">
-        <v>57.09818426111585</v>
+        <v>55.55388064450398</v>
       </c>
     </row>
     <row r="237">
@@ -17712,10 +17712,10 @@
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>61.07180668260186</v>
+        <v>59.64683712145221</v>
       </c>
       <c r="T237" t="n">
-        <v>61.07180668260186</v>
+        <v>59.64683712145221</v>
       </c>
     </row>
     <row r="238">
@@ -17786,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>62.10120785602701</v>
+        <v>60.70715281158085</v>
       </c>
       <c r="T238" t="n">
-        <v>62.10120785602701</v>
+        <v>60.70715281158085</v>
       </c>
     </row>
     <row r="239">
@@ -17860,10 +17860,10 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>42.05682557449752</v>
+        <v>40.06080658552649</v>
       </c>
       <c r="T239" t="n">
-        <v>42.05682557449752</v>
+        <v>40.06080658552649</v>
       </c>
     </row>
     <row r="240">
@@ -17934,10 +17934,10 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>40.2752251381147</v>
+        <v>38.22570191981951</v>
       </c>
       <c r="T240" t="n">
-        <v>40.2752251381147</v>
+        <v>38.22570191981951</v>
       </c>
     </row>
     <row r="241">
@@ -18008,10 +18008,10 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>30.11443304211623</v>
+        <v>27.75976544951719</v>
       </c>
       <c r="T241" t="n">
-        <v>30.11443304211623</v>
+        <v>27.75976544951719</v>
       </c>
     </row>
     <row r="242">
@@ -18082,10 +18082,10 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>34.52000228024588</v>
+        <v>32.29764077716428</v>
       </c>
       <c r="T242" t="n">
-        <v>34.52000228024588</v>
+        <v>32.29764077716428</v>
       </c>
     </row>
     <row r="243">
@@ -18228,10 +18228,10 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>50.46765956436265</v>
+        <v>48.72423098871399</v>
       </c>
       <c r="T244" t="n">
-        <v>50.46765956436265</v>
+        <v>48.72423098871399</v>
       </c>
     </row>
     <row r="245">
@@ -18302,10 +18302,10 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>46.44678381774956</v>
+        <v>44.58260209586372</v>
       </c>
       <c r="T245" t="n">
-        <v>46.44678381774956</v>
+        <v>44.58260209586372</v>
       </c>
     </row>
     <row r="246">
@@ -18376,10 +18376,10 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>49.25476539119563</v>
+        <v>47.47491171895302</v>
       </c>
       <c r="T246" t="n">
-        <v>49.25476539119563</v>
+        <v>47.47491171895302</v>
       </c>
     </row>
     <row r="247">
@@ -18450,10 +18450,10 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>40.01338262316864</v>
+        <v>37.95599586730329</v>
       </c>
       <c r="T247" t="n">
-        <v>40.01338262316864</v>
+        <v>37.95599586730329</v>
       </c>
     </row>
     <row r="248">
@@ -18524,10 +18524,10 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>31.56291210609807</v>
+        <v>29.25174459041183</v>
       </c>
       <c r="T248" t="n">
-        <v>31.56291210609807</v>
+        <v>29.25174459041183</v>
       </c>
     </row>
     <row r="249">
@@ -18670,10 +18670,10 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>69.88353817232982</v>
+        <v>68.72319859933094</v>
       </c>
       <c r="T250" t="n">
-        <v>69.88353817232982</v>
+        <v>68.72319859933094</v>
       </c>
     </row>
     <row r="251">
@@ -18744,10 +18744,10 @@
         <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>58.89642067458443</v>
+        <v>57.4061208915373</v>
       </c>
       <c r="T251" t="n">
-        <v>58.89642067458443</v>
+        <v>57.4061208915373</v>
       </c>
     </row>
     <row r="252">
@@ -18818,10 +18818,10 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>53.96833145534388</v>
+        <v>52.33003349586413</v>
       </c>
       <c r="T252" t="n">
-        <v>53.96833145534388</v>
+        <v>52.33003349586413</v>
       </c>
     </row>
     <row r="253">
@@ -18892,10 +18892,10 @@
         <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>47.39754582968979</v>
+        <v>45.56191696829989</v>
       </c>
       <c r="T253" t="n">
-        <v>47.39754582968979</v>
+        <v>45.56191696829989</v>
       </c>
     </row>
     <row r="254">
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>44.93350122006952</v>
+        <v>43.02387327046331</v>
       </c>
       <c r="T254" t="n">
-        <v>44.93350122006952</v>
+        <v>43.02387327046331</v>
       </c>
     </row>
     <row r="255">
@@ -19040,10 +19040,10 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>48.11781078735068</v>
+        <v>46.30381260177442</v>
       </c>
       <c r="T255" t="n">
-        <v>48.11781078735068</v>
+        <v>46.30381260177442</v>
       </c>
     </row>
     <row r="256">
@@ -19114,10 +19114,10 @@
         <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>42.8801307120526</v>
+        <v>40.90883685559948</v>
       </c>
       <c r="T256" t="n">
-        <v>42.8801307120526</v>
+        <v>40.90883685559948</v>
       </c>
     </row>
     <row r="257">
@@ -19188,10 +19188,10 @@
         <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>37.44028414566278</v>
+        <v>35.30562324448253</v>
       </c>
       <c r="T257" t="n">
-        <v>37.44028414566278</v>
+        <v>35.30562324448253</v>
       </c>
     </row>
     <row r="258">
@@ -19331,13 +19331,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S259" t="n">
-        <v>59.52884589083887</v>
+        <v>66.68489144290291</v>
       </c>
       <c r="T259" t="n">
-        <v>59.52884589083887</v>
+        <v>66.68489144290291</v>
       </c>
     </row>
     <row r="260">
@@ -19405,13 +19405,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S260" t="n">
-        <v>45.97059949427648</v>
+        <v>52.71946984048569</v>
       </c>
       <c r="T260" t="n">
-        <v>45.97059949427648</v>
+        <v>52.71946984048569</v>
       </c>
     </row>
     <row r="261">
@@ -19479,13 +19479,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S261" t="n">
-        <v>36.28613778244621</v>
+        <v>42.74416869590197</v>
       </c>
       <c r="T261" t="n">
-        <v>36.28613778244621</v>
+        <v>42.74416869590197</v>
       </c>
     </row>
     <row r="262">
@@ -19553,13 +19553,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S262" t="n">
-        <v>32.4123530977141</v>
+        <v>38.75404823806847</v>
       </c>
       <c r="T262" t="n">
-        <v>32.4123530977141</v>
+        <v>38.75404823806847</v>
       </c>
     </row>
     <row r="263">
@@ -19627,7 +19627,7 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -19697,7 +19697,7 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>12.54354569315199</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -19772,10 +19772,10 @@
         <v>0</v>
       </c>
       <c r="S265" t="n">
-        <v>66.08099075226349</v>
+        <v>64.80645477190836</v>
       </c>
       <c r="T265" t="n">
-        <v>66.08099075226349</v>
+        <v>64.80645477190836</v>
       </c>
     </row>
     <row r="266">
@@ -19846,10 +19846,10 @@
         <v>0</v>
       </c>
       <c r="S266" t="n">
-        <v>64.26488442082146</v>
+        <v>62.93580794549886</v>
       </c>
       <c r="T266" t="n">
-        <v>64.26488442082146</v>
+        <v>62.93580794549886</v>
       </c>
     </row>
     <row r="267">
@@ -19920,10 +19920,10 @@
         <v>0</v>
       </c>
       <c r="S267" t="n">
-        <v>61.84340931223203</v>
+        <v>60.44161217695285</v>
       </c>
       <c r="T267" t="n">
-        <v>61.84340931223203</v>
+        <v>60.44161217695285</v>
       </c>
     </row>
     <row r="268">
@@ -19994,10 +19994,10 @@
         <v>0</v>
       </c>
       <c r="S268" t="n">
-        <v>57.00045909505321</v>
+        <v>55.45322063986082</v>
       </c>
       <c r="T268" t="n">
-        <v>57.00045909505321</v>
+        <v>55.45322063986082</v>
       </c>
     </row>
     <row r="269">
@@ -20068,10 +20068,10 @@
         <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>56.75831158419427</v>
+        <v>55.20380106300622</v>
       </c>
       <c r="T269" t="n">
-        <v>56.75831158419427</v>
+        <v>55.20380106300622</v>
       </c>
     </row>
     <row r="270">
@@ -20142,10 +20142,10 @@
         <v>0</v>
       </c>
       <c r="S270" t="n">
-        <v>47.07241114983663</v>
+        <v>45.22701798882217</v>
       </c>
       <c r="T270" t="n">
-        <v>47.07241114983663</v>
+        <v>45.22701798882217</v>
       </c>
     </row>
     <row r="271">
@@ -20216,10 +20216,10 @@
         <v>0</v>
       </c>
       <c r="S271" t="n">
-        <v>46.46704237268928</v>
+        <v>44.60346904668566</v>
       </c>
       <c r="T271" t="n">
-        <v>46.46704237268928</v>
+        <v>44.60346904668566</v>
       </c>
     </row>
     <row r="272">
@@ -20290,10 +20290,10 @@
         <v>0</v>
       </c>
       <c r="S272" t="n">
-        <v>45.25630481839457</v>
+        <v>43.35637116241265</v>
       </c>
       <c r="T272" t="n">
-        <v>45.25630481839457</v>
+        <v>43.35637116241265</v>
       </c>
     </row>
     <row r="273">
@@ -20364,10 +20364,10 @@
         <v>0</v>
       </c>
       <c r="S273" t="n">
-        <v>33.14892927544752</v>
+        <v>30.88539231968259</v>
       </c>
       <c r="T273" t="n">
-        <v>33.14892927544752</v>
+        <v>30.88539231968259</v>
       </c>
     </row>
     <row r="274">
@@ -20438,10 +20438,10 @@
         <v>0</v>
       </c>
       <c r="S274" t="n">
-        <v>31.93819172115281</v>
+        <v>29.63829443540958</v>
       </c>
       <c r="T274" t="n">
-        <v>31.93819172115281</v>
+        <v>29.63829443540958</v>
       </c>
     </row>
     <row r="275">
@@ -20512,10 +20512,10 @@
         <v>0</v>
       </c>
       <c r="S275" t="n">
-        <v>30.12208538971075</v>
+        <v>27.76764760900006</v>
       </c>
       <c r="T275" t="n">
-        <v>30.12208538971075</v>
+        <v>27.76764760900006</v>
       </c>
     </row>
     <row r="276">
@@ -20586,10 +20586,10 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>29.5167166125634</v>
+        <v>27.14409866686356</v>
       </c>
       <c r="T276" t="n">
-        <v>29.5167166125634</v>
+        <v>27.14409866686356</v>
       </c>
     </row>
     <row r="277">
@@ -20659,13 +20659,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S277" t="n">
-        <v>59.04229671584907</v>
+        <v>66.49767614246426</v>
       </c>
       <c r="T277" t="n">
-        <v>59.04229671584907</v>
+        <v>66.49767614246426</v>
       </c>
     </row>
     <row r="278">
@@ -20733,13 +20733,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S278" t="n">
-        <v>55.9557385240998</v>
+        <v>63.31842381237663</v>
       </c>
       <c r="T278" t="n">
-        <v>55.9557385240998</v>
+        <v>63.31842381237663</v>
       </c>
     </row>
     <row r="279">
@@ -20807,13 +20807,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S279" t="n">
-        <v>31.26327299010561</v>
+        <v>37.8844051716756</v>
       </c>
       <c r="T279" t="n">
-        <v>31.26327299010561</v>
+        <v>37.8844051716756</v>
       </c>
     </row>
     <row r="280">
@@ -20881,13 +20881,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S280" t="n">
-        <v>30.74884662481406</v>
+        <v>37.35452978332766</v>
       </c>
       <c r="T280" t="n">
-        <v>30.74884662481406</v>
+        <v>37.35452978332766</v>
       </c>
     </row>
     <row r="281">
@@ -20955,13 +20955,13 @@
         <v>-4.745900000000006</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S281" t="n">
-        <v>20.46031931898314</v>
+        <v>26.7570220163689</v>
       </c>
       <c r="T281" t="n">
-        <v>20.46031931898314</v>
+        <v>26.7570220163689</v>
       </c>
     </row>
     <row r="282">
@@ -21031,13 +21031,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S282" t="n">
-        <v>52.24241572669569</v>
+        <v>58.83773906243938</v>
       </c>
       <c r="T282" t="n">
-        <v>52.24241572669569</v>
+        <v>58.83773906243938</v>
       </c>
     </row>
     <row r="283">
@@ -21105,13 +21105,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S283" t="n">
-        <v>42.13451994124446</v>
+        <v>48.4262874610794</v>
       </c>
       <c r="T283" t="n">
-        <v>42.13451994124446</v>
+        <v>48.4262874610794</v>
       </c>
     </row>
     <row r="284">
@@ -21179,13 +21179,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S284" t="n">
-        <v>41.90126080773404</v>
+        <v>48.1860231933557</v>
       </c>
       <c r="T284" t="n">
-        <v>41.90126080773404</v>
+        <v>48.1860231933557</v>
       </c>
     </row>
     <row r="285">
@@ -21253,13 +21253,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S285" t="n">
-        <v>41.66800167422363</v>
+        <v>47.94575892563201</v>
       </c>
       <c r="T285" t="n">
-        <v>41.66800167422363</v>
+        <v>47.94575892563201</v>
       </c>
     </row>
     <row r="286">
@@ -21327,13 +21327,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S286" t="n">
-        <v>41.59024862972016</v>
+        <v>47.86567083639078</v>
       </c>
       <c r="T286" t="n">
-        <v>41.59024862972016</v>
+        <v>47.86567083639078</v>
       </c>
     </row>
     <row r="287">
@@ -21401,13 +21401,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S287" t="n">
-        <v>41.20148340720281</v>
+        <v>47.46523039018463</v>
       </c>
       <c r="T287" t="n">
-        <v>41.20148340720281</v>
+        <v>47.46523039018463</v>
       </c>
     </row>
     <row r="288">
@@ -21475,13 +21475,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S288" t="n">
-        <v>40.03518773965074</v>
+        <v>46.26390905156617</v>
       </c>
       <c r="T288" t="n">
-        <v>40.03518773965074</v>
+        <v>46.26390905156617</v>
       </c>
     </row>
     <row r="289">
@@ -21549,13 +21549,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S289" t="n">
-        <v>39.25765729461603</v>
+        <v>45.46302815915386</v>
       </c>
       <c r="T289" t="n">
-        <v>39.25765729461603</v>
+        <v>45.46302815915386</v>
       </c>
     </row>
     <row r="290">
@@ -21623,13 +21623,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S290" t="n">
-        <v>38.86889207209867</v>
+        <v>45.06258771294771</v>
       </c>
       <c r="T290" t="n">
-        <v>38.86889207209867</v>
+        <v>45.06258771294771</v>
       </c>
     </row>
     <row r="291">
@@ -21697,13 +21697,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S291" t="n">
-        <v>38.71338598309173</v>
+        <v>44.90241153446525</v>
       </c>
       <c r="T291" t="n">
-        <v>38.71338598309173</v>
+        <v>44.90241153446525</v>
       </c>
     </row>
     <row r="292">
@@ -21771,13 +21771,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S292" t="n">
-        <v>38.63563293858826</v>
+        <v>44.82232344522401</v>
       </c>
       <c r="T292" t="n">
-        <v>38.63563293858826</v>
+        <v>44.82232344522401</v>
       </c>
     </row>
     <row r="293">
@@ -21845,13 +21845,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S293" t="n">
-        <v>35.52551115844942</v>
+        <v>41.61879987557479</v>
       </c>
       <c r="T293" t="n">
-        <v>35.52551115844942</v>
+        <v>41.61879987557479</v>
       </c>
     </row>
     <row r="294">
@@ -21919,13 +21919,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S294" t="n">
-        <v>29.30526759817174</v>
+        <v>35.21175273627635</v>
       </c>
       <c r="T294" t="n">
-        <v>29.30526759817174</v>
+        <v>35.21175273627635</v>
       </c>
     </row>
     <row r="295">
@@ -21995,13 +21995,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S295" t="n">
-        <v>43.48172003081821</v>
+        <v>49.81394606259898</v>
       </c>
       <c r="T295" t="n">
-        <v>43.48172003081821</v>
+        <v>49.81394606259898</v>
       </c>
     </row>
     <row r="296">
@@ -22069,13 +22069,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S296" t="n">
-        <v>41.55900861333959</v>
+        <v>47.83349263377811</v>
       </c>
       <c r="T296" t="n">
-        <v>41.55900861333959</v>
+        <v>47.83349263377811</v>
       </c>
     </row>
     <row r="297">
@@ -22143,13 +22143,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S297" t="n">
-        <v>40.40538176285243</v>
+        <v>46.64522057648561</v>
       </c>
       <c r="T297" t="n">
-        <v>40.40538176285243</v>
+        <v>46.64522057648561</v>
       </c>
     </row>
     <row r="298">
@@ -22217,13 +22217,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S298" t="n">
-        <v>40.32847330615328</v>
+        <v>46.56600243933277</v>
       </c>
       <c r="T298" t="n">
-        <v>40.32847330615328</v>
+        <v>46.56600243933277</v>
       </c>
     </row>
     <row r="299">
@@ -22291,13 +22291,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R299" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S299" t="n">
-        <v>36.48305047119606</v>
+        <v>42.60509558169105</v>
       </c>
       <c r="T299" t="n">
-        <v>36.48305047119606</v>
+        <v>42.60509558169105</v>
       </c>
     </row>
     <row r="300">
@@ -22365,13 +22365,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S300" t="n">
-        <v>33.791254486726</v>
+        <v>39.83246078134184</v>
       </c>
       <c r="T300" t="n">
-        <v>33.791254486726</v>
+        <v>39.83246078134184</v>
       </c>
     </row>
     <row r="301">
@@ -22439,13 +22439,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R301" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S301" t="n">
-        <v>33.63743757332772</v>
+        <v>39.67402450703618</v>
       </c>
       <c r="T301" t="n">
-        <v>33.63743757332772</v>
+        <v>39.67402450703618</v>
       </c>
     </row>
     <row r="302">
@@ -22513,13 +22513,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R302" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S302" t="n">
-        <v>31.33018387235338</v>
+        <v>37.29748039245115</v>
       </c>
       <c r="T302" t="n">
-        <v>31.33018387235338</v>
+        <v>37.29748039245115</v>
       </c>
     </row>
     <row r="303">
@@ -22587,13 +22587,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S303" t="n">
-        <v>30.17655702186621</v>
+        <v>36.10920833515863</v>
       </c>
       <c r="T303" t="n">
-        <v>30.17655702186621</v>
+        <v>36.10920833515863</v>
       </c>
     </row>
     <row r="304">
@@ -22661,13 +22661,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S304" t="n">
-        <v>30.09964856516707</v>
+        <v>36.02999019800579</v>
       </c>
       <c r="T304" t="n">
-        <v>30.09964856516707</v>
+        <v>36.02999019800579</v>
       </c>
     </row>
     <row r="305">
@@ -22735,13 +22735,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R305" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S305" t="n">
-        <v>29.71510628167135</v>
+        <v>35.63389951224163</v>
       </c>
       <c r="T305" t="n">
-        <v>29.71510628167135</v>
+        <v>35.63389951224163</v>
       </c>
     </row>
     <row r="306">
@@ -22809,13 +22809,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S306" t="n">
-        <v>18.94792234379112</v>
+        <v>24.54336031084481</v>
       </c>
       <c r="T306" t="n">
-        <v>18.94792234379112</v>
+        <v>24.54336031084481</v>
       </c>
     </row>
     <row r="307">
@@ -22883,13 +22883,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R307" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S307" t="n">
-        <v>17.0252109263125</v>
+        <v>22.56290688202395</v>
       </c>
       <c r="T307" t="n">
-        <v>17.0252109263125</v>
+        <v>22.56290688202395</v>
       </c>
     </row>
     <row r="308">
@@ -22957,13 +22957,13 @@
         <v>1.867959999999982</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>12.04644873936213</v>
       </c>
       <c r="S308" t="n">
-        <v>13.17978809135528</v>
+        <v>18.60200002438222</v>
       </c>
       <c r="T308" t="n">
-        <v>13.17978809135528</v>
+        <v>18.60200002438222</v>
       </c>
     </row>
     <row r="309">
@@ -23036,10 +23036,10 @@
         <v>0</v>
       </c>
       <c r="S309" t="n">
-        <v>77.77487693055934</v>
+        <v>76.85152652189421</v>
       </c>
       <c r="T309" t="n">
-        <v>77.77487693055934</v>
+        <v>76.85152652189421</v>
       </c>
     </row>
     <row r="310">
@@ -23110,10 +23110,10 @@
         <v>0</v>
       </c>
       <c r="S310" t="n">
-        <v>72.13239745504723</v>
+        <v>71.03959462054658</v>
       </c>
       <c r="T310" t="n">
-        <v>72.13239745504723</v>
+        <v>71.03959462054658</v>
       </c>
     </row>
     <row r="311">
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="S311" t="n">
-        <v>69.92423151900158</v>
+        <v>68.76511403043187</v>
       </c>
       <c r="T311" t="n">
-        <v>69.92423151900158</v>
+        <v>68.76511403043187</v>
       </c>
     </row>
     <row r="312">
@@ -23258,10 +23258,10 @@
         <v>0</v>
       </c>
       <c r="S312" t="n">
-        <v>69.59811457466904</v>
+        <v>68.42920328754622</v>
       </c>
       <c r="T312" t="n">
-        <v>69.59811457466904</v>
+        <v>68.42920328754622</v>
       </c>
     </row>
     <row r="313">
@@ -23332,10 +23332,10 @@
         <v>0</v>
       </c>
       <c r="S313" t="n">
-        <v>62.40153680158996</v>
+        <v>61.01650110202493</v>
       </c>
       <c r="T313" t="n">
-        <v>62.40153680158996</v>
+        <v>61.01650110202493</v>
       </c>
     </row>
     <row r="314">
@@ -23406,10 +23406,10 @@
         <v>0</v>
       </c>
       <c r="S314" t="n">
-        <v>62.48352447512649</v>
+        <v>61.10095099278877</v>
       </c>
       <c r="T314" t="n">
-        <v>62.48352447512649</v>
+        <v>61.10095099278877</v>
       </c>
     </row>
     <row r="315">
@@ -23480,10 +23480,10 @@
         <v>0</v>
       </c>
       <c r="S315" t="n">
-        <v>63.38355513421478</v>
+        <v>62.02801097102137</v>
       </c>
       <c r="T315" t="n">
-        <v>63.38355513421478</v>
+        <v>62.02801097102137</v>
       </c>
     </row>
     <row r="316">
@@ -23554,10 +23554,10 @@
         <v>0</v>
       </c>
       <c r="S316" t="n">
-        <v>61.01233072600287</v>
+        <v>59.58557500946385</v>
       </c>
       <c r="T316" t="n">
-        <v>61.01233072600287</v>
+        <v>59.58557500946385</v>
       </c>
     </row>
     <row r="317">
@@ -23628,10 +23628,10 @@
         <v>0</v>
       </c>
       <c r="S317" t="n">
-        <v>61.50333989231527</v>
+        <v>60.09132994396207</v>
       </c>
       <c r="T317" t="n">
-        <v>61.50333989231527</v>
+        <v>60.09132994396207</v>
       </c>
     </row>
     <row r="318">
@@ -23702,10 +23702,10 @@
         <v>0</v>
       </c>
       <c r="S318" t="n">
-        <v>56.10590656250595</v>
+        <v>54.53180330482109</v>
       </c>
       <c r="T318" t="n">
-        <v>56.10590656250595</v>
+        <v>54.53180330482109</v>
       </c>
     </row>
     <row r="319">
@@ -23776,10 +23776,10 @@
         <v>0</v>
       </c>
       <c r="S319" t="n">
-        <v>54.14370364706991</v>
+        <v>52.51067238699794</v>
       </c>
       <c r="T319" t="n">
-        <v>54.14370364706991</v>
+        <v>52.51067238699794</v>
       </c>
     </row>
     <row r="320">
@@ -23850,10 +23850,10 @@
         <v>0</v>
       </c>
       <c r="S320" t="n">
-        <v>60.63738792751113</v>
+        <v>59.19937209615384</v>
       </c>
       <c r="T320" t="n">
-        <v>60.63738792751113</v>
+        <v>59.19937209615384</v>
       </c>
     </row>
     <row r="321">
@@ -23924,10 +23924,10 @@
         <v>0</v>
       </c>
       <c r="S321" t="n">
-        <v>54.55272513984579</v>
+        <v>52.93197743073232</v>
       </c>
       <c r="T321" t="n">
-        <v>54.55272513984579</v>
+        <v>52.93197743073232</v>
       </c>
     </row>
     <row r="322">
@@ -23998,10 +23998,10 @@
         <v>0</v>
       </c>
       <c r="S322" t="n">
-        <v>54.22660819551325</v>
+        <v>52.59606668784667</v>
       </c>
       <c r="T322" t="n">
-        <v>54.22660819551325</v>
+        <v>52.59606668784667</v>
       </c>
     </row>
     <row r="323">
@@ -24072,10 +24072,10 @@
         <v>0</v>
       </c>
       <c r="S323" t="n">
-        <v>58.88890308821417</v>
+        <v>57.39837754036764</v>
       </c>
       <c r="T323" t="n">
-        <v>58.88890308821417</v>
+        <v>57.39837754036764</v>
       </c>
     </row>
     <row r="324">
@@ -24215,13 +24215,13 @@
         <v>-0.3366600000000091</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S325" t="n">
-        <v>48.02713322646</v>
+        <v>55.15171017832049</v>
       </c>
       <c r="T325" t="n">
-        <v>48.02713322646</v>
+        <v>55.15171017832049</v>
       </c>
     </row>
     <row r="326">
@@ -24289,13 +24289,13 @@
         <v>-0.3366600000000091</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S326" t="n">
-        <v>47.84805215114729</v>
+        <v>54.9672510200631</v>
       </c>
       <c r="T326" t="n">
-        <v>47.84805215114729</v>
+        <v>54.9672510200631</v>
       </c>
     </row>
     <row r="327">
@@ -24363,13 +24363,13 @@
         <v>-3.643590000000017</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S327" t="n">
-        <v>45.46080513978893</v>
+        <v>52.508311271691</v>
       </c>
       <c r="T327" t="n">
-        <v>45.46080513978893</v>
+        <v>52.508311271691</v>
       </c>
     </row>
     <row r="328">
@@ -24437,13 +24437,13 @@
         <v>-3.643590000000017</v>
       </c>
       <c r="R328" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S328" t="n">
-        <v>45.19218352681987</v>
+        <v>52.23162253430491</v>
       </c>
       <c r="T328" t="n">
-        <v>45.19218352681987</v>
+        <v>52.23162253430491</v>
       </c>
     </row>
     <row r="329">
@@ -24511,13 +24511,13 @@
         <v>-0.3366600000000091</v>
       </c>
       <c r="R329" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S329" t="n">
-        <v>47.13172784989645</v>
+        <v>54.22941438703353</v>
       </c>
       <c r="T329" t="n">
-        <v>47.13172784989645</v>
+        <v>54.22941438703353</v>
       </c>
     </row>
     <row r="330">
@@ -24585,13 +24585,13 @@
         <v>-0.3366600000000091</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S330" t="n">
-        <v>46.68402516161468</v>
+        <v>53.76826649139005</v>
       </c>
       <c r="T330" t="n">
-        <v>46.68402516161468</v>
+        <v>53.76826649139005</v>
       </c>
     </row>
     <row r="331">
@@ -24659,13 +24659,13 @@
         <v>-3.643590000000017</v>
       </c>
       <c r="R331" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S331" t="n">
-        <v>39.10342696618775</v>
+        <v>45.96001115355359</v>
       </c>
       <c r="T331" t="n">
-        <v>39.10342696618775</v>
+        <v>45.96001115355359</v>
       </c>
     </row>
     <row r="332">
@@ -24733,13 +24733,13 @@
         <v>-3.643590000000017</v>
       </c>
       <c r="R332" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S332" t="n">
-        <v>36.41721083649712</v>
+        <v>43.19312377969272</v>
       </c>
       <c r="T332" t="n">
-        <v>36.41721083649712</v>
+        <v>43.19312377969272</v>
       </c>
     </row>
     <row r="333">
@@ -24807,7 +24807,7 @@
         <v>-0.3366600000000091</v>
       </c>
       <c r="R333" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S333" t="inlineStr"/>
       <c r="T333" t="inlineStr"/>
@@ -24882,10 +24882,10 @@
         <v>0</v>
       </c>
       <c r="S334" t="n">
-        <v>69.91391360400101</v>
+        <v>68.75448625241202</v>
       </c>
       <c r="T334" t="n">
-        <v>69.91391360400101</v>
+        <v>68.75448625241202</v>
       </c>
     </row>
     <row r="335">
@@ -24956,10 +24956,10 @@
         <v>0</v>
       </c>
       <c r="S335" t="n">
-        <v>69.11373296381183</v>
+        <v>67.93027494429131</v>
       </c>
       <c r="T335" t="n">
-        <v>69.11373296381183</v>
+        <v>67.93027494429131</v>
       </c>
     </row>
     <row r="336">
@@ -25030,10 +25030,10 @@
         <v>0</v>
       </c>
       <c r="S336" t="n">
-        <v>67.91346200352808</v>
+        <v>66.69395798211019</v>
       </c>
       <c r="T336" t="n">
-        <v>67.91346200352808</v>
+        <v>66.69395798211019</v>
       </c>
     </row>
     <row r="337">
@@ -25104,10 +25104,10 @@
         <v>0</v>
       </c>
       <c r="S337" t="n">
-        <v>67.75342587549025</v>
+        <v>66.52911572048606</v>
       </c>
       <c r="T337" t="n">
-        <v>67.75342587549025</v>
+        <v>66.52911572048606</v>
       </c>
     </row>
     <row r="338">
@@ -25178,10 +25178,10 @@
         <v>0</v>
       </c>
       <c r="S338" t="n">
-        <v>67.35333555539566</v>
+        <v>66.11701006642568</v>
       </c>
       <c r="T338" t="n">
-        <v>67.35333555539566</v>
+        <v>66.11701006642568</v>
       </c>
     </row>
     <row r="339">
@@ -25252,10 +25252,10 @@
         <v>0</v>
       </c>
       <c r="S339" t="n">
-        <v>65.75297427501732</v>
+        <v>64.46858745018423</v>
       </c>
       <c r="T339" t="n">
-        <v>65.75297427501732</v>
+        <v>64.46858745018423</v>
       </c>
     </row>
     <row r="340">
@@ -25326,10 +25326,10 @@
         <v>0</v>
       </c>
       <c r="S340" t="n">
-        <v>60.9518904338823</v>
+        <v>59.52331960145984</v>
       </c>
       <c r="T340" t="n">
-        <v>60.9518904338823</v>
+        <v>59.52331960145984</v>
       </c>
     </row>
     <row r="341">
@@ -25400,10 +25400,10 @@
         <v>0</v>
       </c>
       <c r="S341" t="n">
-        <v>54.7428212968908</v>
+        <v>53.12778247074147</v>
       </c>
       <c r="T341" t="n">
-        <v>54.7428212968908</v>
+        <v>53.12778247074147</v>
       </c>
     </row>
     <row r="342">
@@ -25474,10 +25474,10 @@
         <v>0</v>
       </c>
       <c r="S342" t="n">
-        <v>51.34972275161226</v>
+        <v>49.63278390401106</v>
       </c>
       <c r="T342" t="n">
-        <v>51.34972275161226</v>
+        <v>49.63278390401106</v>
       </c>
     </row>
     <row r="343">
@@ -25548,10 +25548,10 @@
         <v>0</v>
       </c>
       <c r="S343" t="n">
-        <v>50.3736132475403</v>
+        <v>48.62736031486994</v>
       </c>
       <c r="T343" t="n">
-        <v>50.3736132475403</v>
+        <v>48.62736031486994</v>
       </c>
     </row>
     <row r="344">
@@ -25624,10 +25624,10 @@
         <v>0</v>
       </c>
       <c r="S344" t="n">
-        <v>70.56091784655945</v>
+        <v>69.42092103767837</v>
       </c>
       <c r="T344" t="n">
-        <v>70.56091784655945</v>
+        <v>69.42092103767837</v>
       </c>
     </row>
     <row r="345">
@@ -25698,10 +25698,10 @@
         <v>0</v>
       </c>
       <c r="S345" t="n">
-        <v>73.45573829576384</v>
+        <v>72.40267744289375</v>
       </c>
       <c r="T345" t="n">
-        <v>73.45573829576384</v>
+        <v>72.40267744289375</v>
       </c>
     </row>
     <row r="346">
@@ -25772,10 +25772,10 @@
         <v>0</v>
       </c>
       <c r="S346" t="n">
-        <v>67.9526125501819</v>
+        <v>66.73428428051145</v>
       </c>
       <c r="T346" t="n">
-        <v>67.9526125501819</v>
+        <v>66.73428428051145</v>
       </c>
     </row>
     <row r="347">
@@ -25846,10 +25846,10 @@
         <v>0</v>
       </c>
       <c r="S347" t="n">
-        <v>69.07398461273689</v>
+        <v>67.88933288847329</v>
       </c>
       <c r="T347" t="n">
-        <v>69.07398461273689</v>
+        <v>67.88933288847329</v>
       </c>
     </row>
     <row r="348">
@@ -25920,10 +25920,10 @@
         <v>0</v>
       </c>
       <c r="S348" t="n">
-        <v>64.69223092970995</v>
+        <v>63.37598833405283</v>
       </c>
       <c r="T348" t="n">
-        <v>64.69223092970995</v>
+        <v>63.37598833405283</v>
       </c>
     </row>
     <row r="349">
@@ -25994,10 +25994,10 @@
         <v>0</v>
       </c>
       <c r="S349" t="n">
-        <v>64.42547135615536</v>
+        <v>63.10121755601802</v>
       </c>
       <c r="T349" t="n">
-        <v>64.42547135615536</v>
+        <v>63.10121755601802</v>
       </c>
     </row>
     <row r="350">
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="S350" t="n">
-        <v>61.38244851038155</v>
+        <v>59.96680800598997</v>
       </c>
       <c r="T350" t="n">
-        <v>61.38244851038155</v>
+        <v>59.96680800598997</v>
       </c>
     </row>
     <row r="351">
@@ -26142,10 +26142,10 @@
         <v>0</v>
       </c>
       <c r="S351" t="n">
-        <v>58.30484747554338</v>
+        <v>56.79678183015296</v>
       </c>
       <c r="T351" t="n">
-        <v>58.30484747554338</v>
+        <v>56.79678183015296</v>
       </c>
     </row>
     <row r="352">
@@ -26216,10 +26216,10 @@
         <v>0</v>
       </c>
       <c r="S352" t="n">
-        <v>56.16583791762645</v>
+        <v>54.59353449165615</v>
       </c>
       <c r="T352" t="n">
-        <v>56.16583791762645</v>
+        <v>54.59353449165615</v>
       </c>
     </row>
     <row r="353">
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="S353" t="n">
-        <v>60.33865245590198</v>
+        <v>58.89166513416232</v>
       </c>
       <c r="T353" t="n">
-        <v>60.33865245590198</v>
+        <v>58.89166513416232</v>
       </c>
     </row>
     <row r="354">
@@ -26366,10 +26366,10 @@
         <v>0</v>
       </c>
       <c r="S354" t="n">
-        <v>65.2987149093033</v>
+        <v>64.00068596989755</v>
       </c>
       <c r="T354" t="n">
-        <v>65.2987149093033</v>
+        <v>64.00068596989755</v>
       </c>
     </row>
     <row r="355">
@@ -26440,10 +26440,10 @@
         <v>0</v>
       </c>
       <c r="S355" t="n">
-        <v>61.35724741886809</v>
+        <v>59.94085008654134</v>
       </c>
       <c r="T355" t="n">
-        <v>61.35724741886809</v>
+        <v>59.94085008654134</v>
       </c>
     </row>
     <row r="356">
@@ -26514,10 +26514,10 @@
         <v>0</v>
       </c>
       <c r="S356" t="n">
-        <v>61.96508624374651</v>
+        <v>60.56694325578018</v>
       </c>
       <c r="T356" t="n">
-        <v>61.96508624374651</v>
+        <v>60.56694325578018</v>
       </c>
     </row>
     <row r="357">
@@ -26588,10 +26588,10 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>58.56972831266407</v>
+        <v>57.06961745037959</v>
       </c>
       <c r="T357" t="n">
-        <v>58.56972831266407</v>
+        <v>57.06961745037959</v>
       </c>
     </row>
     <row r="358">
@@ -26662,10 +26662,10 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>55.30496584676121</v>
+        <v>53.70680909489487</v>
       </c>
       <c r="T358" t="n">
-        <v>55.30496584676121</v>
+        <v>53.70680909489487</v>
       </c>
     </row>
     <row r="359">
@@ -26736,10 +26736,10 @@
         <v>0</v>
       </c>
       <c r="S359" t="n">
-        <v>57.3825363176273</v>
+        <v>55.84677223509371</v>
       </c>
       <c r="T359" t="n">
-        <v>57.3825363176273</v>
+        <v>55.84677223509371</v>
       </c>
     </row>
     <row r="360">
@@ -26810,10 +26810,10 @@
         <v>0</v>
       </c>
       <c r="S360" t="n">
-        <v>61.47832697187659</v>
+        <v>60.06556584665797</v>
       </c>
       <c r="T360" t="n">
-        <v>61.47832697187659</v>
+        <v>60.06556584665797</v>
       </c>
     </row>
     <row r="361">
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>48.79916861359001</v>
+        <v>47.00563266221759</v>
       </c>
       <c r="T361" t="n">
-        <v>48.79916861359001</v>
+        <v>47.00563266221759</v>
       </c>
     </row>
     <row r="362">
@@ -26958,10 +26958,10 @@
         <v>0</v>
       </c>
       <c r="S362" t="n">
-        <v>54.52139305568383</v>
+        <v>52.89970439539973</v>
       </c>
       <c r="T362" t="n">
-        <v>54.52139305568383</v>
+        <v>52.89970439539973</v>
       </c>
     </row>
     <row r="363">
@@ -27032,10 +27032,10 @@
         <v>0</v>
       </c>
       <c r="S363" t="n">
-        <v>44.59651019279568</v>
+        <v>42.67676187902967</v>
       </c>
       <c r="T363" t="n">
-        <v>44.59651019279568</v>
+        <v>42.67676187902967</v>
       </c>
     </row>
     <row r="364">
@@ -27106,10 +27106,10 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>40.93996133135411</v>
+        <v>38.91040117379737</v>
       </c>
       <c r="T364" t="n">
-        <v>40.93996133135411</v>
+        <v>38.91040117379737</v>
       </c>
     </row>
     <row r="365">
@@ -27252,10 +27252,10 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>63.41272973293118</v>
+        <v>62.05806172826819</v>
       </c>
       <c r="T366" t="n">
-        <v>63.41272973293118</v>
+        <v>62.05806172826819</v>
       </c>
     </row>
     <row r="367">
@@ -27326,10 +27326,10 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>61.97709414952537</v>
+        <v>60.57931177762726</v>
       </c>
       <c r="T367" t="n">
-        <v>61.97709414952537</v>
+        <v>60.57931177762726</v>
       </c>
     </row>
     <row r="368">
@@ -27400,10 +27400,10 @@
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>63.91379872364339</v>
+        <v>62.57417859932374</v>
       </c>
       <c r="T368" t="n">
-        <v>63.91379872364339</v>
+        <v>62.57417859932374</v>
       </c>
     </row>
     <row r="369">
@@ -27474,10 +27474,10 @@
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>60.3483259779596</v>
+        <v>58.90162916711789</v>
       </c>
       <c r="T369" t="n">
-        <v>60.3483259779596</v>
+        <v>58.90162916711789</v>
       </c>
     </row>
     <row r="370">
@@ -27548,10 +27548,10 @@
         <v>0</v>
       </c>
       <c r="S370" t="n">
-        <v>60.23974143318856</v>
+        <v>58.7897836597506</v>
       </c>
       <c r="T370" t="n">
-        <v>60.23974143318856</v>
+        <v>58.7897836597506</v>
       </c>
     </row>
     <row r="371">
@@ -27622,10 +27622,10 @@
         <v>0</v>
       </c>
       <c r="S371" t="n">
-        <v>54.03798384199615</v>
+        <v>52.40177765191223</v>
       </c>
       <c r="T371" t="n">
-        <v>54.03798384199615</v>
+        <v>52.40177765191223</v>
       </c>
     </row>
     <row r="372">
@@ -27696,10 +27696,10 @@
         <v>0</v>
       </c>
       <c r="S372" t="n">
-        <v>55.08197555656363</v>
+        <v>53.47712205980423</v>
       </c>
       <c r="T372" t="n">
-        <v>55.08197555656363</v>
+        <v>53.47712205980423</v>
       </c>
     </row>
     <row r="373">
@@ -27770,10 +27770,10 @@
         <v>0</v>
       </c>
       <c r="S373" t="n">
-        <v>53.33840357060556</v>
+        <v>51.68118789797619</v>
       </c>
       <c r="T373" t="n">
-        <v>53.33840357060556</v>
+        <v>51.68118789797619</v>
       </c>
     </row>
     <row r="374">
@@ -27844,10 +27844,10 @@
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>46.82333088434249</v>
+        <v>44.97045745593867</v>
       </c>
       <c r="T374" t="n">
-        <v>46.82333088434249</v>
+        <v>44.97045745593867</v>
       </c>
     </row>
     <row r="375">
@@ -27918,10 +27918,10 @@
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>43.40913699367562</v>
+        <v>41.45373001782033</v>
       </c>
       <c r="T375" t="n">
-        <v>43.40913699367562</v>
+        <v>41.45373001782033</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/france_ratings_2026-03-29.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-29.xlsx
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
@@ -644,7 +644,7 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
@@ -712,7 +712,7 @@
         <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
@@ -780,7 +780,7 @@
         <v>6.25</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
@@ -848,7 +848,7 @@
         <v>18.25</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
@@ -916,7 +916,7 @@
         <v>48.25</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P8" t="n">
-        <v>118.8433657739949</v>
+        <v>143.462102799157</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.541280000000015</v>
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>75.71695608961932</v>
+        <v>109.5464650313647</v>
       </c>
       <c r="T8" t="n">
-        <v>75.71695608961932</v>
+        <v>109.5464650313647</v>
       </c>
     </row>
     <row r="9">
@@ -1060,10 +1060,10 @@
         <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P9" t="n">
-        <v>111.3238415945992</v>
+        <v>135.9688266113169</v>
       </c>
       <c r="Q9" t="n">
         <v>0.7656499999999937</v>
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>72.81956676022145</v>
+        <v>106.6607398606276</v>
       </c>
       <c r="T9" t="n">
-        <v>72.81956676022145</v>
+        <v>106.6607398606276</v>
       </c>
     </row>
     <row r="10">
@@ -1134,10 +1134,10 @@
         <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P10" t="n">
-        <v>102.1333120420045</v>
+        <v>126.8103779372902</v>
       </c>
       <c r="Q10" t="n">
         <v>-6.950520000000012</v>
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>61.19127103721623</v>
+        <v>95.02875586568868</v>
       </c>
       <c r="T10" t="n">
-        <v>61.19127103721623</v>
+        <v>95.02875586568868</v>
       </c>
     </row>
     <row r="11">
@@ -1208,10 +1208,10 @@
         <v>10.75</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P11" t="n">
-        <v>100.8800580121052</v>
+        <v>125.5614985726502</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.541280000000015</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>63.36193350411707</v>
+        <v>97.20725038689082</v>
       </c>
       <c r="T11" t="n">
-        <v>63.36193350411707</v>
+        <v>97.20725038689082</v>
       </c>
     </row>
     <row r="12">
@@ -1282,10 +1282,10 @@
         <v>11.5</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P12" t="n">
-        <v>99.6268039822059</v>
+        <v>124.3126192080102</v>
       </c>
       <c r="Q12" t="n">
         <v>0.7656499999999937</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>64.77443577431302</v>
+        <v>98.6259024177144</v>
       </c>
       <c r="T12" t="n">
-        <v>64.77443577431302</v>
+        <v>98.6259024177144</v>
       </c>
     </row>
     <row r="13">
@@ -1356,10 +1356,10 @@
         <v>16</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P13" t="n">
-        <v>92.10727980281021</v>
+        <v>116.8193430201701</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.438970000000012</v>
@@ -1368,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>58.08624546139065</v>
+        <v>91.94096479508448</v>
       </c>
       <c r="T13" t="n">
-        <v>58.08624546139065</v>
+        <v>91.94096479508448</v>
       </c>
     </row>
     <row r="14">
@@ -1430,10 +1430,10 @@
         <v>16.25</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P14" t="n">
-        <v>91.68952845951044</v>
+        <v>116.4030498986235</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1442,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>57.04075915804615</v>
+        <v>90.89416382460186</v>
       </c>
       <c r="T14" t="n">
-        <v>57.04075915804615</v>
+        <v>90.89416382460186</v>
       </c>
     </row>
     <row r="15">
@@ -1504,10 +1504,10 @@
         <v>25.75</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P15" t="n">
-        <v>80.60999926907621</v>
+        <v>105.3727267103315</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1574,10 +1574,10 @@
         <v>31.25</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P16" t="n">
-        <v>76.01473449277884</v>
+        <v>100.7935023733181</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.541280000000015</v>
@@ -1644,10 +1644,10 @@
         <v>50.25</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P17" t="n">
-        <v>60.14018344738791</v>
+        <v>84.97436375454468</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.541280000000015</v>
@@ -1714,10 +1714,10 @@
         <v>57.75</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P18" t="n">
-        <v>53.87391329789149</v>
+        <v>78.72996693134462</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.541280000000015</v>
@@ -1784,10 +1784,10 @@
         <v>58.25</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.001364237532808402</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P19" t="n">
-        <v>53.45616195459174</v>
+        <v>78.31367380979796</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.541280000000015</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
@@ -1924,7 +1924,7 @@
         <v>0.25</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
@@ -1992,7 +1992,7 @@
         <v>1.5</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
@@ -2060,7 +2060,7 @@
         <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
@@ -2128,7 +2128,7 @@
         <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
@@ -2196,7 +2196,7 @@
         <v>2.75</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
@@ -2264,7 +2264,7 @@
         <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
@@ -2332,7 +2332,7 @@
         <v>5.25</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
@@ -2400,7 +2400,7 @@
         <v>10.75</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
@@ -2468,7 +2468,7 @@
         <v>17.75</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
@@ -2536,7 +2536,7 @@
         <v>19.5</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
@@ -2604,7 +2604,7 @@
         <v>21.25</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
@@ -2672,7 +2672,7 @@
         <v>22.75</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.0004621044301280541</v>
+        <v>0.0002168743338563402</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P33" t="n">
-        <v>101.1544686741075</v>
+        <v>101.9681008531559</v>
       </c>
       <c r="Q33" t="n">
         <v>-1.438970000000012</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>64.30883120794934</v>
+        <v>81.70373131865838</v>
       </c>
       <c r="T33" t="n">
-        <v>64.30883120794934</v>
+        <v>81.70373131865838</v>
       </c>
     </row>
     <row r="34">
@@ -2816,10 +2816,10 @@
         <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P34" t="n">
-        <v>94.8397556643297</v>
+        <v>95.66914381261788</v>
       </c>
       <c r="Q34" t="n">
         <v>1.867959999999982</v>
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>62.24010157804597</v>
+        <v>79.64127223023277</v>
       </c>
       <c r="T34" t="n">
-        <v>62.24010157804597</v>
+        <v>79.64127223023277</v>
       </c>
     </row>
     <row r="35">
@@ -2890,10 +2890,10 @@
         <v>4.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P35" t="n">
-        <v>89.78798525650748</v>
+        <v>90.62997818018744</v>
       </c>
       <c r="Q35" t="n">
         <v>1.867959999999982</v>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>58.76553340203153</v>
+        <v>76.16768298258373</v>
       </c>
       <c r="T35" t="n">
-        <v>58.76553340203153</v>
+        <v>76.16768298258373</v>
       </c>
     </row>
     <row r="36">
@@ -2964,10 +2964,10 @@
         <v>8.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P36" t="n">
-        <v>79.68444444086305</v>
+        <v>80.55164691532656</v>
       </c>
       <c r="Q36" t="n">
         <v>-1.438970000000012</v>
@@ -2976,10 +2976,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>49.54191645988792</v>
+        <v>66.94097701614993</v>
       </c>
       <c r="T36" t="n">
-        <v>49.54191645988792</v>
+        <v>66.94097701614993</v>
       </c>
     </row>
     <row r="37">
@@ -3038,10 +3038,10 @@
         <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P37" t="n">
-        <v>73.36973143108528</v>
+        <v>74.2526898747885</v>
       </c>
       <c r="Q37" t="n">
         <v>1.867959999999982</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>47.47318682998456</v>
+        <v>64.87851792772432</v>
       </c>
       <c r="T37" t="n">
-        <v>47.47318682998456</v>
+        <v>64.87851792772432</v>
       </c>
     </row>
     <row r="38">
@@ -3112,10 +3112,10 @@
         <v>11.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P38" t="n">
-        <v>72.73826013010751</v>
+        <v>73.62279417073469</v>
       </c>
       <c r="Q38" t="n">
         <v>-1.438970000000012</v>
@@ -3124,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>44.76438521786806</v>
+        <v>62.16479180063248</v>
       </c>
       <c r="T38" t="n">
-        <v>44.76438521786806</v>
+        <v>62.16479180063248</v>
       </c>
     </row>
     <row r="39">
@@ -3186,10 +3186,10 @@
         <v>41.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0009817048792196417</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P39" t="n">
-        <v>23.80915299964589</v>
+        <v>24.82052264812083</v>
       </c>
       <c r="Q39" t="n">
         <v>-1.438970000000012</v>
@@ -3258,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P40" t="n">
-        <v>79.86793160216462</v>
+        <v>81.23342783777031</v>
       </c>
       <c r="Q40" t="n">
         <v>-5.848210000000009</v>
@@ -3270,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>46.63547670753705</v>
+        <v>64.37157114277989</v>
       </c>
       <c r="T40" t="n">
-        <v>46.63547670753705</v>
+        <v>64.37157114277989</v>
       </c>
     </row>
     <row r="41">
@@ -3332,10 +3332,10 @@
         <v>0.75</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P41" t="n">
-        <v>78.5264174890974</v>
+        <v>79.89622653741377</v>
       </c>
       <c r="Q41" t="n">
         <v>1.867959999999982</v>
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>51.01991516964209</v>
+        <v>68.76871120572407</v>
       </c>
       <c r="T41" t="n">
-        <v>51.01991516964209</v>
+        <v>68.76871120572407</v>
       </c>
     </row>
     <row r="42">
@@ -3406,10 +3406,10 @@
         <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P42" t="n">
-        <v>74.05470377887335</v>
+        <v>75.43888886955864</v>
       </c>
       <c r="Q42" t="n">
         <v>0.7656499999999937</v>
@@ -3418,10 +3418,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>47.18614525683967</v>
+        <v>64.93634414965962</v>
       </c>
       <c r="T42" t="n">
-        <v>47.18614525683967</v>
+        <v>64.93634414965962</v>
       </c>
     </row>
     <row r="43">
@@ -3480,10 +3480,10 @@
         <v>3.75</v>
       </c>
       <c r="O43" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P43" t="n">
-        <v>73.16036103682853</v>
+        <v>74.54742133598762</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3492,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>44.29654272350545</v>
+        <v>62.04231176538674</v>
       </c>
       <c r="T43" t="n">
-        <v>44.29654272350545</v>
+        <v>62.04231176538674</v>
       </c>
     </row>
     <row r="44">
@@ -3554,10 +3554,10 @@
         <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P44" t="n">
-        <v>73.07092676262405</v>
+        <v>74.45827458263051</v>
       </c>
       <c r="Q44" t="n">
         <v>-5.848210000000009</v>
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>41.9605499390688</v>
+        <v>59.70133380293731</v>
       </c>
       <c r="T44" t="n">
-        <v>41.9605499390688</v>
+        <v>59.70133380293731</v>
       </c>
     </row>
     <row r="45">
@@ -3628,10 +3628,10 @@
         <v>3.85</v>
       </c>
       <c r="O45" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P45" t="n">
-        <v>72.98149248841958</v>
+        <v>74.36912782927341</v>
       </c>
       <c r="Q45" t="n">
         <v>0.7656499999999937</v>
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>46.44799892497626</v>
+        <v>64.19893825389499</v>
       </c>
       <c r="T45" t="n">
-        <v>46.44799892497626</v>
+        <v>64.19893825389499</v>
       </c>
     </row>
     <row r="46">
@@ -3702,10 +3702,10 @@
         <v>6.85</v>
       </c>
       <c r="O46" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P46" t="n">
-        <v>67.61543603615071</v>
+        <v>69.02032262784725</v>
       </c>
       <c r="Q46" t="n">
         <v>-5.848210000000009</v>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>38.20830608542981</v>
+        <v>55.95285383280051</v>
       </c>
       <c r="T46" t="n">
-        <v>38.20830608542981</v>
+        <v>55.95285383280051</v>
       </c>
     </row>
     <row r="47">
@@ -3776,10 +3776,10 @@
         <v>13.85</v>
       </c>
       <c r="O47" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P47" t="n">
-        <v>55.09463764752336</v>
+        <v>56.5397771578529</v>
       </c>
       <c r="Q47" t="n">
         <v>-2.541280000000015</v>
@@ -3788,10 +3788,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>31.87107947047142</v>
+        <v>49.62931252001568</v>
       </c>
       <c r="T47" t="n">
-        <v>31.87107947047142</v>
+        <v>49.62931252001568</v>
       </c>
     </row>
     <row r="48">
@@ -3850,10 +3850,10 @@
         <v>28.85</v>
       </c>
       <c r="O48" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P48" t="n">
-        <v>36.18672126224121</v>
+        <v>37.69560246296859</v>
       </c>
       <c r="Q48" t="n">
         <v>-5.848210000000009</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P49" t="n">
-        <v>90.40458204494996</v>
+        <v>90.09668529947784</v>
       </c>
       <c r="Q49" t="n">
         <v>-5.848210000000009</v>
@@ -3934,10 +3934,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S49" t="n">
-        <v>62.16795569996496</v>
+        <v>78.78501494071776</v>
       </c>
       <c r="T49" t="n">
-        <v>62.16795569996496</v>
+        <v>78.78501494071776</v>
       </c>
     </row>
     <row r="50">
@@ -3996,10 +3996,10 @@
         <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P50" t="n">
-        <v>84.15087144883182</v>
+        <v>83.85857846423276</v>
       </c>
       <c r="Q50" t="n">
         <v>-1.438970000000012</v>
@@ -4008,10 +4008,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S50" t="n">
-        <v>60.8993432497746</v>
+        <v>77.52434350467584</v>
       </c>
       <c r="T50" t="n">
-        <v>60.8993432497746</v>
+        <v>77.52434350467584</v>
       </c>
     </row>
     <row r="51">
@@ -4070,10 +4070,10 @@
         <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P51" t="n">
-        <v>82.90012932960821</v>
+        <v>82.61095709718376</v>
       </c>
       <c r="Q51" t="n">
         <v>-1.438970000000012</v>
@@ -4082,10 +4082,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S51" t="n">
-        <v>60.03909260237261</v>
+        <v>76.66433522516459</v>
       </c>
       <c r="T51" t="n">
-        <v>60.03909260237261</v>
+        <v>76.66433522516459</v>
       </c>
     </row>
     <row r="52">
@@ -4144,10 +4144,10 @@
         <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P52" t="n">
-        <v>72.89419237581919</v>
+        <v>72.62998616079163</v>
       </c>
       <c r="Q52" t="n">
         <v>-2.541280000000015</v>
@@ -4156,10 +4156,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S52" t="n">
-        <v>52.39892722645178</v>
+        <v>69.02442649869612</v>
       </c>
       <c r="T52" t="n">
-        <v>52.39892722645178</v>
+        <v>69.02442649869612</v>
       </c>
     </row>
     <row r="53">
@@ -4218,10 +4218,10 @@
         <v>7.1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P53" t="n">
-        <v>72.64404395197447</v>
+        <v>72.38046188738184</v>
       </c>
       <c r="Q53" t="n">
         <v>-1.438970000000012</v>
@@ -4230,10 +4230,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S53" t="n">
-        <v>52.98503729367629</v>
+        <v>69.61226733317244</v>
       </c>
       <c r="T53" t="n">
-        <v>52.98503729367629</v>
+        <v>69.61226733317244</v>
       </c>
     </row>
     <row r="54">
@@ -4292,10 +4292,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P54" t="n">
-        <v>72.39389552812975</v>
+        <v>72.13093761397204</v>
       </c>
       <c r="Q54" t="n">
         <v>2.970269999999999</v>
@@ -4304,10 +4304,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S54" t="n">
-        <v>55.8456279510155</v>
+        <v>72.47963563878446</v>
       </c>
       <c r="T54" t="n">
-        <v>55.8456279510155</v>
+        <v>72.47963563878446</v>
       </c>
     </row>
     <row r="55">
@@ -4366,10 +4366,10 @@
         <v>7.35</v>
       </c>
       <c r="O55" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P55" t="n">
-        <v>72.01867289236264</v>
+        <v>71.75665120385733</v>
       </c>
       <c r="Q55" t="n">
         <v>-1.438970000000012</v>
@@ -4378,10 +4378,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S55" t="n">
-        <v>52.55491196997528</v>
+        <v>69.18226319341682</v>
       </c>
       <c r="T55" t="n">
-        <v>52.55491196997528</v>
+        <v>69.18226319341682</v>
       </c>
     </row>
     <row r="56">
@@ -4440,10 +4440,10 @@
         <v>8.35</v>
       </c>
       <c r="O56" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P56" t="n">
-        <v>69.5171886539154</v>
+        <v>69.2614084697593</v>
       </c>
       <c r="Q56" t="n">
         <v>-1.438970000000012</v>
@@ -4452,10 +4452,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S56" t="n">
-        <v>50.8344106751713</v>
+        <v>67.46224663439435</v>
       </c>
       <c r="T56" t="n">
-        <v>50.8344106751713</v>
+        <v>67.46224663439435</v>
       </c>
     </row>
     <row r="57">
@@ -4514,10 +4514,10 @@
         <v>38.35</v>
       </c>
       <c r="O57" t="n">
-        <v>0.001038836764722591</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P57" t="n">
-        <v>17.43417392342444</v>
+        <v>17.31248259249058</v>
       </c>
       <c r="Q57" t="n">
         <v>1.867959999999982</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P58" t="n">
-        <v>108.6957573779524</v>
+        <v>118.6747058673424</v>
       </c>
       <c r="Q58" t="n">
         <v>-2.541280000000015</v>
@@ -4598,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>68.73751040045033</v>
+        <v>92.46005792749008</v>
       </c>
       <c r="T58" t="n">
-        <v>68.73751040045033</v>
+        <v>92.46005792749008</v>
       </c>
     </row>
     <row r="59">
@@ -4660,10 +4660,10 @@
         <v>4</v>
       </c>
       <c r="O59" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P59" t="n">
-        <v>101.3301924407646</v>
+        <v>111.3328203695082</v>
       </c>
       <c r="Q59" t="n">
         <v>-5.848210000000009</v>
@@ -4672,10 +4672,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>61.39705185348043</v>
+        <v>85.11963419237367</v>
       </c>
       <c r="T59" t="n">
-        <v>61.39705185348043</v>
+        <v>85.11963419237367</v>
       </c>
     </row>
     <row r="60">
@@ -4734,10 +4734,10 @@
         <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P60" t="n">
-        <v>93.96462750357676</v>
+        <v>103.990934871674</v>
       </c>
       <c r="Q60" t="n">
         <v>6.277199999999993</v>
@@ -4746,10 +4746,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>64.67083606037914</v>
+        <v>88.41700532255715</v>
       </c>
       <c r="T60" t="n">
-        <v>64.67083606037914</v>
+        <v>88.41700532255715</v>
       </c>
     </row>
     <row r="61">
@@ -4808,10 +4808,10 @@
         <v>11</v>
       </c>
       <c r="O61" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P61" t="n">
-        <v>88.44045380068587</v>
+        <v>98.48452074829834</v>
       </c>
       <c r="Q61" t="n">
         <v>-3.643590000000017</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>54.04791082239363</v>
+        <v>77.78275071116448</v>
       </c>
       <c r="T61" t="n">
-        <v>54.04791082239363</v>
+        <v>77.78275071116448</v>
       </c>
     </row>
     <row r="62">
@@ -4882,10 +4882,10 @@
         <v>15</v>
       </c>
       <c r="O62" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P62" t="n">
-        <v>81.07488886349805</v>
+        <v>91.14263525046412</v>
       </c>
       <c r="Q62" t="n">
         <v>-2.541280000000015</v>
@@ -4894,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>49.74009306224335</v>
+        <v>73.4816969375623</v>
       </c>
       <c r="T62" t="n">
-        <v>49.74009306224335</v>
+        <v>73.4816969375623</v>
       </c>
     </row>
     <row r="63">
@@ -4956,10 +4956,10 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>0.0006095290851422144</v>
+        <v>0.001453171281148455</v>
       </c>
       <c r="P63" t="n">
-        <v>70.03103098377402</v>
+        <v>80.14047602086777</v>
       </c>
       <c r="Q63" t="n">
         <v>-2.541280000000015</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
@@ -5096,7 +5096,7 @@
         <v>1.25</v>
       </c>
       <c r="O65" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
@@ -5164,7 +5164,7 @@
         <v>2.5</v>
       </c>
       <c r="O66" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
@@ -5232,7 +5232,7 @@
         <v>2.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
@@ -5300,7 +5300,7 @@
         <v>5.75</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
@@ -5368,7 +5368,7 @@
         <v>7.75</v>
       </c>
       <c r="O69" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
@@ -5436,7 +5436,7 @@
         <v>13.25</v>
       </c>
       <c r="O70" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
@@ -5504,7 +5504,7 @@
         <v>15.75</v>
       </c>
       <c r="O71" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
@@ -5572,7 +5572,7 @@
         <v>17.75</v>
       </c>
       <c r="O72" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
@@ -5642,10 +5642,10 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P73" t="n">
-        <v>120.3649516474506</v>
+        <v>142.3303635933625</v>
       </c>
       <c r="Q73" t="n">
         <v>11.78874999999999</v>
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>86.61957351004526</v>
+        <v>118.6442888248616</v>
       </c>
       <c r="T73" t="n">
-        <v>86.61957351004526</v>
+        <v>118.6442888248616</v>
       </c>
     </row>
     <row r="74">
@@ -5716,10 +5716,10 @@
         <v>0.05</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P74" t="n">
-        <v>120.2708664527387</v>
+        <v>142.2365808716695</v>
       </c>
       <c r="Q74" t="n">
         <v>2.970269999999999</v>
@@ -5728,10 +5728,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>80.48958087533452</v>
+        <v>112.5009027525596</v>
       </c>
       <c r="T74" t="n">
-        <v>80.48958087533452</v>
+        <v>112.5009027525596</v>
       </c>
     </row>
     <row r="75">
@@ -5790,10 +5790,10 @@
         <v>0.3</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P75" t="n">
-        <v>119.8004404791794</v>
+        <v>141.7676672632045</v>
       </c>
       <c r="Q75" t="n">
         <v>-1.438970000000012</v>
@@ -5802,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>77.13338478315717</v>
+        <v>109.1383020446777</v>
       </c>
       <c r="T75" t="n">
-        <v>77.13338478315717</v>
+        <v>109.1383020446777</v>
       </c>
     </row>
     <row r="76">
@@ -5864,10 +5864,10 @@
         <v>1.3</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P76" t="n">
-        <v>117.9187365849418</v>
+        <v>139.8920128293443</v>
       </c>
       <c r="Q76" t="n">
         <v>5.174889999999976</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>80.38812474195564</v>
+        <v>112.4044340014787</v>
       </c>
       <c r="T76" t="n">
-        <v>80.38812474195564</v>
+        <v>112.4044340014787</v>
       </c>
     </row>
     <row r="77">
@@ -5938,10 +5938,10 @@
         <v>1.4</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P77" t="n">
-        <v>117.730566195518</v>
+        <v>139.7044473859583</v>
       </c>
       <c r="Q77" t="n">
         <v>-6.950520000000012</v>
@@ -5950,10 +5950,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>71.91894045605864</v>
+        <v>103.9168743087675</v>
       </c>
       <c r="T77" t="n">
-        <v>71.91894045605864</v>
+        <v>103.9168743087675</v>
       </c>
     </row>
     <row r="78">
@@ -6012,10 +6012,10 @@
         <v>2.65</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P78" t="n">
-        <v>115.3784363277211</v>
+        <v>137.3598793436332</v>
       </c>
       <c r="Q78" t="n">
         <v>2.970269999999999</v>
@@ -6024,10 +6024,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>77.12460569961408</v>
+        <v>109.1393029903366</v>
       </c>
       <c r="T78" t="n">
-        <v>77.12460569961408</v>
+        <v>109.1393029903366</v>
       </c>
     </row>
     <row r="79">
@@ -6086,10 +6086,10 @@
         <v>3.65</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P79" t="n">
-        <v>113.4967324334835</v>
+        <v>135.4842249097731</v>
       </c>
       <c r="Q79" t="n">
         <v>6.277199999999993</v>
@@ -6098,10 +6098,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>78.10486506829787</v>
+        <v>110.1259074760019</v>
       </c>
       <c r="T79" t="n">
-        <v>78.10486506829787</v>
+        <v>110.1259074760019</v>
       </c>
     </row>
     <row r="80">
@@ -6160,10 +6160,10 @@
         <v>4.4</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P80" t="n">
-        <v>112.0854545128053</v>
+        <v>134.077484084378</v>
       </c>
       <c r="Q80" t="n">
         <v>-1.438970000000012</v>
@@ -6172,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>71.82707777529035</v>
+        <v>103.8373178042492</v>
       </c>
       <c r="T80" t="n">
-        <v>71.82707777529035</v>
+        <v>103.8373178042492</v>
       </c>
     </row>
     <row r="81">
@@ -6234,10 +6234,10 @@
         <v>4.9</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P81" t="n">
-        <v>111.1446025656866</v>
+        <v>133.1396568674479</v>
       </c>
       <c r="Q81" t="n">
         <v>1.867959999999982</v>
@@ -6246,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>73.45444775468957</v>
+        <v>105.4703837826496</v>
       </c>
       <c r="T81" t="n">
-        <v>73.45444775468957</v>
+        <v>105.4703837826496</v>
       </c>
     </row>
     <row r="82">
@@ -6308,10 +6308,10 @@
         <v>12.4</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P82" t="n">
-        <v>97.03182335890483</v>
+        <v>119.0722486134971</v>
       </c>
       <c r="Q82" t="n">
         <v>12.89105999999998</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>71.32939056100662</v>
+        <v>103.3718862954074</v>
       </c>
       <c r="T82" t="n">
-        <v>71.32939056100662</v>
+        <v>103.3718862954074</v>
       </c>
     </row>
     <row r="83">
@@ -6382,10 +6382,10 @@
         <v>15.9</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P83" t="n">
-        <v>90.44585972907335</v>
+        <v>112.5074580949868</v>
       </c>
       <c r="Q83" t="n">
         <v>-0.3366600000000091</v>
@@ -6394,10 +6394,10 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>57.70169392553954</v>
+        <v>89.72854596171825</v>
       </c>
       <c r="T83" t="n">
-        <v>57.70169392553954</v>
+        <v>89.72854596171825</v>
       </c>
     </row>
     <row r="84">
@@ -6456,10 +6456,10 @@
         <v>28.9</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P84" t="n">
-        <v>74.35504713405086</v>
+        <v>96.47779868853306</v>
       </c>
       <c r="Q84" t="n">
         <v>0.7656499999999937</v>
@@ -6526,10 +6526,10 @@
         <v>58.9</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.0002981738118022428</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P85" t="n">
-        <v>46.1294887204874</v>
+        <v>68.34298218063145</v>
       </c>
       <c r="Q85" t="n">
         <v>-1.438970000000012</v>
@@ -6598,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P86" t="n">
-        <v>37.07874678051884</v>
+        <v>38.87793541825886</v>
       </c>
       <c r="Q86" t="n">
         <v>1.867959999999982</v>
@@ -6610,10 +6610,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S86" t="n">
-        <v>28.74658826782138</v>
+        <v>46.74194088822649</v>
       </c>
       <c r="T86" t="n">
-        <v>28.74658826782138</v>
+        <v>46.74194088822649</v>
       </c>
     </row>
     <row r="87">
@@ -6672,10 +6672,10 @@
         <v>1.5</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P87" t="n">
-        <v>34.47545166662547</v>
+        <v>36.28300959705312</v>
       </c>
       <c r="Q87" t="n">
         <v>1.867959999999982</v>
@@ -6684,10 +6684,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S87" t="n">
-        <v>26.9560622491603</v>
+        <v>44.95321094988554</v>
       </c>
       <c r="T87" t="n">
-        <v>26.9560622491603</v>
+        <v>44.95321094988554</v>
       </c>
     </row>
     <row r="88">
@@ -6746,10 +6746,10 @@
         <v>2.25</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P88" t="n">
-        <v>33.17380410967879</v>
+        <v>34.98554668645026</v>
       </c>
       <c r="Q88" t="n">
         <v>1.867959999999982</v>
@@ -6758,10 +6758,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S88" t="n">
-        <v>26.06079923982975</v>
+        <v>44.05884598071506</v>
       </c>
       <c r="T88" t="n">
-        <v>26.06079923982975</v>
+        <v>44.05884598071506</v>
       </c>
     </row>
     <row r="89">
@@ -6820,10 +6820,10 @@
         <v>2.4</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P89" t="n">
-        <v>32.91347459828945</v>
+        <v>34.72605410432968</v>
       </c>
       <c r="Q89" t="n">
         <v>-2.541280000000015</v>
@@ -6832,10 +6832,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S89" t="n">
-        <v>22.84910585114404</v>
+        <v>40.8406030253667</v>
       </c>
       <c r="T89" t="n">
-        <v>22.84910585114404</v>
+        <v>40.8406030253667</v>
       </c>
     </row>
     <row r="90">
@@ -6894,10 +6894,10 @@
         <v>3.65</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P90" t="n">
-        <v>30.74406200337832</v>
+        <v>32.56361591999157</v>
       </c>
       <c r="Q90" t="n">
         <v>1.867959999999982</v>
@@ -6906,10 +6906,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S90" t="n">
-        <v>24.38964162241274</v>
+        <v>42.38936470493017</v>
       </c>
       <c r="T90" t="n">
-        <v>24.38964162241274</v>
+        <v>42.38936470493017</v>
       </c>
     </row>
     <row r="91">
@@ -6968,10 +6968,10 @@
         <v>3.7</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P91" t="n">
-        <v>30.65728549958187</v>
+        <v>32.47711839261805</v>
       </c>
       <c r="Q91" t="n">
         <v>1.867959999999982</v>
@@ -6980,10 +6980,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S91" t="n">
-        <v>24.32995742179071</v>
+        <v>42.32974037365214</v>
       </c>
       <c r="T91" t="n">
-        <v>24.32995742179071</v>
+        <v>42.32974037365214</v>
       </c>
     </row>
     <row r="92">
@@ -7042,10 +7042,10 @@
         <v>3.85</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P92" t="n">
-        <v>30.39695598819253</v>
+        <v>32.21762581049747</v>
       </c>
       <c r="Q92" t="n">
         <v>1.867959999999982</v>
@@ -7054,10 +7054,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S92" t="n">
-        <v>24.15090481992459</v>
+        <v>42.15086737981805</v>
       </c>
       <c r="T92" t="n">
-        <v>24.15090481992459</v>
+        <v>42.15086737981805</v>
       </c>
     </row>
     <row r="93">
@@ -7116,10 +7116,10 @@
         <v>3.879999999999999</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P93" t="n">
-        <v>30.34489008591467</v>
+        <v>32.16572729407336</v>
       </c>
       <c r="Q93" t="n">
         <v>1.867959999999982</v>
@@ -7128,10 +7128,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S93" t="n">
-        <v>24.11509429955137</v>
+        <v>42.11509278105123</v>
       </c>
       <c r="T93" t="n">
-        <v>24.11509429955137</v>
+        <v>42.11509278105123</v>
       </c>
     </row>
     <row r="94">
@@ -7190,10 +7190,10 @@
         <v>8.879999999999999</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P94" t="n">
-        <v>21.66723970627011</v>
+        <v>23.5159745567209</v>
       </c>
       <c r="Q94" t="n">
         <v>-2.541280000000015</v>
@@ -7202,10 +7202,10 @@
         <v>9.063867016622922</v>
       </c>
       <c r="S94" t="n">
-        <v>15.11403345052815</v>
+        <v>33.11328969173381</v>
       </c>
       <c r="T94" t="n">
-        <v>15.11403345052815</v>
+        <v>33.11328969173381</v>
       </c>
     </row>
     <row r="95">
@@ -7266,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P95" t="n">
-        <v>105.2319019916634</v>
+        <v>111.8595701859632</v>
       </c>
       <c r="Q95" t="n">
         <v>4.072579999999988</v>
@@ -7278,10 +7278,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>70.90405893720717</v>
+        <v>92.32131491056035</v>
       </c>
       <c r="T95" t="n">
-        <v>70.90405893720717</v>
+        <v>92.32131491056035</v>
       </c>
     </row>
     <row r="96">
@@ -7340,10 +7340,10 @@
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P96" t="n">
-        <v>103.3124703129018</v>
+        <v>109.9460514110518</v>
       </c>
       <c r="Q96" t="n">
         <v>4.072579999999988</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>69.583888840654</v>
+        <v>91.00229134068002</v>
       </c>
       <c r="T96" t="n">
-        <v>69.583888840654</v>
+        <v>91.00229134068002</v>
       </c>
     </row>
     <row r="97">
@@ -7414,10 +7414,10 @@
         <v>2.25</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P97" t="n">
-        <v>100.9131807144497</v>
+        <v>107.5541529424126</v>
       </c>
       <c r="Q97" t="n">
         <v>2.970269999999999</v>
@@ -7426,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>67.17551602325764</v>
+        <v>88.59366938795102</v>
       </c>
       <c r="T97" t="n">
-        <v>67.17551602325764</v>
+        <v>88.59366938795102</v>
       </c>
     </row>
     <row r="98">
@@ -7488,10 +7488,10 @@
         <v>4.25</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P98" t="n">
-        <v>97.0743173569265</v>
+        <v>103.7271153925898</v>
       </c>
       <c r="Q98" t="n">
         <v>-0.3366600000000091</v>
@@ -7500,10 +7500,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>62.26069524003659</v>
+        <v>83.67609477705463</v>
       </c>
       <c r="T98" t="n">
-        <v>62.26069524003659</v>
+        <v>83.67609477705463</v>
       </c>
     </row>
     <row r="99">
@@ -7562,10 +7562,10 @@
         <v>5</v>
       </c>
       <c r="O99" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P99" t="n">
-        <v>95.63474359785529</v>
+        <v>102.2919763114063</v>
       </c>
       <c r="Q99" t="n">
         <v>-4.745900000000006</v>
@@ -7574,10 +7574,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>58.23792688080211</v>
+        <v>79.64745713813011</v>
       </c>
       <c r="T99" t="n">
-        <v>58.23792688080211</v>
+        <v>79.64745713813011</v>
       </c>
     </row>
     <row r="100">
@@ -7636,10 +7636,10 @@
         <v>7</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P100" t="n">
-        <v>91.79588024033205</v>
+        <v>98.46493876158351</v>
       </c>
       <c r="Q100" t="n">
         <v>2.970269999999999</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>60.90470806463008</v>
+        <v>82.32830743101937</v>
       </c>
       <c r="T100" t="n">
-        <v>60.90470806463008</v>
+        <v>82.32830743101937</v>
       </c>
     </row>
     <row r="101">
@@ -7710,10 +7710,10 @@
         <v>8.25</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P101" t="n">
-        <v>89.39659064188004</v>
+        <v>96.07304029294428</v>
       </c>
       <c r="Q101" t="n">
         <v>-0.3366600000000091</v>
@@ -7722,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>56.98001485382392</v>
+        <v>78.40000049753323</v>
       </c>
       <c r="T101" t="n">
-        <v>56.98001485382392</v>
+        <v>78.40000049753323</v>
       </c>
     </row>
     <row r="102">
@@ -7784,10 +7784,10 @@
         <v>14.25</v>
       </c>
       <c r="O102" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P102" t="n">
-        <v>77.88000056931034</v>
+        <v>84.591927643476</v>
       </c>
       <c r="Q102" t="n">
         <v>-3.643590000000017</v>
@@ -7796,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>46.78451368439018</v>
+        <v>68.20633160711546</v>
       </c>
       <c r="T102" t="n">
-        <v>46.78451368439018</v>
+        <v>68.20633160711546</v>
       </c>
     </row>
     <row r="103">
@@ -7858,10 +7858,10 @@
         <v>16.75</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P103" t="n">
-        <v>73.08142137240631</v>
+        <v>79.80813070619755</v>
       </c>
       <c r="Q103" t="n">
         <v>-1.438970000000012</v>
@@ -7870,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>45.00040883641707</v>
+        <v>66.42845766317171</v>
       </c>
       <c r="T103" t="n">
-        <v>45.00040883641707</v>
+        <v>66.42845766317171</v>
       </c>
     </row>
     <row r="104">
@@ -7932,10 +7932,10 @@
         <v>18.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P104" t="n">
-        <v>69.24255801488306</v>
+        <v>75.98109315637478</v>
       </c>
       <c r="Q104" t="n">
         <v>1.867959999999982</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>44.63454923342542</v>
+        <v>66.06993799454671</v>
       </c>
       <c r="T104" t="n">
-        <v>44.63454923342542</v>
+        <v>66.06993799454671</v>
       </c>
     </row>
     <row r="105">
@@ -8006,10 +8006,10 @@
         <v>18.8</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P105" t="n">
-        <v>69.14658643094498</v>
+        <v>75.88541721762923</v>
       </c>
       <c r="Q105" t="n">
         <v>0.7656499999999937</v>
@@ -8018,10 +8018,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>43.81038053189286</v>
+        <v>65.24414432567414</v>
       </c>
       <c r="T105" t="n">
-        <v>43.81038053189286</v>
+        <v>65.24414432567414</v>
       </c>
     </row>
     <row r="106">
@@ -8080,10 +8080,10 @@
         <v>19.05</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P106" t="n">
-        <v>68.66672851125458</v>
+        <v>75.40703752390138</v>
       </c>
       <c r="Q106" t="n">
         <v>-5.848210000000009</v>
@@ -8092,10 +8092,10 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>38.93137682752516</v>
+        <v>60.35533349093267</v>
       </c>
       <c r="T106" t="n">
-        <v>38.93137682752516</v>
+        <v>60.35533349093267</v>
       </c>
     </row>
     <row r="107">
@@ -8154,10 +8154,10 @@
         <v>19.2</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P107" t="n">
-        <v>68.37881375944033</v>
+        <v>75.12000970766468</v>
       </c>
       <c r="Q107" t="n">
         <v>6.277199999999993</v>
@@ -8166,10 +8166,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>47.0731134767961</v>
+        <v>68.51574734961484</v>
       </c>
       <c r="T107" t="n">
-        <v>47.0731134767961</v>
+        <v>68.51574734961484</v>
       </c>
     </row>
     <row r="108">
@@ -8228,10 +8228,10 @@
         <v>24.2</v>
       </c>
       <c r="O108" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P108" t="n">
-        <v>62.8156337476784</v>
+        <v>69.5781363292502</v>
       </c>
       <c r="Q108" t="n">
         <v>4.072579999999988</v>
@@ -8298,10 +8298,10 @@
         <v>24.45</v>
       </c>
       <c r="O109" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P109" t="n">
-        <v>62.5757047878332</v>
+        <v>69.33894648238628</v>
       </c>
       <c r="Q109" t="n">
         <v>-0.3366600000000091</v>
@@ -8368,10 +8368,10 @@
         <v>35.45</v>
       </c>
       <c r="O110" t="n">
-        <v>0.0004131244526489613</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P110" t="n">
-        <v>52.01883055464431</v>
+        <v>58.81459322037369</v>
       </c>
       <c r="Q110" t="n">
         <v>2.970269999999999</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P111" t="n">
-        <v>101.9108950892356</v>
+        <v>105.2305928193862</v>
       </c>
       <c r="Q111" t="n">
         <v>5.174889999999976</v>
@@ -8452,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>69.37805656040467</v>
+        <v>88.51168178075679</v>
       </c>
       <c r="T111" t="n">
-        <v>69.37805656040467</v>
+        <v>88.51168178075679</v>
       </c>
     </row>
     <row r="112">
@@ -8514,10 +8514,10 @@
         <v>2</v>
       </c>
       <c r="O112" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P112" t="n">
-        <v>98.09199115991443</v>
+        <v>101.4234532117636</v>
       </c>
       <c r="Q112" t="n">
         <v>-10.25745000000001</v>
@@ -8526,10 +8526,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>56.13720155204206</v>
+        <v>75.24955579202077</v>
       </c>
       <c r="T112" t="n">
-        <v>56.13720155204206</v>
+        <v>75.24955579202077</v>
       </c>
     </row>
     <row r="113">
@@ -8588,10 +8588,10 @@
         <v>2.25</v>
       </c>
       <c r="O113" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P113" t="n">
-        <v>97.61462816874928</v>
+        <v>100.9475607608108</v>
       </c>
       <c r="Q113" t="n">
         <v>-3.643590000000017</v>
@@ -8600,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>60.35783620045971</v>
+        <v>79.48056934386264</v>
       </c>
       <c r="T113" t="n">
-        <v>60.35783620045971</v>
+        <v>79.48056934386264</v>
       </c>
     </row>
     <row r="114">
@@ -8662,10 +8662,10 @@
         <v>5.25</v>
       </c>
       <c r="O114" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P114" t="n">
-        <v>91.88627227476748</v>
+        <v>95.23685134937681</v>
       </c>
       <c r="Q114" t="n">
         <v>-6.950520000000012</v>
@@ -8674,10 +8674,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>54.14343722860401</v>
+        <v>73.26454518757276</v>
       </c>
       <c r="T114" t="n">
-        <v>54.14343722860401</v>
+        <v>73.26454518757276</v>
       </c>
     </row>
     <row r="115">
@@ -8736,10 +8736,10 @@
         <v>7.75</v>
       </c>
       <c r="O115" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P115" t="n">
-        <v>87.11264236311597</v>
+        <v>90.47792683984851</v>
       </c>
       <c r="Q115" t="n">
         <v>-1.438970000000012</v>
@@ -8748,10 +8748,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>54.65097289401101</v>
+        <v>73.78334373517046</v>
       </c>
       <c r="T115" t="n">
-        <v>54.65097289401101</v>
+        <v>73.78334373517046</v>
       </c>
     </row>
     <row r="116">
@@ -8810,10 +8810,10 @@
         <v>8.75</v>
       </c>
       <c r="O116" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P116" t="n">
-        <v>85.20319039845538</v>
+        <v>88.57435703603718</v>
       </c>
       <c r="Q116" t="n">
         <v>5.174889999999976</v>
@@ -8822,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>57.88662794699341</v>
+        <v>77.0302331157238</v>
       </c>
       <c r="T116" t="n">
-        <v>57.88662794699341</v>
+        <v>77.0302331157238</v>
       </c>
     </row>
     <row r="117">
@@ -8884,10 +8884,10 @@
         <v>9.5</v>
       </c>
       <c r="O117" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P117" t="n">
-        <v>83.77110142495992</v>
+        <v>87.14667968317869</v>
       </c>
       <c r="Q117" t="n">
         <v>2.970269999999999</v>
@@ -8896,10 +8896,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>55.38532795814837</v>
+        <v>74.52642396367813</v>
       </c>
       <c r="T117" t="n">
-        <v>55.38532795814837</v>
+        <v>74.52642396367813</v>
       </c>
     </row>
     <row r="118">
@@ -8958,10 +8958,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O118" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P118" t="n">
-        <v>83.67562882672689</v>
+        <v>87.05150119298813</v>
       </c>
       <c r="Q118" t="n">
         <v>-9.155140000000017</v>
@@ -8970,10 +8970,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>46.9799004880321</v>
+        <v>66.10254829142799</v>
       </c>
       <c r="T118" t="n">
-        <v>46.9799004880321</v>
+        <v>66.10254829142799</v>
       </c>
     </row>
     <row r="119">
@@ -9032,10 +9032,10 @@
         <v>10.05</v>
       </c>
       <c r="O119" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P119" t="n">
-        <v>82.72090284439659</v>
+        <v>86.09971629108247</v>
       </c>
       <c r="Q119" t="n">
         <v>-4.745900000000006</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>49.3558882112282</v>
+        <v>68.48583547208324</v>
       </c>
       <c r="T119" t="n">
-        <v>49.3558882112282</v>
+        <v>68.48583547208324</v>
       </c>
     </row>
     <row r="120">
@@ -9106,10 +9106,10 @@
         <v>14.05</v>
       </c>
       <c r="O120" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P120" t="n">
-        <v>75.08309498575417</v>
+        <v>78.48543707583718</v>
       </c>
       <c r="Q120" t="n">
         <v>2.970269999999999</v>
@@ -9118,10 +9118,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>49.4097850791745</v>
+        <v>68.55607065786097</v>
       </c>
       <c r="T120" t="n">
-        <v>49.4097850791745</v>
+        <v>68.55607065786097</v>
       </c>
     </row>
     <row r="121">
@@ -9180,10 +9180,10 @@
         <v>15.05</v>
       </c>
       <c r="O121" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P121" t="n">
-        <v>73.17364302109357</v>
+        <v>76.58186727202586</v>
       </c>
       <c r="Q121" t="n">
         <v>-10.25745000000001</v>
@@ -9192,10 +9192,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>38.99855659146869</v>
+        <v>58.12579521160012</v>
       </c>
       <c r="T121" t="n">
-        <v>38.99855659146869</v>
+        <v>58.12579521160012</v>
       </c>
     </row>
     <row r="122">
@@ -9254,10 +9254,10 @@
         <v>15.3</v>
       </c>
       <c r="O122" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P122" t="n">
-        <v>72.69628002992843</v>
+        <v>76.10597482107303</v>
       </c>
       <c r="Q122" t="n">
         <v>5.174889999999976</v>
@@ -9266,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>49.28447281352555</v>
+        <v>68.43554868647051</v>
       </c>
       <c r="T122" t="n">
-        <v>49.28447281352555</v>
+        <v>68.43554868647051</v>
       </c>
     </row>
     <row r="123">
@@ -9328,10 +9328,10 @@
         <v>18.3</v>
       </c>
       <c r="O123" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P123" t="n">
-        <v>66.96792413594662</v>
+        <v>70.39526540963908</v>
       </c>
       <c r="Q123" t="n">
         <v>6.277199999999993</v>
@@ -9340,10 +9340,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>46.10271462848945</v>
+        <v>65.25889449169492</v>
       </c>
       <c r="T123" t="n">
-        <v>46.10271462848945</v>
+        <v>65.25889449169492</v>
       </c>
     </row>
     <row r="124">
@@ -9402,10 +9402,10 @@
         <v>19.05</v>
       </c>
       <c r="O124" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P124" t="n">
-        <v>65.53583516245116</v>
+        <v>68.96758805678058</v>
       </c>
       <c r="Q124" t="n">
         <v>-8.052830000000014</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>35.26165247589049</v>
+        <v>54.39681794548502</v>
       </c>
       <c r="T124" t="n">
-        <v>35.26165247589049</v>
+        <v>54.39681794548502</v>
       </c>
     </row>
     <row r="125">
@@ -9476,10 +9476,10 @@
         <v>19.08</v>
       </c>
       <c r="O125" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P125" t="n">
-        <v>65.47855160351135</v>
+        <v>68.91048096266624</v>
       </c>
       <c r="Q125" t="n">
         <v>4.072579999999988</v>
@@ -9488,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>43.56201545582699</v>
+        <v>62.7157203727977</v>
       </c>
       <c r="T125" t="n">
-        <v>43.56201545582699</v>
+        <v>62.7157203727977</v>
       </c>
     </row>
     <row r="126">
@@ -9550,10 +9550,10 @@
         <v>19.33</v>
       </c>
       <c r="O126" t="n">
-        <v>0.0005856244526489607</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P126" t="n">
-        <v>65.0011886123462</v>
+        <v>68.4345885117134</v>
       </c>
       <c r="Q126" t="n">
         <v>5.174889999999976</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>43.99184912072013</v>
+        <v>63.14752147274674</v>
       </c>
       <c r="T126" t="n">
-        <v>43.99184912072013</v>
+        <v>63.14752147274674</v>
       </c>
     </row>
     <row r="127">
@@ -9626,10 +9626,10 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P127" t="n">
-        <v>111.8466819708988</v>
+        <v>124.8184124716513</v>
       </c>
       <c r="Q127" t="n">
         <v>-3.643590000000017</v>
@@ -9638,10 +9638,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>70.14653149502513</v>
+        <v>95.93518502495283</v>
       </c>
       <c r="T127" t="n">
-        <v>70.14653149502513</v>
+        <v>95.93518502495283</v>
       </c>
     </row>
     <row r="128">
@@ -9700,10 +9700,10 @@
         <v>0.25</v>
       </c>
       <c r="O128" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P128" t="n">
-        <v>111.2210564367968</v>
+        <v>124.1943479485811</v>
       </c>
       <c r="Q128" t="n">
         <v>-5.848210000000009</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>68.19991075235026</v>
+        <v>93.98532092818789</v>
       </c>
       <c r="T128" t="n">
-        <v>68.19991075235026</v>
+        <v>93.98532092818789</v>
       </c>
     </row>
     <row r="129">
@@ -9774,10 +9774,10 @@
         <v>1.25</v>
       </c>
       <c r="O129" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P129" t="n">
-        <v>108.7185543003888</v>
+        <v>121.6980898563003</v>
       </c>
       <c r="Q129" t="n">
         <v>-5.848210000000009</v>
@@ -9786,10 +9786,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>66.47870935528999</v>
+        <v>92.26460446415663</v>
       </c>
       <c r="T129" t="n">
-        <v>66.47870935528999</v>
+        <v>92.26460446415663</v>
       </c>
     </row>
     <row r="130">
@@ -9848,10 +9848,10 @@
         <v>1.5</v>
       </c>
       <c r="O130" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P130" t="n">
-        <v>108.0929287662869</v>
+        <v>121.0740253332301</v>
       </c>
       <c r="Q130" t="n">
         <v>-2.541280000000015</v>
@@ -9860,10 +9860,10 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>68.32288959613965</v>
+        <v>94.11395281928452</v>
       </c>
       <c r="T130" t="n">
-        <v>68.32288959613965</v>
+        <v>94.11395281928452</v>
       </c>
     </row>
     <row r="131">
@@ -9922,10 +9922,10 @@
         <v>1.75</v>
       </c>
       <c r="O131" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P131" t="n">
-        <v>107.4673032321849</v>
+        <v>120.4499608101599</v>
       </c>
       <c r="Q131" t="n">
         <v>-1.438970000000012</v>
@@ -9934,10 +9934,10 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>68.65074944357949</v>
+        <v>94.44361619365529</v>
       </c>
       <c r="T131" t="n">
-        <v>68.65074944357949</v>
+        <v>94.44361619365529</v>
       </c>
     </row>
     <row r="132">
@@ -9996,10 +9996,10 @@
         <v>2.25</v>
       </c>
       <c r="O132" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P132" t="n">
-        <v>106.2160521639809</v>
+        <v>119.2018317640196</v>
       </c>
       <c r="Q132" t="n">
         <v>-2.541280000000015</v>
@@ -10008,10 +10008,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>67.03198854834443</v>
+        <v>92.82341547126111</v>
       </c>
       <c r="T132" t="n">
-        <v>67.03198854834443</v>
+        <v>92.82341547126111</v>
       </c>
     </row>
     <row r="133">
@@ -10070,10 +10070,10 @@
         <v>2.5</v>
       </c>
       <c r="O133" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P133" t="n">
-        <v>105.5904266298789</v>
+        <v>118.5777672409494</v>
       </c>
       <c r="Q133" t="n">
         <v>-5.848210000000009</v>
@@ -10082,10 +10082,10 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>64.32720760896467</v>
+        <v>90.11370888411759</v>
       </c>
       <c r="T133" t="n">
-        <v>64.32720760896467</v>
+        <v>90.11370888411759</v>
       </c>
     </row>
     <row r="134">
@@ -10144,10 +10144,10 @@
         <v>2.75</v>
       </c>
       <c r="O134" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P134" t="n">
-        <v>104.9648010957769</v>
+        <v>117.9537027178792</v>
       </c>
       <c r="Q134" t="n">
         <v>-5.848210000000009</v>
@@ -10156,10 +10156,10 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>63.89690725969961</v>
+        <v>89.68352976810979</v>
       </c>
       <c r="T134" t="n">
-        <v>63.89690725969961</v>
+        <v>89.68352976810979</v>
       </c>
     </row>
     <row r="135">
@@ -10218,10 +10218,10 @@
         <v>3.25</v>
       </c>
       <c r="O135" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P135" t="n">
-        <v>103.7135500275729</v>
+        <v>116.7055736717388</v>
       </c>
       <c r="Q135" t="n">
         <v>-5.848210000000009</v>
@@ -10230,10 +10230,10 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>63.03630656116949</v>
+        <v>88.82317153609418</v>
       </c>
       <c r="T135" t="n">
-        <v>63.03630656116949</v>
+        <v>88.82317153609418</v>
       </c>
     </row>
     <row r="136">
@@ -10292,10 +10292,10 @@
         <v>3.5</v>
       </c>
       <c r="O136" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P136" t="n">
-        <v>103.0879244934709</v>
+        <v>116.0815091486686</v>
       </c>
       <c r="Q136" t="n">
         <v>-2.541280000000015</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>64.88048680201911</v>
+        <v>90.67251989122207</v>
       </c>
       <c r="T136" t="n">
-        <v>64.88048680201911</v>
+        <v>90.67251989122207</v>
       </c>
     </row>
     <row r="137">
@@ -10366,10 +10366,10 @@
         <v>4</v>
       </c>
       <c r="O137" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P137" t="n">
-        <v>101.8366734252669</v>
+        <v>114.8333801025282</v>
       </c>
       <c r="Q137" t="n">
         <v>-2.541280000000015</v>
@@ -10378,10 +10378,10 @@
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>64.01988610348897</v>
+        <v>89.81216165920645</v>
       </c>
       <c r="T137" t="n">
-        <v>64.01988610348897</v>
+        <v>89.81216165920645</v>
       </c>
     </row>
     <row r="138">
@@ -10440,10 +10440,10 @@
         <v>6</v>
       </c>
       <c r="O138" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P138" t="n">
-        <v>96.83166915245101</v>
+        <v>109.8408639179666</v>
       </c>
       <c r="Q138" t="n">
         <v>-2.541280000000015</v>
@@ -10452,10 +10452,10 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>60.57748330936847</v>
+        <v>86.37072873114397</v>
       </c>
       <c r="T138" t="n">
-        <v>60.57748330936847</v>
+        <v>86.37072873114397</v>
       </c>
     </row>
     <row r="139">
@@ -10514,10 +10514,10 @@
         <v>7</v>
       </c>
       <c r="O139" t="n">
-        <v>9.395817958185719e-05</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P139" t="n">
-        <v>94.32916701604304</v>
+        <v>107.3446058256859</v>
       </c>
       <c r="Q139" t="n">
         <v>-5.848210000000009</v>
@@ -10526,10 +10526,10 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>56.5818013221935</v>
+        <v>82.37048479597703</v>
       </c>
       <c r="T139" t="n">
-        <v>56.5818013221935</v>
+        <v>82.37048479597703</v>
       </c>
     </row>
     <row r="140">
@@ -10590,10 +10590,10 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P140" t="n">
-        <v>82.49631191784735</v>
+        <v>83.6852390701916</v>
       </c>
       <c r="Q140" t="n">
         <v>-1.438970000000012</v>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>51.47589691861418</v>
+        <v>69.10101953303121</v>
       </c>
       <c r="T140" t="n">
-        <v>51.47589691861418</v>
+        <v>69.10101953303121</v>
       </c>
     </row>
     <row r="141">
@@ -10664,10 +10664,10 @@
         <v>0.75</v>
       </c>
       <c r="O141" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P141" t="n">
-        <v>80.68111150455852</v>
+        <v>81.87456780048086</v>
       </c>
       <c r="Q141" t="n">
         <v>-0.3366600000000091</v>
@@ -10676,10 +10676,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>50.9855764679532</v>
+        <v>68.61273312424899</v>
       </c>
       <c r="T141" t="n">
-        <v>50.9855764679532</v>
+        <v>68.61273312424899</v>
       </c>
     </row>
     <row r="142">
@@ -10738,10 +10738,10 @@
         <v>1.5</v>
       </c>
       <c r="O142" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P142" t="n">
-        <v>78.86591109126968</v>
+        <v>80.06389653077011</v>
       </c>
       <c r="Q142" t="n">
         <v>-2.541280000000015</v>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>48.22077542717751</v>
+        <v>65.84491924433105</v>
       </c>
       <c r="T142" t="n">
-        <v>48.22077542717751</v>
+        <v>65.84491924433105</v>
       </c>
     </row>
     <row r="143">
@@ -10812,10 +10812,10 @@
         <v>1.75</v>
       </c>
       <c r="O143" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P143" t="n">
-        <v>78.26084428684007</v>
+        <v>79.46033944086653</v>
       </c>
       <c r="Q143" t="n">
         <v>-3.643590000000017</v>
@@ -10824,10 +10824,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>47.04645501468399</v>
+        <v>64.66903378756555</v>
       </c>
       <c r="T143" t="n">
-        <v>47.04645501468399</v>
+        <v>64.66903378756555</v>
       </c>
     </row>
     <row r="144">
@@ -10886,10 +10886,10 @@
         <v>2.75</v>
       </c>
       <c r="O144" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P144" t="n">
-        <v>75.84057706912162</v>
+        <v>77.04611108125221</v>
       </c>
       <c r="Q144" t="n">
         <v>-2.541280000000015</v>
@@ -10898,10 +10898,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>46.13997434823439</v>
+        <v>63.7647044123964</v>
       </c>
       <c r="T144" t="n">
-        <v>46.13997434823439</v>
+        <v>63.7647044123964</v>
       </c>
     </row>
     <row r="145">
@@ -10960,10 +10960,10 @@
         <v>2.78</v>
       </c>
       <c r="O145" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P145" t="n">
-        <v>75.76796905259008</v>
+        <v>76.97368423046377</v>
       </c>
       <c r="Q145" t="n">
         <v>-5.848210000000009</v>
@@ -10972,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>43.81555453222506</v>
+        <v>61.43525178529428</v>
       </c>
       <c r="T145" t="n">
-        <v>43.81555453222506</v>
+        <v>61.43525178529428</v>
       </c>
     </row>
     <row r="146">
@@ -11034,10 +11034,10 @@
         <v>8.779999999999999</v>
       </c>
       <c r="O146" t="n">
-        <v>0.0006857000305949789</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P146" t="n">
-        <v>61.24636574627939</v>
+        <v>62.48831407277781</v>
       </c>
       <c r="Q146" t="n">
         <v>-2.541280000000015</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>36.10218994341273</v>
+        <v>53.72974806314363</v>
       </c>
       <c r="T146" t="n">
-        <v>36.10218994341273</v>
+        <v>53.72974806314363</v>
       </c>
     </row>
     <row r="147">
@@ -11110,10 +11110,10 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P147" t="n">
-        <v>103.4429458407869</v>
+        <v>107.7608644819934</v>
       </c>
       <c r="Q147" t="n">
         <v>-2.541280000000015</v>
@@ -11122,10 +11122,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>65.12466770803968</v>
+        <v>84.9369469896956</v>
       </c>
       <c r="T147" t="n">
-        <v>65.12466770803968</v>
+        <v>84.9369469896956</v>
       </c>
     </row>
     <row r="148">
@@ -11184,10 +11184,10 @@
         <v>1.5</v>
       </c>
       <c r="O148" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P148" t="n">
-        <v>100.949887333826</v>
+        <v>105.2762685251667</v>
       </c>
       <c r="Q148" t="n">
         <v>1.867959999999982</v>
@@ -11196,10 +11196,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>66.44260235227296</v>
+        <v>86.26363941093561</v>
       </c>
       <c r="T148" t="n">
-        <v>66.44260235227296</v>
+        <v>86.26363941093561</v>
       </c>
     </row>
     <row r="149">
@@ -11258,10 +11258,10 @@
         <v>2.75</v>
       </c>
       <c r="O149" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P149" t="n">
-        <v>98.87233857802522</v>
+        <v>103.2057718944777</v>
       </c>
       <c r="Q149" t="n">
         <v>1.867959999999982</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>65.01368056678439</v>
+        <v>84.83640812737369</v>
       </c>
       <c r="T149" t="n">
-        <v>65.01368056678439</v>
+        <v>84.83640812737369</v>
       </c>
     </row>
     <row r="150">
@@ -11332,10 +11332,10 @@
         <v>3</v>
       </c>
       <c r="O150" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P150" t="n">
-        <v>98.45682882686506</v>
+        <v>102.7916725683399</v>
       </c>
       <c r="Q150" t="n">
         <v>-1.438970000000012</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>62.45341561957195</v>
+        <v>82.27143439952562</v>
       </c>
       <c r="T150" t="n">
-        <v>62.45341561957195</v>
+        <v>82.27143439952562</v>
       </c>
     </row>
     <row r="151">
@@ -11406,10 +11406,10 @@
         <v>11.5</v>
       </c>
       <c r="O151" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P151" t="n">
-        <v>84.32949728741985</v>
+        <v>88.71229547965513</v>
       </c>
       <c r="Q151" t="n">
         <v>2.970269999999999</v>
@@ -11418,10 +11418,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>55.76938826506913</v>
+        <v>75.60563163281901</v>
       </c>
       <c r="T151" t="n">
-        <v>55.76938826506913</v>
+        <v>75.60563163281901</v>
       </c>
     </row>
     <row r="152">
@@ -11480,10 +11480,10 @@
         <v>13</v>
       </c>
       <c r="O152" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P152" t="n">
-        <v>81.83643878045893</v>
+        <v>86.22769952282839</v>
       </c>
       <c r="Q152" t="n">
         <v>-1.438970000000012</v>
@@ -11492,10 +11492,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>51.0220413356632</v>
+        <v>70.85358413103046</v>
       </c>
       <c r="T152" t="n">
-        <v>51.0220413356632</v>
+        <v>70.85358413103046</v>
       </c>
     </row>
     <row r="153">
@@ -11554,10 +11554,10 @@
         <v>17</v>
       </c>
       <c r="O153" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P153" t="n">
-        <v>75.18828276189649</v>
+        <v>79.60211030462378</v>
       </c>
       <c r="Q153" t="n">
         <v>2.970269999999999</v>
@@ -11566,10 +11566,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>49.48213240891933</v>
+        <v>69.32581398514665</v>
       </c>
       <c r="T153" t="n">
-        <v>49.48213240891933</v>
+        <v>69.32581398514665</v>
       </c>
     </row>
     <row r="154">
@@ -11628,10 +11628,10 @@
         <v>37</v>
       </c>
       <c r="O154" t="n">
-        <v>0.000513073424000417</v>
+        <v>0.0009577994379587559</v>
       </c>
       <c r="P154" t="n">
-        <v>56.07824520070118</v>
+        <v>60.55988728791486</v>
       </c>
       <c r="Q154" t="n">
         <v>-0.3366600000000091</v>
@@ -11700,10 +11700,10 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P155" t="n">
-        <v>106.0312214023344</v>
+        <v>111.9531083031537</v>
       </c>
       <c r="Q155" t="n">
         <v>-9.155140000000017</v>
@@ -11712,10 +11712,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>62.35590221583757</v>
+        <v>83.26768256492349</v>
       </c>
       <c r="T155" t="n">
-        <v>62.35590221583757</v>
+        <v>83.26768256492349</v>
       </c>
     </row>
     <row r="156">
@@ -11774,10 +11774,10 @@
         <v>2.5</v>
       </c>
       <c r="O156" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P156" t="n">
-        <v>98.19232916025543</v>
+        <v>104.1332757968973</v>
       </c>
       <c r="Q156" t="n">
         <v>1.867959999999982</v>
@@ -11786,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>64.54597540767529</v>
+        <v>85.47575357017143</v>
       </c>
       <c r="T156" t="n">
-        <v>64.54597540767529</v>
+        <v>85.47575357017143</v>
       </c>
     </row>
     <row r="157">
@@ -11848,10 +11848,10 @@
         <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P157" t="n">
-        <v>96.62455071183963</v>
+        <v>102.5693092956461</v>
       </c>
       <c r="Q157" t="n">
         <v>1.867959999999982</v>
@@ -11860,10 +11860,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>63.46766965263304</v>
+        <v>84.3976827904639</v>
       </c>
       <c r="T157" t="n">
-        <v>63.46766965263304</v>
+        <v>84.3976827904639</v>
       </c>
     </row>
     <row r="158">
@@ -11922,10 +11922,10 @@
         <v>6</v>
       </c>
       <c r="O158" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P158" t="n">
-        <v>87.21788002134483</v>
+        <v>93.18551028813843</v>
       </c>
       <c r="Q158" t="n">
         <v>-4.745900000000006</v>
@@ -11934,10 +11934,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>52.44887394215012</v>
+        <v>73.37020316994726</v>
       </c>
       <c r="T158" t="n">
-        <v>52.44887394215012</v>
+        <v>73.37020316994726</v>
       </c>
     </row>
     <row r="159">
@@ -11996,10 +11996,10 @@
         <v>6.25</v>
       </c>
       <c r="O159" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P159" t="n">
-        <v>86.43399079713691</v>
+        <v>92.40352703751279</v>
       </c>
       <c r="Q159" t="n">
         <v>-4.745900000000006</v>
@@ -12008,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>51.90972106462898</v>
+        <v>72.83116778009349</v>
       </c>
       <c r="T159" t="n">
-        <v>51.90972106462898</v>
+        <v>72.83116778009349</v>
       </c>
     </row>
     <row r="160">
@@ -12070,10 +12070,10 @@
         <v>9.75</v>
       </c>
       <c r="O160" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P160" t="n">
-        <v>75.45954165822631</v>
+        <v>81.45576152875387</v>
       </c>
       <c r="Q160" t="n">
         <v>6.277199999999993</v>
@@ -12082,10 +12082,10 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>51.94318274638221</v>
+        <v>72.88309722592635</v>
       </c>
       <c r="T160" t="n">
-        <v>51.94318274638221</v>
+        <v>72.88309722592635</v>
       </c>
     </row>
     <row r="161">
@@ -12144,10 +12144,10 @@
         <v>11.75</v>
       </c>
       <c r="O161" t="n">
-        <v>0.0004720154776482063</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P161" t="n">
-        <v>69.18842786456311</v>
+        <v>75.19989552374878</v>
       </c>
       <c r="Q161" t="n">
         <v>-4.745900000000006</v>
@@ -12156,10 +12156,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>40.04835775916418</v>
+        <v>60.97238920331053</v>
       </c>
       <c r="T161" t="n">
-        <v>40.04835775916418</v>
+        <v>60.97238920331053</v>
       </c>
     </row>
     <row r="162">
@@ -12220,10 +12220,10 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P162" t="n">
-        <v>76.03268159593719</v>
+        <v>75.92716816494551</v>
       </c>
       <c r="Q162" t="n">
         <v>-0.3366600000000091</v>
@@ -12232,10 +12232,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>47.78842273271603</v>
+        <v>64.51308152865269</v>
       </c>
       <c r="T162" t="n">
-        <v>47.78842273271603</v>
+        <v>64.51308152865269</v>
       </c>
     </row>
     <row r="163">
@@ -12294,10 +12294,10 @@
         <v>3</v>
       </c>
       <c r="O163" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P163" t="n">
-        <v>67.92940082103821</v>
+        <v>67.84410605120064</v>
       </c>
       <c r="Q163" t="n">
         <v>-2.541280000000015</v>
@@ -12306,10 +12306,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>40.69872919903493</v>
+        <v>57.42159365543105</v>
       </c>
       <c r="T163" t="n">
-        <v>40.69872919903493</v>
+        <v>57.42159365543105</v>
       </c>
     </row>
     <row r="164">
@@ -12368,10 +12368,10 @@
         <v>6</v>
       </c>
       <c r="O164" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P164" t="n">
-        <v>59.82612004613924</v>
+        <v>59.76104393745578</v>
       </c>
       <c r="Q164" t="n">
         <v>-6.950520000000012</v>
@@ -12380,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>32.09271527194403</v>
+        <v>48.81042080145231</v>
       </c>
       <c r="T164" t="n">
-        <v>32.09271527194403</v>
+        <v>48.81042080145231</v>
       </c>
     </row>
     <row r="165">
@@ -12442,10 +12442,10 @@
         <v>6.25</v>
       </c>
       <c r="O165" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P165" t="n">
-        <v>59.15084664823099</v>
+        <v>59.08745542797704</v>
       </c>
       <c r="Q165" t="n">
         <v>-2.541280000000015</v>
@@ -12454,10 +12454,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>34.66090829707436</v>
+        <v>51.3854738552612</v>
       </c>
       <c r="T165" t="n">
-        <v>34.66090829707436</v>
+        <v>51.3854738552612</v>
       </c>
     </row>
     <row r="166">
@@ -12516,10 +12516,10 @@
         <v>7.75</v>
       </c>
       <c r="O166" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P166" t="n">
-        <v>55.0992062607815</v>
+        <v>55.0459243711046</v>
       </c>
       <c r="Q166" t="n">
         <v>-0.3366600000000091</v>
@@ -12528,10 +12528,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>33.39054212034851</v>
+        <v>50.11925738978609</v>
       </c>
       <c r="T166" t="n">
-        <v>33.39054212034851</v>
+        <v>50.11925738978609</v>
       </c>
     </row>
     <row r="167">
@@ -12590,10 +12590,10 @@
         <v>8.25</v>
       </c>
       <c r="O167" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P167" t="n">
-        <v>53.748659464965</v>
+        <v>53.69874735214712</v>
       </c>
       <c r="Q167" t="n">
         <v>-0.3366600000000091</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>32.46164659696996</v>
+        <v>49.19062357437533</v>
       </c>
       <c r="T167" t="n">
-        <v>32.46164659696996</v>
+        <v>49.19062357437533</v>
       </c>
     </row>
     <row r="168">
@@ -12664,10 +12664,10 @@
         <v>9.75</v>
       </c>
       <c r="O168" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P168" t="n">
-        <v>49.69701907751551</v>
+        <v>49.65721629527469</v>
       </c>
       <c r="Q168" t="n">
         <v>-2.541280000000015</v>
@@ -12676,10 +12676,10 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>28.15863963342451</v>
+        <v>44.88503714738596</v>
       </c>
       <c r="T168" t="n">
-        <v>28.15863963342451</v>
+        <v>44.88503714738596</v>
       </c>
     </row>
     <row r="169">
@@ -12738,10 +12738,10 @@
         <v>10.25</v>
       </c>
       <c r="O169" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P169" t="n">
-        <v>48.34647228169902</v>
+        <v>48.31003927631721</v>
       </c>
       <c r="Q169" t="n">
         <v>-2.541280000000015</v>
@@ -12750,10 +12750,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>27.22974411004597</v>
+        <v>43.9564033319752</v>
       </c>
       <c r="T169" t="n">
-        <v>27.22974411004597</v>
+        <v>43.9564033319752</v>
       </c>
     </row>
     <row r="170">
@@ -12812,10 +12812,10 @@
         <v>15.25</v>
       </c>
       <c r="O170" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P170" t="n">
-        <v>34.84100432353406</v>
+        <v>34.83826908674244</v>
       </c>
       <c r="Q170" t="n">
         <v>-2.541280000000015</v>
@@ -12824,10 +12824,10 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>17.94078887626047</v>
+        <v>34.67006517786772</v>
       </c>
       <c r="T170" t="n">
-        <v>17.94078887626047</v>
+        <v>34.67006517786772</v>
       </c>
     </row>
     <row r="171">
@@ -12886,10 +12886,10 @@
         <v>21.25</v>
       </c>
       <c r="O171" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P171" t="n">
-        <v>20.3306949771901</v>
+        <v>20.36437866544448</v>
       </c>
       <c r="Q171" t="n">
         <v>-2.541280000000015</v>
@@ -12956,10 +12956,10 @@
         <v>37.25</v>
       </c>
       <c r="O172" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P172" t="n">
-        <v>-1.278053755873842</v>
+        <v>-1.190453637875166</v>
       </c>
       <c r="Q172" t="n">
         <v>-2.541280000000015</v>
@@ -13026,10 +13026,10 @@
         <v>41.25</v>
       </c>
       <c r="O173" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P173" t="n">
-        <v>-6.680240939139836</v>
+        <v>-6.579161713705076</v>
       </c>
       <c r="Q173" t="n">
         <v>-9.155140000000017</v>
@@ -13096,10 +13096,10 @@
         <v>48.75</v>
       </c>
       <c r="O174" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P174" t="n">
-        <v>-16.80934190776357</v>
+        <v>-16.68298935588616</v>
       </c>
       <c r="Q174" t="n">
         <v>-9.155140000000017</v>
@@ -13168,10 +13168,10 @@
         <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P175" t="n">
-        <v>104.2123860073827</v>
+        <v>114.832994288998</v>
       </c>
       <c r="Q175" t="n">
         <v>-2.541280000000015</v>
@@ -13180,10 +13180,10 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>65.65388263674299</v>
+        <v>89.81189571086739</v>
       </c>
       <c r="T175" t="n">
-        <v>65.65388263674299</v>
+        <v>89.81189571086739</v>
       </c>
     </row>
     <row r="176">
@@ -13242,10 +13242,10 @@
         <v>0.25</v>
       </c>
       <c r="O176" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P176" t="n">
-        <v>103.5427081261142</v>
+        <v>114.1650145667524</v>
       </c>
       <c r="Q176" t="n">
         <v>-9.155140000000017</v>
@@ -13254,10 +13254,10 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>60.6443222474059</v>
+        <v>84.79239010074988</v>
       </c>
       <c r="T176" t="n">
-        <v>60.6443222474059</v>
+        <v>84.79239010074988</v>
       </c>
     </row>
     <row r="177">
@@ -13316,10 +13316,10 @@
         <v>7.75</v>
       </c>
       <c r="O177" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P177" t="n">
-        <v>83.4523716880576</v>
+        <v>94.12562289938583</v>
       </c>
       <c r="Q177" t="n">
         <v>-0.3366600000000091</v>
@@ -13328,10 +13328,10 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>52.89162754781469</v>
+        <v>77.05760998839517</v>
       </c>
       <c r="T177" t="n">
-        <v>52.89162754781469</v>
+        <v>77.05760998839517</v>
       </c>
     </row>
     <row r="178">
@@ -13390,10 +13390,10 @@
         <v>9.75</v>
       </c>
       <c r="O178" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P178" t="n">
-        <v>78.09494863790917</v>
+        <v>88.78178512142141</v>
       </c>
       <c r="Q178" t="n">
         <v>-15.76900000000001</v>
@@ -13402,10 +13402,10 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>38.59259112108464</v>
+        <v>62.73620978032638</v>
       </c>
       <c r="T178" t="n">
-        <v>38.59259112108464</v>
+        <v>62.73620978032638</v>
       </c>
     </row>
     <row r="179">
@@ -13464,10 +13464,10 @@
         <v>16.25</v>
       </c>
       <c r="O179" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P179" t="n">
-        <v>60.68332372492677</v>
+        <v>71.41431234303701</v>
       </c>
       <c r="Q179" t="n">
         <v>-13.56438000000001</v>
@@ -13476,10 +13476,10 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>28.13333207769472</v>
+        <v>52.28417739708468</v>
       </c>
       <c r="T179" t="n">
-        <v>28.13333207769472</v>
+        <v>52.28417739708468</v>
       </c>
     </row>
     <row r="180">
@@ -13538,10 +13538,10 @@
         <v>17.25</v>
       </c>
       <c r="O180" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P180" t="n">
-        <v>58.00461219985256</v>
+        <v>68.74239345405479</v>
       </c>
       <c r="Q180" t="n">
         <v>-6.950520000000012</v>
@@ -13550,10 +13550,10 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>30.83989642149341</v>
+        <v>55.00142966797164</v>
       </c>
       <c r="T180" t="n">
-        <v>30.83989642149341</v>
+        <v>55.00142966797164</v>
       </c>
     </row>
     <row r="181">
@@ -13612,10 +13612,10 @@
         <v>18.75</v>
       </c>
       <c r="O181" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P181" t="n">
-        <v>53.98654491224124</v>
+        <v>64.73451512058148</v>
       </c>
       <c r="Q181" t="n">
         <v>-2.541280000000015</v>
@@ -13624,10 +13624,10 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>31.10894195366692</v>
+        <v>55.27809562240925</v>
       </c>
       <c r="T181" t="n">
-        <v>31.10894195366692</v>
+        <v>55.27809562240925</v>
       </c>
     </row>
     <row r="182">
@@ -13686,10 +13686,10 @@
         <v>21.75</v>
       </c>
       <c r="O182" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P182" t="n">
-        <v>48.30992656075703</v>
+        <v>59.07964209929761</v>
       </c>
       <c r="Q182" t="n">
         <v>-9.155140000000017</v>
@@ -13756,10 +13756,10 @@
         <v>24.75</v>
       </c>
       <c r="O183" t="n">
-        <v>0.00145999663943547</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P183" t="n">
-        <v>44.29185927314572</v>
+        <v>55.07176376582429</v>
       </c>
       <c r="Q183" t="n">
         <v>-13.56438000000001</v>
@@ -13828,10 +13828,10 @@
         <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P184" t="n">
-        <v>92.57974732937191</v>
+        <v>101.4981810837327</v>
       </c>
       <c r="Q184" t="n">
         <v>-0.3366600000000091</v>
@@ -13840,10 +13840,10 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>59.16936512764104</v>
+        <v>82.13964949747609</v>
       </c>
       <c r="T184" t="n">
-        <v>59.16936512764104</v>
+        <v>82.13964949747609</v>
       </c>
     </row>
     <row r="185">
@@ -13902,10 +13902,10 @@
         <v>2</v>
       </c>
       <c r="O185" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P185" t="n">
-        <v>86.95865861279279</v>
+        <v>95.89075966384104</v>
       </c>
       <c r="Q185" t="n">
         <v>-2.541280000000015</v>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="S185" t="n">
-        <v>53.78690387815869</v>
+        <v>76.75466613759457</v>
       </c>
       <c r="T185" t="n">
-        <v>53.78690387815869</v>
+        <v>76.75466613759457</v>
       </c>
     </row>
     <row r="186">
@@ -13976,10 +13976,10 @@
         <v>4</v>
       </c>
       <c r="O186" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P186" t="n">
-        <v>81.33756989621367</v>
+        <v>90.28333824394939</v>
       </c>
       <c r="Q186" t="n">
         <v>-6.950520000000012</v>
@@ -13988,10 +13988,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>46.88812223526654</v>
+        <v>69.84999779695595</v>
       </c>
       <c r="T186" t="n">
-        <v>46.88812223526654</v>
+        <v>69.84999779695595</v>
       </c>
     </row>
     <row r="187">
@@ -14050,10 +14050,10 @@
         <v>5</v>
       </c>
       <c r="O187" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P187" t="n">
-        <v>78.5270255379241</v>
+        <v>87.47962753400355</v>
       </c>
       <c r="Q187" t="n">
         <v>-6.950520000000012</v>
@@ -14062,10 +14062,10 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>44.95505180723027</v>
+        <v>67.91734860739376</v>
       </c>
       <c r="T187" t="n">
-        <v>44.95505180723027</v>
+        <v>67.91734860739376</v>
       </c>
     </row>
     <row r="188">
@@ -14124,10 +14124,10 @@
         <v>5.5</v>
       </c>
       <c r="O188" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P188" t="n">
-        <v>77.12175335877932</v>
+        <v>86.07777217903065</v>
       </c>
       <c r="Q188" t="n">
         <v>-2.541280000000015</v>
@@ -14136,10 +14136,10 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>47.02115738003173</v>
+        <v>69.99039397412693</v>
       </c>
       <c r="T188" t="n">
-        <v>47.02115738003173</v>
+        <v>69.99039397412693</v>
       </c>
     </row>
     <row r="189">
@@ -14198,10 +14198,10 @@
         <v>6.5</v>
       </c>
       <c r="O189" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P189" t="n">
-        <v>74.31120900048975</v>
+        <v>83.27406146908483</v>
       </c>
       <c r="Q189" t="n">
         <v>-2.541280000000015</v>
@@ -14210,10 +14210,10 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>45.08808695199546</v>
+        <v>68.05774478456475</v>
       </c>
       <c r="T189" t="n">
-        <v>45.08808695199546</v>
+        <v>68.05774478456475</v>
       </c>
     </row>
     <row r="190">
@@ -14272,10 +14272,10 @@
         <v>15.5</v>
       </c>
       <c r="O190" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P190" t="n">
-        <v>49.0163097758837</v>
+        <v>58.04066507957239</v>
       </c>
       <c r="Q190" t="n">
         <v>-2.541280000000015</v>
@@ -14284,10 +14284,10 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>27.690453099669</v>
+        <v>50.66390207850508</v>
       </c>
       <c r="T190" t="n">
-        <v>27.690453099669</v>
+        <v>50.66390207850508</v>
       </c>
     </row>
     <row r="191">
@@ -14346,10 +14346,10 @@
         <v>17</v>
       </c>
       <c r="O191" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P191" t="n">
-        <v>44.80049323844936</v>
+        <v>53.83509901465366</v>
       </c>
       <c r="Q191" t="n">
         <v>-9.155140000000017</v>
@@ -14358,10 +14358,10 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>20.24188627738519</v>
+        <v>43.2058733518904</v>
       </c>
       <c r="T191" t="n">
-        <v>20.24188627738519</v>
+        <v>43.2058733518904</v>
       </c>
     </row>
     <row r="192">
@@ -14420,10 +14420,10 @@
         <v>21.5</v>
       </c>
       <c r="O192" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P192" t="n">
-        <v>34.27972260875253</v>
+        <v>43.34527070171565</v>
       </c>
       <c r="Q192" t="n">
         <v>-2.541280000000015</v>
@@ -14490,10 +14490,10 @@
         <v>23.5</v>
       </c>
       <c r="O193" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P193" t="n">
-        <v>31.46917825046297</v>
+        <v>40.54155999176982</v>
       </c>
       <c r="Q193" t="n">
         <v>-2.541280000000015</v>
@@ -14560,10 +14560,10 @@
         <v>30.5</v>
       </c>
       <c r="O194" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P194" t="n">
-        <v>21.6322729964495</v>
+        <v>30.72857250695944</v>
       </c>
       <c r="Q194" t="n">
         <v>-2.541280000000015</v>
@@ -14630,10 +14630,10 @@
         <v>30.75</v>
       </c>
       <c r="O195" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P195" t="n">
-        <v>21.2809549516633</v>
+        <v>30.3781086682162</v>
       </c>
       <c r="Q195" t="n">
         <v>-2.541280000000015</v>
@@ -14700,10 +14700,10 @@
         <v>38.75</v>
       </c>
       <c r="O196" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P196" t="n">
-        <v>10.03877751850506</v>
+        <v>19.1632658284329</v>
       </c>
       <c r="Q196" t="n">
         <v>-9.155140000000017</v>
@@ -14772,10 +14772,10 @@
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P197" t="n">
-        <v>92.0213361353249</v>
+        <v>100.937004690931</v>
       </c>
       <c r="Q197" t="n">
         <v>-0.3366600000000091</v>
@@ -14784,10 +14784,10 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>58.7852942757746</v>
+        <v>81.75282032251798</v>
       </c>
       <c r="T197" t="n">
-        <v>58.7852942757746</v>
+        <v>81.75282032251798</v>
       </c>
     </row>
     <row r="198">
@@ -14846,10 +14846,10 @@
         <v>0.05</v>
       </c>
       <c r="O198" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P198" t="n">
-        <v>91.88087401397924</v>
+        <v>100.7968840937246</v>
       </c>
       <c r="Q198" t="n">
         <v>-2.541280000000015</v>
@@ -14858,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>57.17236513387388</v>
+        <v>80.1365476454371</v>
       </c>
       <c r="T198" t="n">
-        <v>57.17236513387388</v>
+        <v>80.1365476454371</v>
       </c>
     </row>
     <row r="199">
@@ -14920,10 +14920,10 @@
         <v>7.05</v>
       </c>
       <c r="O199" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P199" t="n">
-        <v>72.21617702558542</v>
+        <v>81.18000048483096</v>
       </c>
       <c r="Q199" t="n">
         <v>-2.541280000000015</v>
@@ -14932,10 +14932,10 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>43.64714034514573</v>
+        <v>66.61427016011243</v>
       </c>
       <c r="T199" t="n">
-        <v>43.64714034514573</v>
+        <v>66.61427016011243</v>
       </c>
     </row>
     <row r="200">
@@ -14994,10 +14994,10 @@
         <v>7.3</v>
       </c>
       <c r="O200" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P200" t="n">
-        <v>71.51386641885708</v>
+        <v>80.47939749879903</v>
       </c>
       <c r="Q200" t="n">
         <v>-0.3366600000000091</v>
@@ -15006,10 +15006,10 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>44.68041699610097</v>
+        <v>67.65101665925081</v>
       </c>
       <c r="T200" t="n">
-        <v>44.68041699610097</v>
+        <v>67.65101665925081</v>
       </c>
     </row>
     <row r="201">
@@ -15068,10 +15068,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O201" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P201" t="n">
-        <v>67.30000277848697</v>
+        <v>76.27577958260753</v>
       </c>
       <c r="Q201" t="n">
         <v>-0.3366600000000091</v>
@@ -15080,10 +15080,10 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>41.7821545413735</v>
+        <v>64.75338576953837</v>
       </c>
       <c r="T201" t="n">
-        <v>41.7821545413735</v>
+        <v>64.75338576953837</v>
       </c>
     </row>
     <row r="202">
@@ -15142,10 +15142,10 @@
         <v>10.3</v>
       </c>
       <c r="O202" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P202" t="n">
-        <v>63.08613913811688</v>
+        <v>72.07216166641602</v>
       </c>
       <c r="Q202" t="n">
         <v>-2.541280000000015</v>
@@ -15154,10 +15154,10 @@
         <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>37.36757169323624</v>
+        <v>60.33606989906881</v>
       </c>
       <c r="T202" t="n">
-        <v>37.36757169323624</v>
+        <v>60.33606989906881</v>
       </c>
     </row>
     <row r="203">
@@ -15216,10 +15216,10 @@
         <v>10.8</v>
       </c>
       <c r="O203" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P203" t="n">
-        <v>61.68151792466017</v>
+        <v>70.67095569435219</v>
       </c>
       <c r="Q203" t="n">
         <v>-2.541280000000015</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>36.40148420832708</v>
+        <v>59.37019293583133</v>
       </c>
       <c r="T203" t="n">
-        <v>36.40148420832708</v>
+        <v>59.37019293583133</v>
       </c>
     </row>
     <row r="204">
@@ -15290,10 +15290,10 @@
         <v>11.55</v>
       </c>
       <c r="O204" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P204" t="n">
-        <v>59.57458610447512</v>
+        <v>68.56914673625644</v>
       </c>
       <c r="Q204" t="n">
         <v>-9.155140000000017</v>
@@ -15302,10 +15302,10 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>30.40339180073395</v>
+        <v>53.36232254870373</v>
       </c>
       <c r="T204" t="n">
-        <v>30.40339180073395</v>
+        <v>53.36232254870373</v>
       </c>
     </row>
     <row r="205">
@@ -15364,10 +15364,10 @@
         <v>12.55</v>
       </c>
       <c r="O205" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P205" t="n">
-        <v>56.76534367756172</v>
+        <v>65.76673479212877</v>
       </c>
       <c r="Q205" t="n">
         <v>-11.35976000000001</v>
@@ -15376,10 +15376,10 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>26.95489643750584</v>
+        <v>49.91088364147165</v>
       </c>
       <c r="T205" t="n">
-        <v>26.95489643750584</v>
+        <v>49.91088364147165</v>
       </c>
     </row>
     <row r="206">
@@ -15438,10 +15438,10 @@
         <v>14.05</v>
       </c>
       <c r="O206" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P206" t="n">
-        <v>52.55148003719162</v>
+        <v>61.56311687593727</v>
       </c>
       <c r="Q206" t="n">
         <v>-2.541280000000015</v>
@@ -15450,10 +15450,10 @@
         <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>30.12191555641759</v>
+        <v>53.09199267478774</v>
       </c>
       <c r="T206" t="n">
-        <v>30.12191555641759</v>
+        <v>53.09199267478774</v>
       </c>
     </row>
     <row r="207">
@@ -15512,10 +15512,10 @@
         <v>15.55</v>
       </c>
       <c r="O207" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P207" t="n">
-        <v>48.33761639682152</v>
+        <v>57.35949895974576</v>
       </c>
       <c r="Q207" t="n">
         <v>-0.3366600000000091</v>
@@ -15524,10 +15524,10 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>28.73997349509994</v>
+        <v>51.71404676583244</v>
       </c>
       <c r="T207" t="n">
-        <v>28.73997349509994</v>
+        <v>51.71404676583244</v>
       </c>
     </row>
     <row r="208">
@@ -15586,10 +15586,10 @@
         <v>21.55</v>
       </c>
       <c r="O208" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P208" t="n">
-        <v>33.67808673491079</v>
+        <v>42.74097224326133</v>
       </c>
       <c r="Q208" t="n">
         <v>-9.155140000000017</v>
@@ -15656,10 +15656,10 @@
         <v>23.55</v>
       </c>
       <c r="O209" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P209" t="n">
-        <v>30.86884430799739</v>
+        <v>39.93856029913366</v>
       </c>
       <c r="Q209" t="n">
         <v>-4.745900000000006</v>
@@ -15726,10 +15726,10 @@
         <v>39.55</v>
       </c>
       <c r="O210" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P210" t="n">
-        <v>8.394904892690192</v>
+        <v>17.51926474611231</v>
       </c>
       <c r="Q210" t="n">
         <v>-2.541280000000015</v>
@@ -15796,10 +15796,10 @@
         <v>44.55</v>
       </c>
       <c r="O211" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P211" t="n">
-        <v>1.371798825406685</v>
+        <v>10.51323488579314</v>
       </c>
       <c r="Q211" t="n">
         <v>-2.541280000000015</v>
@@ -15868,10 +15868,10 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P212" t="n">
-        <v>102.7231611127946</v>
+        <v>111.1294387770813</v>
       </c>
       <c r="Q212" t="n">
         <v>4.072579999999988</v>
@@ -15880,10 +15880,10 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>69.17856658187628</v>
+        <v>91.81802194576062</v>
       </c>
       <c r="T212" t="n">
-        <v>69.17856658187628</v>
+        <v>91.81802194576062</v>
       </c>
     </row>
     <row r="213">
@@ -15942,10 +15942,10 @@
         <v>5.5</v>
       </c>
       <c r="O213" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P213" t="n">
-        <v>91.61517883603042</v>
+        <v>100.0556751869729</v>
       </c>
       <c r="Q213" t="n">
         <v>-2.541280000000015</v>
@@ -15954,10 +15954,10 @@
         <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>56.98962206851367</v>
+        <v>79.62561875828465</v>
       </c>
       <c r="T213" t="n">
-        <v>56.98962206851367</v>
+        <v>79.62561875828465</v>
       </c>
     </row>
     <row r="214">
@@ -16016,10 +16016,10 @@
         <v>6</v>
       </c>
       <c r="O214" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P214" t="n">
-        <v>90.60536226541551</v>
+        <v>99.04896940605396</v>
       </c>
       <c r="Q214" t="n">
         <v>-2.541280000000015</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>56.29507812913793</v>
+        <v>78.93167800872058</v>
       </c>
       <c r="T214" t="n">
-        <v>56.29507812913793</v>
+        <v>78.93167800872058</v>
       </c>
     </row>
     <row r="215">
@@ -16090,10 +16090,10 @@
         <v>13</v>
       </c>
       <c r="O215" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P215" t="n">
-        <v>76.4679302768066</v>
+        <v>84.95508847318871</v>
       </c>
       <c r="Q215" t="n">
         <v>-0.3366600000000091</v>
@@ -16102,10 +16102,10 @@
         <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>48.0877833712873</v>
+        <v>70.73619249558098</v>
       </c>
       <c r="T215" t="n">
-        <v>48.0877833712873</v>
+        <v>70.73619249558098</v>
       </c>
     </row>
     <row r="216">
@@ -16164,10 +16164,10 @@
         <v>13.5</v>
       </c>
       <c r="O216" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P216" t="n">
-        <v>75.45811370619168</v>
+        <v>83.94838269226976</v>
       </c>
       <c r="Q216" t="n">
         <v>4.072579999999988</v>
@@ -16176,10 +16176,10 @@
         <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>50.42588021873116</v>
+        <v>73.0816217075312</v>
       </c>
       <c r="T216" t="n">
-        <v>50.42588021873116</v>
+        <v>73.0816217075312</v>
       </c>
     </row>
     <row r="217">
@@ -16238,10 +16238,10 @@
         <v>15</v>
       </c>
       <c r="O217" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P217" t="n">
-        <v>72.42866399434691</v>
+        <v>80.92826534951291</v>
       </c>
       <c r="Q217" t="n">
         <v>-2.541280000000015</v>
@@ -16250,10 +16250,10 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>43.79328722037451</v>
+        <v>66.44074451656763</v>
       </c>
       <c r="T217" t="n">
-        <v>43.79328722037451</v>
+        <v>66.44074451656763</v>
       </c>
     </row>
     <row r="218">
@@ -16312,10 +16312,10 @@
         <v>20</v>
       </c>
       <c r="O218" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P218" t="n">
-        <v>62.3428974982337</v>
+        <v>70.87850488159881</v>
       </c>
       <c r="Q218" t="n">
         <v>-4.745900000000006</v>
@@ -16324,10 +16324,10 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>35.34005551289436</v>
+        <v>57.99357541460331</v>
       </c>
       <c r="T218" t="n">
-        <v>35.34005551289436</v>
+        <v>57.99357541460331</v>
       </c>
     </row>
     <row r="219">
@@ -16386,10 +16386,10 @@
         <v>22</v>
       </c>
       <c r="O219" t="n">
-        <v>0.001534834443800835</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P219" t="n">
-        <v>60.32326435700385</v>
+        <v>68.86509331976092</v>
       </c>
       <c r="Q219" t="n">
         <v>1.867959999999982</v>
@@ -16458,10 +16458,10 @@
         <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P220" t="n">
-        <v>120.3616702580797</v>
+        <v>140.4483692721155</v>
       </c>
       <c r="Q220" t="n">
         <v>6.277199999999993</v>
@@ -16470,10 +16470,10 @@
         <v>0</v>
       </c>
       <c r="S220" t="n">
-        <v>82.82651561257558</v>
+        <v>113.5477831869008</v>
       </c>
       <c r="T220" t="n">
-        <v>82.82651561257558</v>
+        <v>113.5477831869008</v>
       </c>
     </row>
     <row r="221">
@@ -16532,10 +16532,10 @@
         <v>3.5</v>
       </c>
       <c r="O221" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P221" t="n">
-        <v>110.4476699855551</v>
+        <v>130.559105623899</v>
       </c>
       <c r="Q221" t="n">
         <v>-1.438970000000012</v>
@@ -16544,10 +16544,10 @@
         <v>0</v>
       </c>
       <c r="S221" t="n">
-        <v>70.70062238675146</v>
+        <v>101.4120350330644</v>
       </c>
       <c r="T221" t="n">
-        <v>70.70062238675146</v>
+        <v>101.4120350330644</v>
       </c>
     </row>
     <row r="222">
@@ -16606,10 +16606,10 @@
         <v>7.5</v>
       </c>
       <c r="O222" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P222" t="n">
-        <v>99.11738395981267</v>
+        <v>119.2570900259373</v>
       </c>
       <c r="Q222" t="n">
         <v>-1.438970000000012</v>
@@ -16618,10 +16618,10 @@
         <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>62.90774027373457</v>
+        <v>93.62134849456561</v>
       </c>
       <c r="T222" t="n">
-        <v>62.90774027373457</v>
+        <v>93.62134849456561</v>
       </c>
     </row>
     <row r="223">
@@ -16680,10 +16680,10 @@
         <v>16</v>
       </c>
       <c r="O223" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P223" t="n">
-        <v>75.04052615511004</v>
+        <v>95.24030688026872</v>
       </c>
       <c r="Q223" t="n">
         <v>-1.438970000000012</v>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>46.34786578357365</v>
+        <v>77.06613960025567</v>
       </c>
       <c r="T223" t="n">
-        <v>46.34786578357365</v>
+        <v>77.06613960025567</v>
       </c>
     </row>
     <row r="224">
@@ -16754,10 +16754,10 @@
         <v>20.5</v>
       </c>
       <c r="O224" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P224" t="n">
-        <v>63.00037787723296</v>
+        <v>83.24058002538001</v>
       </c>
       <c r="Q224" t="n">
         <v>-1.438970000000012</v>
@@ -16824,10 +16824,10 @@
         <v>28</v>
       </c>
       <c r="O225" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P225" t="n">
-        <v>52.37823472809944</v>
+        <v>72.64494040229091</v>
       </c>
       <c r="Q225" t="n">
         <v>6.277199999999993</v>
@@ -16894,10 +16894,10 @@
         <v>34</v>
       </c>
       <c r="O226" t="n">
-        <v>-0.0001517504078770264</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P226" t="n">
-        <v>43.88052020879263</v>
+        <v>64.16842870381964</v>
       </c>
       <c r="Q226" t="n">
         <v>6.277199999999993</v>
@@ -16966,10 +16966,10 @@
         <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P227" t="n">
-        <v>84.93609474236163</v>
+        <v>84.89432820506531</v>
       </c>
       <c r="Q227" t="n">
         <v>-0.3366600000000091</v>
@@ -16978,10 +16978,10 @@
         <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>53.91212066019392</v>
+        <v>70.69430932891558</v>
       </c>
       <c r="T227" t="n">
-        <v>53.91212066019392</v>
+        <v>70.69430932891558</v>
       </c>
     </row>
     <row r="228">
@@ -17040,10 +17040,10 @@
         <v>1.5</v>
       </c>
       <c r="O228" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P228" t="n">
-        <v>80.32753011506682</v>
+        <v>80.29696899067901</v>
       </c>
       <c r="Q228" t="n">
         <v>-2.541280000000015</v>
@@ -17052,10 +17052,10 @@
         <v>0</v>
       </c>
       <c r="S228" t="n">
-        <v>49.2260655602523</v>
+        <v>66.00558036359499</v>
       </c>
       <c r="T228" t="n">
-        <v>49.2260655602523</v>
+        <v>66.00558036359499</v>
       </c>
     </row>
     <row r="229">
@@ -17114,10 +17114,10 @@
         <v>2.5</v>
       </c>
       <c r="O229" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P229" t="n">
-        <v>77.25515369687028</v>
+        <v>77.2320628477548</v>
       </c>
       <c r="Q229" t="n">
         <v>-4.745900000000006</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>45.5965886958213</v>
+        <v>62.3731993931289</v>
       </c>
       <c r="T229" t="n">
-        <v>45.5965886958213</v>
+        <v>62.3731993931289</v>
       </c>
     </row>
     <row r="230">
@@ -17188,10 +17188,10 @@
         <v>6.5</v>
       </c>
       <c r="O230" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P230" t="n">
-        <v>64.96564802408413</v>
+        <v>64.97243827605801</v>
       </c>
       <c r="Q230" t="n">
         <v>4.072579999999988</v>
@@ -17200,10 +17200,10 @@
         <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>43.20924438537568</v>
+        <v>60.00115535732157</v>
       </c>
       <c r="T230" t="n">
-        <v>43.20924438537568</v>
+        <v>60.00115535732157</v>
       </c>
     </row>
     <row r="231">
@@ -17262,10 +17262,10 @@
         <v>9</v>
       </c>
       <c r="O231" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P231" t="n">
-        <v>57.28470697859278</v>
+        <v>57.31017291874753</v>
       </c>
       <c r="Q231" t="n">
         <v>1.867959999999982</v>
@@ -17274,10 +17274,10 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>36.41003281441285</v>
+        <v>53.19973040229203</v>
       </c>
       <c r="T231" t="n">
-        <v>36.41003281441285</v>
+        <v>53.19973040229203</v>
       </c>
     </row>
     <row r="232">
@@ -17336,10 +17336,10 @@
         <v>16.5</v>
       </c>
       <c r="O232" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P232" t="n">
-        <v>34.24188384211874</v>
+        <v>34.32337684681603</v>
       </c>
       <c r="Q232" t="n">
         <v>4.072579999999988</v>
@@ -17348,10 +17348,10 @@
         <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>22.0776796751636</v>
+        <v>38.87419546023195</v>
       </c>
       <c r="T232" t="n">
-        <v>22.0776796751636</v>
+        <v>38.87419546023195</v>
       </c>
     </row>
     <row r="233">
@@ -17410,10 +17410,10 @@
         <v>19</v>
       </c>
       <c r="O233" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P233" t="n">
-        <v>26.56094279662739</v>
+        <v>26.66111148950554</v>
       </c>
       <c r="Q233" t="n">
         <v>-6.950520000000012</v>
@@ -17422,10 +17422,10 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>9.213186530561574</v>
+        <v>25.99403058217388</v>
       </c>
       <c r="T233" t="n">
-        <v>9.213186530561574</v>
+        <v>25.99403058217388</v>
       </c>
     </row>
     <row r="234">
@@ -17484,10 +17484,10 @@
         <v>24</v>
       </c>
       <c r="O234" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P234" t="n">
-        <v>17.35299134704272</v>
+        <v>17.47579193194417</v>
       </c>
       <c r="Q234" t="n">
         <v>-4.745900000000006</v>
@@ -17554,10 +17554,10 @@
         <v>25.5</v>
       </c>
       <c r="O235" t="n">
-        <v>0.0007468001764514667</v>
+        <v>0.0007666524497767008</v>
       </c>
       <c r="P235" t="n">
-        <v>15.04870903339531</v>
+        <v>15.17711232475102</v>
       </c>
       <c r="Q235" t="n">
         <v>-0.3366600000000091</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P236" t="n">
-        <v>96.14157481987853</v>
+        <v>102.5168091213787</v>
       </c>
       <c r="Q236" t="n">
         <v>-9.155140000000017</v>
@@ -17638,10 +17638,10 @@
         <v>0</v>
       </c>
       <c r="S236" t="n">
-        <v>55.55388064450398</v>
+        <v>76.7630685541306</v>
       </c>
       <c r="T236" t="n">
-        <v>55.55388064450398</v>
+        <v>76.7630685541306</v>
       </c>
     </row>
     <row r="237">
@@ -17700,10 +17700,10 @@
         <v>0.25</v>
       </c>
       <c r="O237" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P237" t="n">
-        <v>95.47857701722612</v>
+        <v>101.8554925385072</v>
       </c>
       <c r="Q237" t="n">
         <v>-2.541280000000015</v>
@@ -17712,10 +17712,10 @@
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>59.64683712145221</v>
+        <v>80.86626585267405</v>
       </c>
       <c r="T237" t="n">
-        <v>59.64683712145221</v>
+        <v>80.86626585267405</v>
       </c>
     </row>
     <row r="238">
@@ -17774,10 +17774,10 @@
         <v>0.5</v>
       </c>
       <c r="O238" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P238" t="n">
-        <v>94.81557921457372</v>
+        <v>101.1941759556357</v>
       </c>
       <c r="Q238" t="n">
         <v>-0.3366600000000091</v>
@@ -17786,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>60.70715281158085</v>
+        <v>81.93009318970323</v>
       </c>
       <c r="T238" t="n">
-        <v>60.70715281158085</v>
+        <v>81.93009318970323</v>
       </c>
     </row>
     <row r="239">
@@ -17848,10 +17848,10 @@
         <v>6</v>
       </c>
       <c r="O239" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P239" t="n">
-        <v>80.22962755622073</v>
+        <v>86.64521113246195</v>
       </c>
       <c r="Q239" t="n">
         <v>-15.76900000000001</v>
@@ -17860,10 +17860,10 @@
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>40.06080658552649</v>
+        <v>61.26343016238858</v>
       </c>
       <c r="T239" t="n">
-        <v>40.06080658552649</v>
+        <v>61.26343016238858</v>
       </c>
     </row>
     <row r="240">
@@ -17922,10 +17922,10 @@
         <v>9.5</v>
       </c>
       <c r="O240" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P240" t="n">
-        <v>70.94765831908703</v>
+        <v>77.38677897226049</v>
       </c>
       <c r="Q240" t="n">
         <v>-9.155140000000017</v>
@@ -17934,10 +17934,10 @@
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>38.22570191981951</v>
+        <v>59.44047809246876</v>
       </c>
       <c r="T240" t="n">
-        <v>38.22570191981951</v>
+        <v>59.44047809246876</v>
       </c>
     </row>
     <row r="241">
@@ -17996,10 +17996,10 @@
         <v>10.25</v>
       </c>
       <c r="O241" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P241" t="n">
-        <v>68.9586649111298</v>
+        <v>75.40282922364588</v>
       </c>
       <c r="Q241" t="n">
         <v>-22.38286000000001</v>
@@ -18008,10 +18008,10 @@
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>27.75976544951719</v>
+        <v>48.95479527674215</v>
       </c>
       <c r="T241" t="n">
-        <v>27.75976544951719</v>
+        <v>48.95479527674215</v>
       </c>
     </row>
     <row r="242">
@@ -18070,10 +18070,10 @@
         <v>12.75</v>
       </c>
       <c r="O242" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P242" t="n">
-        <v>62.32868688460571</v>
+        <v>68.78966339493056</v>
       </c>
       <c r="Q242" t="n">
         <v>-9.155140000000017</v>
@@ -18082,10 +18082,10 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>32.29764077716428</v>
+        <v>53.5143287240055</v>
       </c>
       <c r="T242" t="n">
-        <v>32.29764077716428</v>
+        <v>53.5143287240055</v>
       </c>
     </row>
     <row r="243">
@@ -18144,10 +18144,10 @@
         <v>23.75</v>
       </c>
       <c r="O243" t="n">
-        <v>0.001669668887601671</v>
+        <v>0.002147765216413183</v>
       </c>
       <c r="P243" t="n">
-        <v>38.146978876651</v>
+        <v>44.67433376417927</v>
       </c>
       <c r="Q243" t="n">
         <v>-13.56438000000001</v>
@@ -18216,10 +18216,10 @@
         <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P244" t="n">
-        <v>84.00713900417944</v>
+        <v>83.8656507321738</v>
       </c>
       <c r="Q244" t="n">
         <v>-6.950520000000012</v>
@@ -18228,10 +18228,10 @@
         <v>0</v>
       </c>
       <c r="S244" t="n">
-        <v>48.72423098871399</v>
+        <v>65.42616814702174</v>
       </c>
       <c r="T244" t="n">
-        <v>48.72423098871399</v>
+        <v>65.42616814702174</v>
       </c>
     </row>
     <row r="245">
@@ -18290,10 +18290,10 @@
         <v>2.5</v>
       </c>
       <c r="O245" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P245" t="n">
-        <v>77.98551064025365</v>
+        <v>77.86053997168524</v>
       </c>
       <c r="Q245" t="n">
         <v>-6.950520000000012</v>
@@ -18302,10 +18302,10 @@
         <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>44.58260209586372</v>
+        <v>61.28673521504366</v>
       </c>
       <c r="T245" t="n">
-        <v>44.58260209586372</v>
+        <v>61.28673521504366</v>
       </c>
     </row>
     <row r="246">
@@ -18364,10 +18364,10 @@
         <v>3.5</v>
       </c>
       <c r="O246" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P246" t="n">
-        <v>75.57685929468335</v>
+        <v>75.45849566748981</v>
       </c>
       <c r="Q246" t="n">
         <v>-0.3366600000000091</v>
@@ -18376,10 +18376,10 @@
         <v>0</v>
       </c>
       <c r="S246" t="n">
-        <v>47.47491171895302</v>
+        <v>64.19001698452382</v>
       </c>
       <c r="T246" t="n">
-        <v>47.47491171895302</v>
+        <v>64.19001698452382</v>
       </c>
     </row>
     <row r="247">
@@ -18438,10 +18438,10 @@
         <v>6.5</v>
       </c>
       <c r="O247" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P247" t="n">
-        <v>68.35090525797241</v>
+        <v>68.25236275490354</v>
       </c>
       <c r="Q247" t="n">
         <v>-6.950520000000012</v>
@@ -18450,10 +18450,10 @@
         <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>37.95599586730329</v>
+        <v>54.66364252387875</v>
       </c>
       <c r="T247" t="n">
-        <v>37.95599586730329</v>
+        <v>54.66364252387875</v>
       </c>
     </row>
     <row r="248">
@@ -18512,10 +18512,10 @@
         <v>14.5</v>
       </c>
       <c r="O248" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P248" t="n">
-        <v>49.08169449340991</v>
+        <v>49.03600832134013</v>
       </c>
       <c r="Q248" t="n">
         <v>-0.3366600000000091</v>
@@ -18524,10 +18524,10 @@
         <v>0</v>
       </c>
       <c r="S248" t="n">
-        <v>29.25174459041183</v>
+        <v>45.9765120838203</v>
       </c>
       <c r="T248" t="n">
-        <v>29.25174459041183</v>
+        <v>45.9765120838203</v>
       </c>
     </row>
     <row r="249">
@@ -18586,10 +18586,10 @@
         <v>26.5</v>
       </c>
       <c r="O249" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P249" t="n">
-        <v>28.0156369891222</v>
+        <v>28.02805050117461</v>
       </c>
       <c r="Q249" t="n">
         <v>-0.3366600000000091</v>
@@ -18658,10 +18658,10 @@
         <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P250" t="n">
-        <v>106.4703290559639</v>
+        <v>112.7158455835573</v>
       </c>
       <c r="Q250" t="n">
         <v>-0.3366600000000091</v>
@@ -18670,10 +18670,10 @@
         <v>0</v>
       </c>
       <c r="S250" t="n">
-        <v>68.72319859933094</v>
+        <v>89.87219127771758</v>
       </c>
       <c r="T250" t="n">
-        <v>68.72319859933094</v>
+        <v>89.87219127771758</v>
       </c>
     </row>
     <row r="251">
@@ -18732,10 +18732,10 @@
         <v>4</v>
       </c>
       <c r="O251" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P251" t="n">
-        <v>96.62997795084884</v>
+        <v>102.9024870139184</v>
       </c>
       <c r="Q251" t="n">
         <v>-6.950520000000012</v>
@@ -18744,10 +18744,10 @@
         <v>0</v>
       </c>
       <c r="S251" t="n">
-        <v>57.4061208915373</v>
+        <v>78.54860837640354</v>
       </c>
       <c r="T251" t="n">
-        <v>57.4061208915373</v>
+        <v>78.54860837640354</v>
       </c>
     </row>
     <row r="252">
@@ -18806,10 +18806,10 @@
         <v>7</v>
       </c>
       <c r="O252" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P252" t="n">
-        <v>89.24971462201255</v>
+        <v>95.54246808668917</v>
       </c>
       <c r="Q252" t="n">
         <v>-6.950520000000012</v>
@@ -18818,10 +18818,10 @@
         <v>0</v>
       </c>
       <c r="S252" t="n">
-        <v>52.33003349586413</v>
+        <v>73.47521240712155</v>
       </c>
       <c r="T252" t="n">
-        <v>52.33003349586413</v>
+        <v>73.47521240712155</v>
       </c>
     </row>
     <row r="253">
@@ -18880,10 +18880,10 @@
         <v>11</v>
       </c>
       <c r="O253" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P253" t="n">
-        <v>79.40936351689747</v>
+        <v>85.72910951705022</v>
       </c>
       <c r="Q253" t="n">
         <v>-6.950520000000012</v>
@@ -18892,10 +18892,10 @@
         <v>0</v>
       </c>
       <c r="S253" t="n">
-        <v>45.56191696829989</v>
+        <v>66.71068444807889</v>
       </c>
       <c r="T253" t="n">
-        <v>45.56191696829989</v>
+        <v>66.71068444807889</v>
       </c>
     </row>
     <row r="254">
@@ -18954,10 +18954,10 @@
         <v>12.5</v>
       </c>
       <c r="O254" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P254" t="n">
-        <v>75.71923185247933</v>
+        <v>82.04910005343561</v>
       </c>
       <c r="Q254" t="n">
         <v>-6.950520000000012</v>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="S254" t="n">
-        <v>43.02387327046331</v>
+        <v>64.1739864634379</v>
       </c>
       <c r="T254" t="n">
-        <v>43.02387327046331</v>
+        <v>64.1739864634379</v>
       </c>
     </row>
     <row r="255">
@@ -19028,10 +19028,10 @@
         <v>13.25</v>
       </c>
       <c r="O255" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P255" t="n">
-        <v>73.87416602027025</v>
+        <v>80.20909532162831</v>
       </c>
       <c r="Q255" t="n">
         <v>-0.3366600000000091</v>
@@ -19040,10 +19040,10 @@
         <v>0</v>
       </c>
       <c r="S255" t="n">
-        <v>46.30381260177442</v>
+        <v>67.4646924133888</v>
       </c>
       <c r="T255" t="n">
-        <v>46.30381260177442</v>
+        <v>67.4646924133888</v>
       </c>
     </row>
     <row r="256">
@@ -19102,10 +19102,10 @@
         <v>13.75</v>
       </c>
       <c r="O256" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P256" t="n">
-        <v>72.64412213213086</v>
+        <v>78.98242550042343</v>
       </c>
       <c r="Q256" t="n">
         <v>-6.950520000000012</v>
@@ -19114,10 +19114,10 @@
         <v>0</v>
       </c>
       <c r="S256" t="n">
-        <v>40.90883685559948</v>
+        <v>62.06007147623707</v>
       </c>
       <c r="T256" t="n">
-        <v>40.90883685559948</v>
+        <v>62.06007147623707</v>
       </c>
     </row>
     <row r="257">
@@ -19176,10 +19176,10 @@
         <v>19.75</v>
       </c>
       <c r="O257" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P257" t="n">
-        <v>57.88359547445825</v>
+        <v>64.26238764596502</v>
       </c>
       <c r="Q257" t="n">
         <v>-0.3366600000000091</v>
@@ -19188,10 +19188,10 @@
         <v>0</v>
       </c>
       <c r="S257" t="n">
-        <v>35.30562324448253</v>
+        <v>56.47233447994451</v>
       </c>
       <c r="T257" t="n">
-        <v>35.30562324448253</v>
+        <v>56.47233447994451</v>
       </c>
     </row>
     <row r="258">
@@ -19250,10 +19250,10 @@
         <v>22.75</v>
       </c>
       <c r="O258" t="n">
-        <v>0.0007085078861518348</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P258" t="n">
-        <v>53.89292480436574</v>
+        <v>60.28585261904565</v>
       </c>
       <c r="Q258" t="n">
         <v>-6.950520000000012</v>
@@ -19322,10 +19322,10 @@
         <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P259" t="n">
-        <v>95.37247242546729</v>
+        <v>95.15268885902782</v>
       </c>
       <c r="Q259" t="n">
         <v>-4.745900000000006</v>
@@ -19334,10 +19334,10 @@
         <v>12.54354569315199</v>
       </c>
       <c r="S259" t="n">
-        <v>66.68489144290291</v>
+        <v>83.37271141353199</v>
       </c>
       <c r="T259" t="n">
-        <v>66.68489144290291</v>
+        <v>83.37271141353199</v>
       </c>
     </row>
     <row r="260">
@@ -19396,10 +19396,10 @@
         <v>7</v>
       </c>
       <c r="O260" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P260" t="n">
-        <v>75.06776116066263</v>
+        <v>74.89796824849522</v>
       </c>
       <c r="Q260" t="n">
         <v>-4.745900000000006</v>
@@ -19408,10 +19408,10 @@
         <v>12.54354569315199</v>
       </c>
       <c r="S260" t="n">
-        <v>52.71946984048569</v>
+        <v>69.41076119024711</v>
       </c>
       <c r="T260" t="n">
-        <v>52.71946984048569</v>
+        <v>69.41076119024711</v>
       </c>
     </row>
     <row r="261">
@@ -19470,10 +19470,10 @@
         <v>12</v>
       </c>
       <c r="O261" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P261" t="n">
-        <v>60.56439597151645</v>
+        <v>60.43031066954337</v>
       </c>
       <c r="Q261" t="n">
         <v>-4.745900000000006</v>
@@ -19482,10 +19482,10 @@
         <v>12.54354569315199</v>
       </c>
       <c r="S261" t="n">
-        <v>42.74416869590197</v>
+        <v>59.43793960218649</v>
       </c>
       <c r="T261" t="n">
-        <v>42.74416869590197</v>
+        <v>59.43793960218649</v>
       </c>
     </row>
     <row r="262">
@@ -19544,10 +19544,10 @@
         <v>14</v>
       </c>
       <c r="O262" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P262" t="n">
-        <v>54.76304989585797</v>
+        <v>54.64324763796262</v>
       </c>
       <c r="Q262" t="n">
         <v>-4.745900000000006</v>
@@ -19556,10 +19556,10 @@
         <v>12.54354569315199</v>
       </c>
       <c r="S262" t="n">
-        <v>38.75404823806847</v>
+        <v>55.44881096696224</v>
       </c>
       <c r="T262" t="n">
-        <v>38.75404823806847</v>
+        <v>55.44881096696224</v>
       </c>
     </row>
     <row r="263">
@@ -19618,10 +19618,10 @@
         <v>21</v>
       </c>
       <c r="O263" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P263" t="n">
-        <v>35.92028646961339</v>
+        <v>35.84725439211385</v>
       </c>
       <c r="Q263" t="n">
         <v>-4.745900000000006</v>
@@ -19688,10 +19688,10 @@
         <v>22</v>
       </c>
       <c r="O264" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P264" t="n">
-        <v>34.46994995069878</v>
+        <v>34.40048863421867</v>
       </c>
       <c r="Q264" t="n">
         <v>-4.745900000000006</v>
@@ -19760,10 +19760,10 @@
         <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P265" t="n">
-        <v>100.7756672850471</v>
+        <v>101.4350904124156</v>
       </c>
       <c r="Q265" t="n">
         <v>-0.3366600000000091</v>
@@ -19772,10 +19772,10 @@
         <v>0</v>
       </c>
       <c r="S265" t="n">
-        <v>64.80645477190836</v>
+        <v>82.09615994116871</v>
       </c>
       <c r="T265" t="n">
-        <v>64.80645477190836</v>
+        <v>82.09615994116871</v>
       </c>
     </row>
     <row r="266">
@@ -19834,10 +19834,10 @@
         <v>0.75</v>
       </c>
       <c r="O266" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P266" t="n">
-        <v>98.055882321155</v>
+        <v>98.72176565108387</v>
       </c>
       <c r="Q266" t="n">
         <v>-0.3366600000000091</v>
@@ -19846,10 +19846,10 @@
         <v>0</v>
       </c>
       <c r="S266" t="n">
-        <v>62.93580794549886</v>
+        <v>80.22581544292757</v>
       </c>
       <c r="T266" t="n">
-        <v>62.93580794549886</v>
+        <v>80.22581544292757</v>
       </c>
     </row>
     <row r="267">
@@ -19908,10 +19908,10 @@
         <v>1.75</v>
       </c>
       <c r="O267" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P267" t="n">
-        <v>94.42950236929886</v>
+        <v>95.10399930264151</v>
       </c>
       <c r="Q267" t="n">
         <v>-0.3366600000000091</v>
@@ -19920,10 +19920,10 @@
         <v>0</v>
       </c>
       <c r="S267" t="n">
-        <v>60.44161217695285</v>
+        <v>77.73202277860611</v>
       </c>
       <c r="T267" t="n">
-        <v>60.44161217695285</v>
+        <v>77.73202277860611</v>
       </c>
     </row>
     <row r="268">
@@ -19982,10 +19982,10 @@
         <v>3.75</v>
       </c>
       <c r="O268" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P268" t="n">
-        <v>87.17674246558659</v>
+        <v>87.86846660575679</v>
       </c>
       <c r="Q268" t="n">
         <v>-0.3366600000000091</v>
@@ -19994,10 +19994,10 @@
         <v>0</v>
       </c>
       <c r="S268" t="n">
-        <v>55.45322063986082</v>
+        <v>72.74443744996313</v>
       </c>
       <c r="T268" t="n">
-        <v>55.45322063986082</v>
+        <v>72.74443744996313</v>
       </c>
     </row>
     <row r="269">
@@ -20056,10 +20056,10 @@
         <v>3.85</v>
       </c>
       <c r="O269" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P269" t="n">
-        <v>86.81410447040098</v>
+        <v>87.50668997091256</v>
       </c>
       <c r="Q269" t="n">
         <v>-0.3366600000000091</v>
@@ -20068,10 +20068,10 @@
         <v>0</v>
       </c>
       <c r="S269" t="n">
-        <v>55.20380106300622</v>
+        <v>72.495058183531</v>
       </c>
       <c r="T269" t="n">
-        <v>55.20380106300622</v>
+        <v>72.495058183531</v>
       </c>
     </row>
     <row r="270">
@@ -20130,10 +20130,10 @@
         <v>7.85</v>
       </c>
       <c r="O270" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P270" t="n">
-        <v>72.30858466297644</v>
+        <v>73.03562457714312</v>
       </c>
       <c r="Q270" t="n">
         <v>-0.3366600000000091</v>
@@ -20142,10 +20142,10 @@
         <v>0</v>
       </c>
       <c r="S270" t="n">
-        <v>45.22701798882217</v>
+        <v>62.51988752624507</v>
       </c>
       <c r="T270" t="n">
-        <v>45.22701798882217</v>
+        <v>62.51988752624507</v>
       </c>
     </row>
     <row r="271">
@@ -20204,10 +20204,10 @@
         <v>8.1</v>
       </c>
       <c r="O271" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P271" t="n">
-        <v>71.4019896750124</v>
+        <v>72.13118299003253</v>
       </c>
       <c r="Q271" t="n">
         <v>-0.3366600000000091</v>
@@ -20216,10 +20216,10 @@
         <v>0</v>
       </c>
       <c r="S271" t="n">
-        <v>44.60346904668566</v>
+        <v>61.89643936016469</v>
       </c>
       <c r="T271" t="n">
-        <v>44.60346904668566</v>
+        <v>61.89643936016469</v>
       </c>
     </row>
     <row r="272">
@@ -20278,10 +20278,10 @@
         <v>8.6</v>
       </c>
       <c r="O272" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P272" t="n">
-        <v>69.58879969908433</v>
+        <v>70.32229981581135</v>
       </c>
       <c r="Q272" t="n">
         <v>-0.3366600000000091</v>
@@ -20290,10 +20290,10 @@
         <v>0</v>
       </c>
       <c r="S272" t="n">
-        <v>43.35637116241265</v>
+        <v>60.64954302800395</v>
       </c>
       <c r="T272" t="n">
-        <v>43.35637116241265</v>
+        <v>60.64954302800395</v>
       </c>
     </row>
     <row r="273">
@@ -20352,10 +20352,10 @@
         <v>13.6</v>
       </c>
       <c r="O273" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P273" t="n">
-        <v>51.45689993980366</v>
+        <v>52.23346807359955</v>
       </c>
       <c r="Q273" t="n">
         <v>-0.3366600000000091</v>
@@ -20364,10 +20364,10 @@
         <v>0</v>
       </c>
       <c r="S273" t="n">
-        <v>30.88539231968259</v>
+        <v>48.18057970639654</v>
       </c>
       <c r="T273" t="n">
-        <v>30.88539231968259</v>
+        <v>48.18057970639654</v>
       </c>
     </row>
     <row r="274">
@@ -20426,10 +20426,10 @@
         <v>14.1</v>
       </c>
       <c r="O274" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P274" t="n">
-        <v>49.64370996387559</v>
+        <v>50.42458489937837</v>
       </c>
       <c r="Q274" t="n">
         <v>-0.3366600000000091</v>
@@ -20438,10 +20438,10 @@
         <v>0</v>
       </c>
       <c r="S274" t="n">
-        <v>29.63829443540958</v>
+        <v>46.93368337423581</v>
       </c>
       <c r="T274" t="n">
-        <v>29.63829443540958</v>
+        <v>46.93368337423581</v>
       </c>
     </row>
     <row r="275">
@@ -20500,10 +20500,10 @@
         <v>14.85</v>
       </c>
       <c r="O275" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P275" t="n">
-        <v>46.92392499998349</v>
+        <v>47.7112601380466</v>
       </c>
       <c r="Q275" t="n">
         <v>-0.3366600000000091</v>
@@ -20512,10 +20512,10 @@
         <v>0</v>
       </c>
       <c r="S275" t="n">
-        <v>27.76764760900006</v>
+        <v>45.0633388759947</v>
       </c>
       <c r="T275" t="n">
-        <v>27.76764760900006</v>
+        <v>45.0633388759947</v>
       </c>
     </row>
     <row r="276">
@@ -20574,10 +20574,10 @@
         <v>15.1</v>
       </c>
       <c r="O276" t="n">
-        <v>0.000965094284087884</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P276" t="n">
-        <v>46.01733001201946</v>
+        <v>46.80681855093601</v>
       </c>
       <c r="Q276" t="n">
         <v>-0.3366600000000091</v>
@@ -20586,10 +20586,10 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>27.14409866686356</v>
+        <v>44.43989070991432</v>
       </c>
       <c r="T276" t="n">
-        <v>27.14409866686356</v>
+        <v>44.43989070991432</v>
       </c>
     </row>
     <row r="277">
@@ -20650,10 +20650,10 @@
         <v>0</v>
       </c>
       <c r="O277" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P277" t="n">
-        <v>94.64382063486394</v>
+        <v>94.43889414413331</v>
       </c>
       <c r="Q277" t="n">
         <v>-4.745900000000006</v>
@@ -20662,10 +20662,10 @@
         <v>13</v>
       </c>
       <c r="S277" t="n">
-        <v>66.49767614246426</v>
+        <v>83.19532195274047</v>
       </c>
       <c r="T277" t="n">
-        <v>66.49767614246426</v>
+        <v>83.19532195274047</v>
       </c>
     </row>
     <row r="278">
@@ -20724,10 +20724,10 @@
         <v>1.5</v>
       </c>
       <c r="O278" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P278" t="n">
-        <v>90.02141807243694</v>
+        <v>89.82773064061732</v>
       </c>
       <c r="Q278" t="n">
         <v>-4.745900000000006</v>
@@ -20736,10 +20736,10 @@
         <v>13</v>
       </c>
       <c r="S278" t="n">
-        <v>63.31842381237663</v>
+        <v>80.01676241862182</v>
       </c>
       <c r="T278" t="n">
-        <v>63.31842381237663</v>
+        <v>80.01676241862182</v>
       </c>
     </row>
     <row r="279">
@@ -20798,10 +20798,10 @@
         <v>13.5</v>
       </c>
       <c r="O279" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P279" t="n">
-        <v>53.04219757302094</v>
+        <v>52.93842261248937</v>
       </c>
       <c r="Q279" t="n">
         <v>-4.745900000000006</v>
@@ -20810,10 +20810,10 @@
         <v>13</v>
       </c>
       <c r="S279" t="n">
-        <v>37.8844051716756</v>
+        <v>54.58828614567251</v>
       </c>
       <c r="T279" t="n">
-        <v>37.8844051716756</v>
+        <v>54.58828614567251</v>
       </c>
     </row>
     <row r="280">
@@ -20872,10 +20872,10 @@
         <v>13.75</v>
       </c>
       <c r="O280" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P280" t="n">
-        <v>52.27179714594977</v>
+        <v>52.16989536190337</v>
       </c>
       <c r="Q280" t="n">
         <v>-4.745900000000006</v>
@@ -20884,10 +20884,10 @@
         <v>13</v>
       </c>
       <c r="S280" t="n">
-        <v>37.35452978332766</v>
+        <v>54.0585262233194</v>
       </c>
       <c r="T280" t="n">
-        <v>37.35452978332766</v>
+        <v>54.0585262233194</v>
       </c>
     </row>
     <row r="281">
@@ -20946,10 +20946,10 @@
         <v>18.75</v>
       </c>
       <c r="O281" t="n">
-        <v>0.001000743576924677</v>
+        <v>0.001033478184302046</v>
       </c>
       <c r="P281" t="n">
-        <v>36.86378860452643</v>
+        <v>36.79935035018339</v>
       </c>
       <c r="Q281" t="n">
         <v>-4.745900000000006</v>
@@ -20958,10 +20958,10 @@
         <v>13</v>
       </c>
       <c r="S281" t="n">
-        <v>26.7570220163689</v>
+        <v>43.46332777625718</v>
       </c>
       <c r="T281" t="n">
-        <v>26.7570220163689</v>
+        <v>43.46332777625718</v>
       </c>
     </row>
     <row r="282">
@@ -21022,10 +21022,10 @@
         <v>0</v>
       </c>
       <c r="O282" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P282" t="n">
-        <v>77.84651831633516</v>
+        <v>78.52999107209367</v>
       </c>
       <c r="Q282" t="n">
         <v>1.867959999999982</v>
@@ -21034,10 +21034,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S282" t="n">
-        <v>58.83773906243938</v>
+        <v>76.13077800355981</v>
       </c>
       <c r="T282" t="n">
-        <v>58.83773906243938</v>
+        <v>76.13077800355981</v>
       </c>
     </row>
     <row r="283">
@@ -21096,10 +21096,10 @@
         <v>6.5</v>
       </c>
       <c r="O283" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P283" t="n">
-        <v>62.7090219605852</v>
+        <v>63.4302645922792</v>
       </c>
       <c r="Q283" t="n">
         <v>1.867959999999982</v>
@@ -21108,10 +21108,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S283" t="n">
-        <v>48.4262874610794</v>
+        <v>65.72225973514402</v>
       </c>
       <c r="T283" t="n">
-        <v>48.4262874610794</v>
+        <v>65.72225973514402</v>
       </c>
     </row>
     <row r="284">
@@ -21170,10 +21170,10 @@
         <v>6.65</v>
       </c>
       <c r="O284" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P284" t="n">
-        <v>62.35969512160635</v>
+        <v>63.08180936582195</v>
       </c>
       <c r="Q284" t="n">
         <v>1.867959999999982</v>
@@ -21182,10 +21182,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S284" t="n">
-        <v>48.1860231933557</v>
+        <v>65.48206315971905</v>
       </c>
       <c r="T284" t="n">
-        <v>48.1860231933557</v>
+        <v>65.48206315971905</v>
       </c>
     </row>
     <row r="285">
@@ -21244,10 +21244,10 @@
         <v>6.800000000000001</v>
       </c>
       <c r="O285" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P285" t="n">
-        <v>62.0103682826275</v>
+        <v>62.73335413936469</v>
       </c>
       <c r="Q285" t="n">
         <v>1.867959999999982</v>
@@ -21256,10 +21256,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S285" t="n">
-        <v>47.94575892563201</v>
+        <v>65.24186658429407</v>
       </c>
       <c r="T285" t="n">
-        <v>47.94575892563201</v>
+        <v>65.24186658429407</v>
       </c>
     </row>
     <row r="286">
@@ -21318,10 +21318,10 @@
         <v>6.850000000000001</v>
       </c>
       <c r="O286" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P286" t="n">
-        <v>61.89392600296789</v>
+        <v>62.61720239721227</v>
       </c>
       <c r="Q286" t="n">
         <v>1.867959999999982</v>
@@ -21330,10 +21330,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S286" t="n">
-        <v>47.86567083639078</v>
+        <v>65.1618010591524</v>
       </c>
       <c r="T286" t="n">
-        <v>47.86567083639078</v>
+        <v>65.1618010591524</v>
       </c>
     </row>
     <row r="287">
@@ -21392,10 +21392,10 @@
         <v>7.100000000000001</v>
       </c>
       <c r="O287" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P287" t="n">
-        <v>61.31171460466982</v>
+        <v>62.03644368645018</v>
       </c>
       <c r="Q287" t="n">
         <v>1.867959999999982</v>
@@ -21404,10 +21404,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S287" t="n">
-        <v>47.46523039018463</v>
+        <v>64.76147343344411</v>
       </c>
       <c r="T287" t="n">
-        <v>47.46523039018463</v>
+        <v>64.76147343344411</v>
       </c>
     </row>
     <row r="288">
@@ -21466,10 +21466,10 @@
         <v>7.850000000000001</v>
       </c>
       <c r="O288" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P288" t="n">
-        <v>59.56508040977559</v>
+        <v>60.29416755416389</v>
       </c>
       <c r="Q288" t="n">
         <v>1.867959999999982</v>
@@ -21478,10 +21478,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S288" t="n">
-        <v>46.26390905156617</v>
+        <v>63.56049055631921</v>
       </c>
       <c r="T288" t="n">
-        <v>46.26390905156617</v>
+        <v>63.56049055631921</v>
       </c>
     </row>
     <row r="289">
@@ -21540,10 +21540,10 @@
         <v>8.350000000000001</v>
       </c>
       <c r="O289" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P289" t="n">
-        <v>58.40065761317943</v>
+        <v>59.1326501326397</v>
       </c>
       <c r="Q289" t="n">
         <v>1.867959999999982</v>
@@ -21552,10 +21552,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S289" t="n">
-        <v>45.46302815915386</v>
+        <v>62.75983530490261</v>
       </c>
       <c r="T289" t="n">
-        <v>45.46302815915386</v>
+        <v>62.75983530490261</v>
       </c>
     </row>
     <row r="290">
@@ -21614,10 +21614,10 @@
         <v>8.600000000000001</v>
       </c>
       <c r="O290" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P290" t="n">
-        <v>57.81844621488136</v>
+        <v>58.55189142187761</v>
       </c>
       <c r="Q290" t="n">
         <v>1.867959999999982</v>
@@ -21626,10 +21626,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S290" t="n">
-        <v>45.06258771294771</v>
+        <v>62.35950767919432</v>
       </c>
       <c r="T290" t="n">
-        <v>45.06258771294771</v>
+        <v>62.35950767919432</v>
       </c>
     </row>
     <row r="291">
@@ -21688,10 +21688,10 @@
         <v>8.700000000000001</v>
       </c>
       <c r="O291" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P291" t="n">
-        <v>57.58556165556213</v>
+        <v>58.31958793757277</v>
       </c>
       <c r="Q291" t="n">
         <v>1.867959999999982</v>
@@ -21700,10 +21700,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S291" t="n">
-        <v>44.90241153446525</v>
+        <v>62.199376628911</v>
       </c>
       <c r="T291" t="n">
-        <v>44.90241153446525</v>
+        <v>62.199376628911</v>
       </c>
     </row>
     <row r="292">
@@ -21762,10 +21762,10 @@
         <v>8.750000000000002</v>
       </c>
       <c r="O292" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P292" t="n">
-        <v>57.46911937590251</v>
+        <v>58.20343619542035</v>
       </c>
       <c r="Q292" t="n">
         <v>1.867959999999982</v>
@@ -21774,10 +21774,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S292" t="n">
-        <v>44.82232344522401</v>
+        <v>62.11931110376933</v>
       </c>
       <c r="T292" t="n">
-        <v>44.82232344522401</v>
+        <v>62.11931110376933</v>
       </c>
     </row>
     <row r="293">
@@ -21836,10 +21836,10 @@
         <v>10.75</v>
       </c>
       <c r="O293" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P293" t="n">
-        <v>52.8114281895179</v>
+        <v>53.55736650932359</v>
       </c>
       <c r="Q293" t="n">
         <v>1.867959999999982</v>
@@ -21848,10 +21848,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S293" t="n">
-        <v>41.61879987557479</v>
+        <v>58.91669009810295</v>
       </c>
       <c r="T293" t="n">
-        <v>41.61879987557479</v>
+        <v>58.91669009810295</v>
       </c>
     </row>
     <row r="294">
@@ -21910,10 +21910,10 @@
         <v>14.75</v>
       </c>
       <c r="O294" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P294" t="n">
-        <v>43.4960458167487</v>
+        <v>44.26522713713008</v>
       </c>
       <c r="Q294" t="n">
         <v>1.867959999999982</v>
@@ -21922,10 +21922,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S294" t="n">
-        <v>35.21175273627635</v>
+        <v>52.51144808677016</v>
       </c>
       <c r="T294" t="n">
-        <v>35.21175273627635</v>
+        <v>52.51144808677016</v>
       </c>
     </row>
     <row r="295">
@@ -21986,10 +21986,10 @@
         <v>0</v>
       </c>
       <c r="O295" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P295" t="n">
-        <v>64.72657703626589</v>
+        <v>65.4359618710767</v>
       </c>
       <c r="Q295" t="n">
         <v>1.867959999999982</v>
@@ -21998,10 +21998,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S295" t="n">
-        <v>49.81394606259898</v>
+        <v>67.10482363755533</v>
       </c>
       <c r="T295" t="n">
-        <v>49.81394606259898</v>
+        <v>67.10482363755533</v>
       </c>
     </row>
     <row r="296">
@@ -22060,10 +22060,10 @@
         <v>1.25</v>
       </c>
       <c r="O296" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P296" t="n">
-        <v>61.84714122756537</v>
+        <v>62.56371060139789</v>
       </c>
       <c r="Q296" t="n">
         <v>1.867959999999982</v>
@@ -22072,10 +22072,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S296" t="n">
-        <v>47.83349263377811</v>
+        <v>65.12492818369412</v>
       </c>
       <c r="T296" t="n">
-        <v>47.83349263377811</v>
+        <v>65.12492818369412</v>
       </c>
     </row>
     <row r="297">
@@ -22134,10 +22134,10 @@
         <v>2</v>
       </c>
       <c r="O297" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P297" t="n">
-        <v>60.11947974234506</v>
+        <v>60.8403598395906</v>
       </c>
       <c r="Q297" t="n">
         <v>1.867959999999982</v>
@@ -22146,10 +22146,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S297" t="n">
-        <v>46.64522057648561</v>
+        <v>63.9369909113774</v>
       </c>
       <c r="T297" t="n">
-        <v>46.64522057648561</v>
+        <v>63.9369909113774</v>
       </c>
     </row>
     <row r="298">
@@ -22208,10 +22208,10 @@
         <v>2.05</v>
       </c>
       <c r="O298" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P298" t="n">
-        <v>60.00430230999704</v>
+        <v>60.72546978880345</v>
       </c>
       <c r="Q298" t="n">
         <v>1.867959999999982</v>
@@ -22220,10 +22220,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S298" t="n">
-        <v>46.56600243933277</v>
+        <v>63.85779509322295</v>
       </c>
       <c r="T298" t="n">
-        <v>46.56600243933277</v>
+        <v>63.85779509322295</v>
       </c>
     </row>
     <row r="299">
@@ -22282,10 +22282,10 @@
         <v>4.55</v>
       </c>
       <c r="O299" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P299" t="n">
-        <v>54.245430692596</v>
+        <v>54.98096724944583</v>
       </c>
       <c r="Q299" t="n">
         <v>1.867959999999982</v>
@@ -22294,10 +22294,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S299" t="n">
-        <v>42.60509558169105</v>
+        <v>59.89800418550054</v>
       </c>
       <c r="T299" t="n">
-        <v>42.60509558169105</v>
+        <v>59.89800418550054</v>
       </c>
     </row>
     <row r="300">
@@ -22356,10 +22356,10 @@
         <v>6.3</v>
       </c>
       <c r="O300" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P300" t="n">
-        <v>50.21422056041527</v>
+        <v>50.9598154718955</v>
       </c>
       <c r="Q300" t="n">
         <v>1.867959999999982</v>
@@ -22368,10 +22368,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S300" t="n">
-        <v>39.83246078134184</v>
+        <v>57.12615055009486</v>
       </c>
       <c r="T300" t="n">
-        <v>39.83246078134184</v>
+        <v>57.12615055009486</v>
       </c>
     </row>
     <row r="301">
@@ -22430,10 +22430,10 @@
         <v>6.399999999999999</v>
       </c>
       <c r="O301" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P301" t="n">
-        <v>49.98386569571923</v>
+        <v>50.73003537032119</v>
       </c>
       <c r="Q301" t="n">
         <v>1.867959999999982</v>
@@ -22442,10 +22442,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S301" t="n">
-        <v>39.67402450703618</v>
+        <v>56.96775891378596</v>
       </c>
       <c r="T301" t="n">
-        <v>39.67402450703618</v>
+        <v>56.96775891378596</v>
       </c>
     </row>
     <row r="302">
@@ -22504,10 +22504,10 @@
         <v>7.899999999999999</v>
       </c>
       <c r="O302" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P302" t="n">
-        <v>46.52854272527861</v>
+        <v>47.28333384670661</v>
       </c>
       <c r="Q302" t="n">
         <v>1.867959999999982</v>
@@ -22516,10 +22516,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S302" t="n">
-        <v>37.29748039245115</v>
+        <v>54.59188436915252</v>
       </c>
       <c r="T302" t="n">
-        <v>37.29748039245115</v>
+        <v>54.59188436915252</v>
       </c>
     </row>
     <row r="303">
@@ -22578,10 +22578,10 @@
         <v>8.649999999999999</v>
       </c>
       <c r="O303" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P303" t="n">
-        <v>44.8008812400583</v>
+        <v>45.55998308489933</v>
       </c>
       <c r="Q303" t="n">
         <v>1.867959999999982</v>
@@ -22590,10 +22590,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S303" t="n">
-        <v>36.10920833515863</v>
+        <v>53.40394709683579</v>
       </c>
       <c r="T303" t="n">
-        <v>36.10920833515863</v>
+        <v>53.40394709683579</v>
       </c>
     </row>
     <row r="304">
@@ -22652,10 +22652,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O304" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P304" t="n">
-        <v>44.68570380771027</v>
+        <v>45.44509303411218</v>
       </c>
       <c r="Q304" t="n">
         <v>1.867959999999982</v>
@@ -22664,10 +22664,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S304" t="n">
-        <v>36.02999019800579</v>
+        <v>53.32475127868135</v>
       </c>
       <c r="T304" t="n">
-        <v>36.02999019800579</v>
+        <v>53.32475127868135</v>
       </c>
     </row>
     <row r="305">
@@ -22726,10 +22726,10 @@
         <v>8.949999999999999</v>
       </c>
       <c r="O305" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P305" t="n">
-        <v>44.10981664597017</v>
+        <v>44.87064278017641</v>
       </c>
       <c r="Q305" t="n">
         <v>1.867959999999982</v>
@@ -22738,10 +22738,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S305" t="n">
-        <v>35.63389951224163</v>
+        <v>52.9287721879091</v>
       </c>
       <c r="T305" t="n">
-        <v>35.63389951224163</v>
+        <v>52.9287721879091</v>
       </c>
     </row>
     <row r="306">
@@ -22800,10 +22800,10 @@
         <v>15.95</v>
       </c>
       <c r="O306" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P306" t="n">
-        <v>27.98497611724725</v>
+        <v>28.78603566997507</v>
       </c>
       <c r="Q306" t="n">
         <v>1.867959999999982</v>
@@ -22812,10 +22812,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S306" t="n">
-        <v>24.54336031084481</v>
+        <v>41.84135764628635</v>
       </c>
       <c r="T306" t="n">
-        <v>24.54336031084481</v>
+        <v>41.84135764628635</v>
       </c>
     </row>
     <row r="307">
@@ -22874,10 +22874,10 @@
         <v>17.2</v>
       </c>
       <c r="O307" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P307" t="n">
-        <v>25.10554030854673</v>
+        <v>25.91378440029626</v>
       </c>
       <c r="Q307" t="n">
         <v>1.867959999999982</v>
@@ -22886,10 +22886,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S307" t="n">
-        <v>22.56290688202395</v>
+        <v>39.86146219242515</v>
       </c>
       <c r="T307" t="n">
-        <v>22.56290688202395</v>
+        <v>39.86146219242515</v>
       </c>
     </row>
     <row r="308">
@@ -22948,10 +22948,10 @@
         <v>19.7</v>
       </c>
       <c r="O308" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P308" t="n">
-        <v>19.34666869114569</v>
+        <v>20.16928186093864</v>
       </c>
       <c r="Q308" t="n">
         <v>1.867959999999982</v>
@@ -22960,10 +22960,10 @@
         <v>12.04644873936213</v>
       </c>
       <c r="S308" t="n">
-        <v>18.60200002438222</v>
+        <v>35.90167128470274</v>
       </c>
       <c r="T308" t="n">
-        <v>18.60200002438222</v>
+        <v>35.90167128470274</v>
       </c>
     </row>
     <row r="309">
@@ -23024,10 +23024,10 @@
         <v>0</v>
       </c>
       <c r="O309" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P309" t="n">
-        <v>112.7767789869313</v>
+        <v>125.6995814330882</v>
       </c>
       <c r="Q309" t="n">
         <v>5.174889999999976</v>
@@ -23036,10 +23036,10 @@
         <v>0</v>
       </c>
       <c r="S309" t="n">
-        <v>76.85152652189421</v>
+        <v>102.6213308665546</v>
       </c>
       <c r="T309" t="n">
-        <v>76.85152652189421</v>
+        <v>102.6213308665546</v>
       </c>
     </row>
     <row r="310">
@@ -23098,10 +23098,10 @@
         <v>1.5</v>
       </c>
       <c r="O310" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P310" t="n">
-        <v>109.8382010561608</v>
+        <v>122.7700559364071</v>
       </c>
       <c r="Q310" t="n">
         <v>-0.3366600000000091</v>
@@ -23110,10 +23110,10 @@
         <v>0</v>
       </c>
       <c r="S310" t="n">
-        <v>71.03959462054658</v>
+        <v>96.80274278618552</v>
       </c>
       <c r="T310" t="n">
-        <v>71.03959462054658</v>
+        <v>96.80274278618552</v>
       </c>
     </row>
     <row r="311">
@@ -23172,10 +23172,10 @@
         <v>1.5</v>
       </c>
       <c r="O311" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P311" t="n">
-        <v>109.8382010561608</v>
+        <v>122.7700559364071</v>
       </c>
       <c r="Q311" t="n">
         <v>-3.643590000000017</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="S311" t="n">
-        <v>68.76511403043187</v>
+        <v>94.52321531504981</v>
       </c>
       <c r="T311" t="n">
-        <v>68.76511403043187</v>
+        <v>94.52321531504981</v>
       </c>
     </row>
     <row r="312">
@@ -23246,10 +23246,10 @@
         <v>4</v>
       </c>
       <c r="O312" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P312" t="n">
-        <v>104.9405711715433</v>
+        <v>117.8875134419386</v>
       </c>
       <c r="Q312" t="n">
         <v>0.7656499999999937</v>
@@ -23258,10 +23258,10 @@
         <v>0</v>
       </c>
       <c r="S312" t="n">
-        <v>68.42920328754622</v>
+        <v>94.19695922910364</v>
       </c>
       <c r="T312" t="n">
-        <v>68.42920328754622</v>
+        <v>94.19695922910364</v>
       </c>
     </row>
     <row r="313">
@@ -23320,10 +23320,10 @@
         <v>5</v>
       </c>
       <c r="O313" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P313" t="n">
-        <v>102.9815192176963</v>
+        <v>115.9344964441512</v>
       </c>
       <c r="Q313" t="n">
         <v>-8.052830000000014</v>
@@ -23332,10 +23332,10 @@
         <v>0</v>
       </c>
       <c r="S313" t="n">
-        <v>61.01650110202493</v>
+        <v>86.77196888709094</v>
       </c>
       <c r="T313" t="n">
-        <v>61.01650110202493</v>
+        <v>86.77196888709094</v>
       </c>
     </row>
     <row r="314">
@@ -23394,10 +23394,10 @@
         <v>5.5</v>
       </c>
       <c r="O314" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P314" t="n">
-        <v>102.0019932407728</v>
+        <v>114.9579879452575</v>
       </c>
       <c r="Q314" t="n">
         <v>-6.950520000000012</v>
@@ -23406,10 +23406,10 @@
         <v>0</v>
       </c>
       <c r="S314" t="n">
-        <v>61.10095099278877</v>
+        <v>86.8586861679774</v>
       </c>
       <c r="T314" t="n">
-        <v>61.10095099278877</v>
+        <v>86.8586861679774</v>
       </c>
     </row>
     <row r="315">
@@ -23468,10 +23468,10 @@
         <v>6.5</v>
       </c>
       <c r="O315" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P315" t="n">
-        <v>100.0429412869258</v>
+        <v>113.0049709474701</v>
       </c>
       <c r="Q315" t="n">
         <v>-3.643590000000017</v>
@@ -23480,10 +23480,10 @@
         <v>0</v>
       </c>
       <c r="S315" t="n">
-        <v>62.02801097102137</v>
+        <v>87.79196322012891</v>
       </c>
       <c r="T315" t="n">
-        <v>62.02801097102137</v>
+        <v>87.79196322012891</v>
       </c>
     </row>
     <row r="316">
@@ -23542,10 +23542,10 @@
         <v>7.75</v>
       </c>
       <c r="O316" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P316" t="n">
-        <v>97.5941263446171</v>
+        <v>110.5636997002358</v>
       </c>
       <c r="Q316" t="n">
         <v>-4.745900000000006</v>
@@ -23554,10 +23554,10 @@
         <v>0</v>
       </c>
       <c r="S316" t="n">
-        <v>59.58557500946385</v>
+        <v>85.34930770602014</v>
       </c>
       <c r="T316" t="n">
-        <v>59.58557500946385</v>
+        <v>85.34930770602014</v>
       </c>
     </row>
     <row r="317">
@@ -23616,10 +23616,10 @@
         <v>8.5</v>
       </c>
       <c r="O317" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P317" t="n">
-        <v>96.12483737923185</v>
+        <v>109.0989369518953</v>
       </c>
       <c r="Q317" t="n">
         <v>-2.541280000000015</v>
@@ -23628,10 +23628,10 @@
         <v>0</v>
       </c>
       <c r="S317" t="n">
-        <v>60.09132994396207</v>
+        <v>85.85930487253913</v>
       </c>
       <c r="T317" t="n">
-        <v>60.09132994396207</v>
+        <v>85.85930487253913</v>
       </c>
     </row>
     <row r="318">
@@ -23690,10 +23690,10 @@
         <v>9.25</v>
       </c>
       <c r="O318" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P318" t="n">
-        <v>94.6555484138466</v>
+        <v>107.6341742035547</v>
       </c>
       <c r="Q318" t="n">
         <v>-9.155140000000017</v>
@@ -23702,10 +23702,10 @@
         <v>0</v>
       </c>
       <c r="S318" t="n">
-        <v>54.53180330482109</v>
+        <v>80.29056211602961</v>
       </c>
       <c r="T318" t="n">
-        <v>54.53180330482109</v>
+        <v>80.29056211602961</v>
       </c>
     </row>
     <row r="319">
@@ -23764,10 +23764,10 @@
         <v>10.75</v>
       </c>
       <c r="O319" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P319" t="n">
-        <v>91.71697048307611</v>
+        <v>104.7046487068736</v>
       </c>
       <c r="Q319" t="n">
         <v>-9.155140000000017</v>
@@ -23776,10 +23776,10 @@
         <v>0</v>
       </c>
       <c r="S319" t="n">
-        <v>52.51067238699794</v>
+        <v>78.27118648755334</v>
       </c>
       <c r="T319" t="n">
-        <v>52.51067238699794</v>
+        <v>78.27118648755334</v>
       </c>
     </row>
     <row r="320">
@@ -23838,10 +23838,10 @@
         <v>10.85</v>
       </c>
       <c r="O320" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P320" t="n">
-        <v>91.52106528769141</v>
+        <v>104.5093470070949</v>
       </c>
       <c r="Q320" t="n">
         <v>0.7656499999999937</v>
@@ -23850,10 +23850,10 @@
         <v>0</v>
       </c>
       <c r="S320" t="n">
-        <v>59.19937209615384</v>
+        <v>84.975143859062</v>
       </c>
       <c r="T320" t="n">
-        <v>59.19937209615384</v>
+        <v>84.975143859062</v>
       </c>
     </row>
     <row r="321">
@@ -23912,10 +23912,10 @@
         <v>11</v>
       </c>
       <c r="O321" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P321" t="n">
-        <v>91.22720749461436</v>
+        <v>104.2163944574268</v>
       </c>
       <c r="Q321" t="n">
         <v>-8.052830000000014</v>
@@ -23924,10 +23924,10 @@
         <v>0</v>
       </c>
       <c r="S321" t="n">
-        <v>52.93197743073232</v>
+        <v>78.69446637318586</v>
       </c>
       <c r="T321" t="n">
-        <v>52.93197743073232</v>
+        <v>78.69446637318586</v>
       </c>
     </row>
     <row r="322">
@@ -23986,10 +23986,10 @@
         <v>13.5</v>
       </c>
       <c r="O322" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P322" t="n">
-        <v>86.32957760999687</v>
+        <v>99.33385196295825</v>
       </c>
       <c r="Q322" t="n">
         <v>-3.643590000000017</v>
@@ -23998,10 +23998,10 @@
         <v>0</v>
       </c>
       <c r="S322" t="n">
-        <v>52.59606668784667</v>
+        <v>78.36821028723966</v>
       </c>
       <c r="T322" t="n">
-        <v>52.59606668784667</v>
+        <v>78.36821028723966</v>
       </c>
     </row>
     <row r="323">
@@ -24060,10 +24060,10 @@
         <v>15</v>
       </c>
       <c r="O323" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P323" t="n">
-        <v>83.3909996792264</v>
+        <v>96.40432646627715</v>
       </c>
       <c r="Q323" t="n">
         <v>6.277199999999993</v>
@@ -24072,10 +24072,10 @@
         <v>0</v>
       </c>
       <c r="S323" t="n">
-        <v>57.39837754036764</v>
+        <v>83.18741707217052</v>
       </c>
       <c r="T323" t="n">
-        <v>57.39837754036764</v>
+        <v>83.18741707217052</v>
       </c>
     </row>
     <row r="324">
@@ -24134,10 +24134,10 @@
         <v>45</v>
       </c>
       <c r="O324" t="n">
-        <v>0.000917099054330076</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P324" t="n">
-        <v>49.11477706568104</v>
+        <v>62.24121080287908</v>
       </c>
       <c r="Q324" t="n">
         <v>-8.052830000000014</v>
@@ -24206,10 +24206,10 @@
         <v>0</v>
       </c>
       <c r="O325" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P325" t="n">
-        <v>73.73836809786719</v>
+        <v>74.49767530115554</v>
       </c>
       <c r="Q325" t="n">
         <v>-0.3366600000000091</v>
@@ -24218,10 +24218,10 @@
         <v>13</v>
       </c>
       <c r="S325" t="n">
-        <v>55.15171017832049</v>
+        <v>72.48884420641193</v>
       </c>
       <c r="T325" t="n">
-        <v>55.15171017832049</v>
+        <v>72.48884420641193</v>
       </c>
     </row>
     <row r="326">
@@ -24280,10 +24280,10 @@
         <v>0.1</v>
       </c>
       <c r="O326" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P326" t="n">
-        <v>73.47017784517071</v>
+        <v>74.230137134903</v>
       </c>
       <c r="Q326" t="n">
         <v>-0.3366600000000091</v>
@@ -24292,10 +24292,10 @@
         <v>13</v>
       </c>
       <c r="S326" t="n">
-        <v>54.9672510200631</v>
+        <v>72.30442524394525</v>
       </c>
       <c r="T326" t="n">
-        <v>54.9672510200631</v>
+        <v>72.30442524394525</v>
       </c>
     </row>
     <row r="327">
@@ -24354,10 +24354,10 @@
         <v>0.2</v>
       </c>
       <c r="O327" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P327" t="n">
-        <v>73.20198759247423</v>
+        <v>73.96259896865045</v>
       </c>
       <c r="Q327" t="n">
         <v>-3.643590000000017</v>
@@ -24366,10 +24366,10 @@
         <v>13</v>
       </c>
       <c r="S327" t="n">
-        <v>52.508311271691</v>
+        <v>69.84047881034286</v>
       </c>
       <c r="T327" t="n">
-        <v>52.508311271691</v>
+        <v>69.84047881034286</v>
       </c>
     </row>
     <row r="328">
@@ -24428,10 +24428,10 @@
         <v>0.35</v>
       </c>
       <c r="O328" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P328" t="n">
-        <v>72.7997022134295</v>
+        <v>73.56129171927164</v>
       </c>
       <c r="Q328" t="n">
         <v>-3.643590000000017</v>
@@ -24440,10 +24440,10 @@
         <v>13</v>
       </c>
       <c r="S328" t="n">
-        <v>52.23162253430491</v>
+        <v>69.56385036664284</v>
       </c>
       <c r="T328" t="n">
-        <v>52.23162253430491</v>
+        <v>69.56385036664284</v>
       </c>
     </row>
     <row r="329">
@@ -24502,10 +24502,10 @@
         <v>0.5</v>
       </c>
       <c r="O329" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P329" t="n">
-        <v>72.39741683438476</v>
+        <v>73.15998446989283</v>
       </c>
       <c r="Q329" t="n">
         <v>-0.3366600000000091</v>
@@ -24514,10 +24514,10 @@
         <v>13</v>
       </c>
       <c r="S329" t="n">
-        <v>54.22941438703353</v>
+        <v>71.56674939407853</v>
       </c>
       <c r="T329" t="n">
-        <v>54.22941438703353</v>
+        <v>71.56674939407853</v>
       </c>
     </row>
     <row r="330">
@@ -24576,10 +24576,10 @@
         <v>0.75</v>
       </c>
       <c r="O330" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P330" t="n">
-        <v>71.72694120264354</v>
+        <v>72.49113905426148</v>
       </c>
       <c r="Q330" t="n">
         <v>-0.3366600000000091</v>
@@ -24588,10 +24588,10 @@
         <v>13</v>
       </c>
       <c r="S330" t="n">
-        <v>53.76826649139005</v>
+        <v>71.10570198791183</v>
       </c>
       <c r="T330" t="n">
-        <v>53.76826649139005</v>
+        <v>71.10570198791183</v>
       </c>
     </row>
     <row r="331">
@@ -24650,10 +24650,10 @@
         <v>3.75</v>
       </c>
       <c r="O331" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P331" t="n">
-        <v>63.68123362174894</v>
+        <v>64.46499406668522</v>
       </c>
       <c r="Q331" t="n">
         <v>-3.643590000000017</v>
@@ -24662,10 +24662,10 @@
         <v>13</v>
       </c>
       <c r="S331" t="n">
-        <v>45.96001115355359</v>
+        <v>63.29360564277572</v>
       </c>
       <c r="T331" t="n">
-        <v>45.96001115355359</v>
+        <v>63.29360564277572</v>
       </c>
     </row>
     <row r="332">
@@ -24724,10 +24724,10 @@
         <v>5.25</v>
       </c>
       <c r="O332" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P332" t="n">
-        <v>59.65837983130164</v>
+        <v>60.45192157289708</v>
       </c>
       <c r="Q332" t="n">
         <v>-3.643590000000017</v>
@@ -24736,10 +24736,10 @@
         <v>13</v>
       </c>
       <c r="S332" t="n">
-        <v>43.19312377969272</v>
+        <v>60.52732120577551</v>
       </c>
       <c r="T332" t="n">
-        <v>43.19312377969272</v>
+        <v>60.52732120577551</v>
       </c>
     </row>
     <row r="333">
@@ -24798,10 +24798,10 @@
         <v>20.25</v>
       </c>
       <c r="O333" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P333" t="n">
-        <v>19.78191448465605</v>
+        <v>20.67573151434326</v>
       </c>
       <c r="Q333" t="n">
         <v>-0.3366600000000091</v>
@@ -24870,10 +24870,10 @@
         <v>0</v>
       </c>
       <c r="O334" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P334" t="n">
-        <v>106.5158190368647</v>
+        <v>113.6456196949502</v>
       </c>
       <c r="Q334" t="n">
         <v>-0.3366600000000091</v>
@@ -24882,10 +24882,10 @@
         <v>0</v>
       </c>
       <c r="S334" t="n">
-        <v>68.75448625241202</v>
+        <v>90.51310161717768</v>
       </c>
       <c r="T334" t="n">
-        <v>68.75448625241202</v>
+        <v>90.51310161717768</v>
       </c>
     </row>
     <row r="335">
@@ -24944,10 +24944,10 @@
         <v>0.5</v>
       </c>
       <c r="O335" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P335" t="n">
-        <v>105.3174755060341</v>
+        <v>112.4502661755075</v>
       </c>
       <c r="Q335" t="n">
         <v>-0.3366600000000091</v>
@@ -24956,10 +24956,10 @@
         <v>0</v>
       </c>
       <c r="S335" t="n">
-        <v>67.93027494429131</v>
+        <v>89.68912252318768</v>
       </c>
       <c r="T335" t="n">
-        <v>67.93027494429131</v>
+        <v>89.68912252318768</v>
       </c>
     </row>
     <row r="336">
@@ -25018,10 +25018,10 @@
         <v>1.25</v>
       </c>
       <c r="O336" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P336" t="n">
-        <v>103.5199602097882</v>
+        <v>110.6572358963434</v>
       </c>
       <c r="Q336" t="n">
         <v>-0.3366600000000091</v>
@@ -25030,10 +25030,10 @@
         <v>0</v>
       </c>
       <c r="S336" t="n">
-        <v>66.69395798211019</v>
+        <v>88.45315388220266</v>
       </c>
       <c r="T336" t="n">
-        <v>66.69395798211019</v>
+        <v>88.45315388220266</v>
       </c>
     </row>
     <row r="337">
@@ -25092,10 +25092,10 @@
         <v>1.35</v>
       </c>
       <c r="O337" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P337" t="n">
-        <v>103.2802915036221</v>
+        <v>110.4181651924549</v>
       </c>
       <c r="Q337" t="n">
         <v>-0.3366600000000091</v>
@@ -25104,10 +25104,10 @@
         <v>0</v>
       </c>
       <c r="S337" t="n">
-        <v>66.52911572048606</v>
+        <v>88.28835806340464</v>
       </c>
       <c r="T337" t="n">
-        <v>66.52911572048606</v>
+        <v>88.28835806340464</v>
       </c>
     </row>
     <row r="338">
@@ -25166,10 +25166,10 @@
         <v>1.6</v>
       </c>
       <c r="O338" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P338" t="n">
-        <v>102.6811197382068</v>
+        <v>109.8204884327335</v>
       </c>
       <c r="Q338" t="n">
         <v>-0.3366600000000091</v>
@@ -25178,10 +25178,10 @@
         <v>0</v>
       </c>
       <c r="S338" t="n">
-        <v>66.11701006642568</v>
+        <v>87.87636851640963</v>
       </c>
       <c r="T338" t="n">
-        <v>66.11701006642568</v>
+        <v>87.87636851640963</v>
       </c>
     </row>
     <row r="339">
@@ -25240,10 +25240,10 @@
         <v>2.6</v>
       </c>
       <c r="O339" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P339" t="n">
-        <v>100.2844326765456</v>
+        <v>107.4297813938481</v>
       </c>
       <c r="Q339" t="n">
         <v>-0.3366600000000091</v>
@@ -25252,10 +25252,10 @@
         <v>0</v>
       </c>
       <c r="S339" t="n">
-        <v>64.46858745018423</v>
+        <v>86.22841032842962</v>
       </c>
       <c r="T339" t="n">
-        <v>64.46858745018423</v>
+        <v>86.22841032842962</v>
       </c>
     </row>
     <row r="340">
@@ -25314,10 +25314,10 @@
         <v>5.6</v>
       </c>
       <c r="O340" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P340" t="n">
-        <v>93.09437149156209</v>
+        <v>100.2576602771918</v>
       </c>
       <c r="Q340" t="n">
         <v>-0.3366600000000091</v>
@@ -25326,10 +25326,10 @@
         <v>0</v>
       </c>
       <c r="S340" t="n">
-        <v>59.52331960145984</v>
+        <v>81.2845357644895</v>
       </c>
       <c r="T340" t="n">
-        <v>59.52331960145984</v>
+        <v>81.2845357644895</v>
       </c>
     </row>
     <row r="341">
@@ -25388,10 +25388,10 @@
         <v>8.1</v>
       </c>
       <c r="O341" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P341" t="n">
-        <v>87.10265383740915</v>
+        <v>94.28089267997828</v>
       </c>
       <c r="Q341" t="n">
         <v>-3.643590000000017</v>
@@ -25400,10 +25400,10 @@
         <v>0</v>
       </c>
       <c r="S341" t="n">
-        <v>53.12778247074147</v>
+        <v>74.88511282340374</v>
       </c>
       <c r="T341" t="n">
-        <v>53.12778247074147</v>
+        <v>74.88511282340374</v>
       </c>
     </row>
     <row r="342">
@@ -25462,10 +25462,10 @@
         <v>11.6</v>
       </c>
       <c r="O342" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P342" t="n">
-        <v>78.71424912159503</v>
+        <v>85.91341804387928</v>
       </c>
       <c r="Q342" t="n">
         <v>-0.3366600000000091</v>
@@ -25474,10 +25474,10 @@
         <v>0</v>
       </c>
       <c r="S342" t="n">
-        <v>49.63278390401106</v>
+        <v>71.39678663660932</v>
       </c>
       <c r="T342" t="n">
-        <v>49.63278390401106</v>
+        <v>71.39678663660932</v>
       </c>
     </row>
     <row r="343">
@@ -25536,10 +25536,10 @@
         <v>11.75</v>
       </c>
       <c r="O343" t="n">
-        <v>0.001229456316990812</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P343" t="n">
-        <v>78.35474606234587</v>
+        <v>85.55481198804647</v>
       </c>
       <c r="Q343" t="n">
         <v>-1.438970000000012</v>
@@ -25548,10 +25548,10 @@
         <v>0</v>
       </c>
       <c r="S343" t="n">
-        <v>48.62736031486994</v>
+        <v>70.38975041803376</v>
       </c>
       <c r="T343" t="n">
-        <v>48.62736031486994</v>
+        <v>70.38975041803376</v>
       </c>
     </row>
     <row r="344">
@@ -25612,10 +25612,10 @@
         <v>0</v>
       </c>
       <c r="O344" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P344" t="n">
-        <v>109.6893869338127</v>
+        <v>118.6501868960271</v>
       </c>
       <c r="Q344" t="n">
         <v>-2.541280000000015</v>
@@ -25624,10 +25624,10 @@
         <v>0</v>
       </c>
       <c r="S344" t="n">
-        <v>69.42092103767837</v>
+        <v>92.44315655108443</v>
       </c>
       <c r="T344" t="n">
-        <v>69.42092103767837</v>
+        <v>92.44315655108443</v>
       </c>
     </row>
     <row r="345">
@@ -25686,10 +25686,10 @@
         <v>1.75</v>
       </c>
       <c r="O345" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P345" t="n">
-        <v>107.4107847293526</v>
+        <v>116.3805348737307</v>
       </c>
       <c r="Q345" t="n">
         <v>4.072579999999988</v>
@@ -25698,10 +25698,10 @@
         <v>0</v>
       </c>
       <c r="S345" t="n">
-        <v>72.40267744289375</v>
+        <v>95.43769874747269</v>
       </c>
       <c r="T345" t="n">
-        <v>72.40267744289375</v>
+        <v>95.43769874747269</v>
       </c>
     </row>
     <row r="346">
@@ -25760,10 +25760,10 @@
         <v>3</v>
       </c>
       <c r="O346" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P346" t="n">
-        <v>105.7832117261668</v>
+        <v>114.7593548578047</v>
       </c>
       <c r="Q346" t="n">
         <v>-2.541280000000015</v>
@@ -25772,10 +25772,10 @@
         <v>0</v>
       </c>
       <c r="S346" t="n">
-        <v>66.73428428051145</v>
+        <v>89.76113470099907</v>
       </c>
       <c r="T346" t="n">
-        <v>66.73428428051145</v>
+        <v>89.76113470099907</v>
       </c>
     </row>
     <row r="347">
@@ -25834,10 +25834,10 @@
         <v>4.25</v>
       </c>
       <c r="O347" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P347" t="n">
-        <v>104.155638722981</v>
+        <v>113.1381748418787</v>
       </c>
       <c r="Q347" t="n">
         <v>0.7656499999999937</v>
@@ -25846,10 +25846,10 @@
         <v>0</v>
       </c>
       <c r="S347" t="n">
-        <v>67.88933288847329</v>
+        <v>90.92315306793253</v>
       </c>
       <c r="T347" t="n">
-        <v>67.88933288847329</v>
+        <v>90.92315306793253</v>
       </c>
     </row>
     <row r="348">
@@ -25908,10 +25908,10 @@
         <v>6.75</v>
       </c>
       <c r="O348" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P348" t="n">
-        <v>100.9004927166093</v>
+        <v>109.8958148100268</v>
       </c>
       <c r="Q348" t="n">
         <v>-2.541280000000015</v>
@@ -25920,10 +25920,10 @@
         <v>0</v>
       </c>
       <c r="S348" t="n">
-        <v>63.37598833405283</v>
+        <v>86.40860738839237</v>
       </c>
       <c r="T348" t="n">
-        <v>63.37598833405283</v>
+        <v>86.40860738839237</v>
       </c>
     </row>
     <row r="349">
@@ -25982,10 +25982,10 @@
         <v>8.75</v>
       </c>
       <c r="O349" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P349" t="n">
-        <v>98.29637591151206</v>
+        <v>107.3019267845452</v>
       </c>
       <c r="Q349" t="n">
         <v>-0.3366600000000091</v>
@@ -25994,10 +25994,10 @@
         <v>0</v>
       </c>
       <c r="S349" t="n">
-        <v>63.10121755601802</v>
+        <v>86.14027780242594</v>
       </c>
       <c r="T349" t="n">
-        <v>63.10121755601802</v>
+        <v>86.14027780242594</v>
       </c>
     </row>
     <row r="350">
@@ -26056,10 +26056,10 @@
         <v>12.25</v>
       </c>
       <c r="O350" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P350" t="n">
-        <v>93.73917150259179</v>
+        <v>102.7626227399525</v>
       </c>
       <c r="Q350" t="n">
         <v>-0.3366600000000091</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="S350" t="n">
-        <v>59.96680800598997</v>
+        <v>83.0112523106597</v>
       </c>
       <c r="T350" t="n">
-        <v>59.96680800598997</v>
+        <v>83.0112523106597</v>
       </c>
     </row>
     <row r="351">
@@ -26130,10 +26130,10 @@
         <v>13.25</v>
       </c>
       <c r="O351" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P351" t="n">
-        <v>92.43711310004315</v>
+        <v>101.4656787272117</v>
       </c>
       <c r="Q351" t="n">
         <v>-3.643590000000017</v>
@@ -26142,10 +26142,10 @@
         <v>0</v>
       </c>
       <c r="S351" t="n">
-        <v>56.79678183015296</v>
+        <v>79.8377175561622</v>
       </c>
       <c r="T351" t="n">
-        <v>56.79678183015296</v>
+        <v>79.8377175561622</v>
       </c>
     </row>
     <row r="352">
@@ -26204,10 +26204,10 @@
         <v>18.25</v>
       </c>
       <c r="O352" t="n">
-        <v>0.001073184886675175</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P352" t="n">
-        <v>85.92682108729991</v>
+        <v>94.98095866350775</v>
       </c>
       <c r="Q352" t="n">
         <v>-0.3366600000000091</v>
@@ -26216,10 +26216,10 @@
         <v>0</v>
       </c>
       <c r="S352" t="n">
-        <v>54.59353449165615</v>
+        <v>77.647208610489</v>
       </c>
       <c r="T352" t="n">
-        <v>54.59353449165615</v>
+        <v>77.647208610489</v>
       </c>
     </row>
     <row r="353">
@@ -26280,10 +26280,10 @@
         <v>0</v>
       </c>
       <c r="O353" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P353" t="n">
-        <v>99.8921616572304</v>
+        <v>100.1127745008272</v>
       </c>
       <c r="Q353" t="n">
         <v>-8.052830000000014</v>
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="S353" t="n">
-        <v>58.89166513416232</v>
+        <v>75.86576591016748</v>
       </c>
       <c r="T353" t="n">
-        <v>58.89166513416232</v>
+        <v>75.86576591016748</v>
       </c>
     </row>
     <row r="354">
@@ -26354,10 +26354,10 @@
         <v>0.15</v>
       </c>
       <c r="O354" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P354" t="n">
-        <v>99.60413782200636</v>
+        <v>99.82563793721751</v>
       </c>
       <c r="Q354" t="n">
         <v>-0.3366600000000091</v>
@@ -26366,10 +26366,10 @@
         <v>0</v>
       </c>
       <c r="S354" t="n">
-        <v>64.00068596989755</v>
+        <v>80.98673484577765</v>
       </c>
       <c r="T354" t="n">
-        <v>64.00068596989755</v>
+        <v>80.98673484577765</v>
       </c>
     </row>
     <row r="355">
@@ -26428,10 +26428,10 @@
         <v>2.65</v>
       </c>
       <c r="O355" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P355" t="n">
-        <v>94.8037405682724</v>
+        <v>95.04002854372276</v>
       </c>
       <c r="Q355" t="n">
         <v>-1.438970000000012</v>
@@ -26440,10 +26440,10 @@
         <v>0</v>
       </c>
       <c r="S355" t="n">
-        <v>59.94085008654134</v>
+        <v>76.92808407140265</v>
       </c>
       <c r="T355" t="n">
-        <v>59.94085008654134</v>
+        <v>76.92808407140265</v>
       </c>
     </row>
     <row r="356">
@@ -26502,10 +26502,10 @@
         <v>2.75</v>
       </c>
       <c r="O356" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P356" t="n">
-        <v>94.61172467812304</v>
+        <v>94.84860416798297</v>
       </c>
       <c r="Q356" t="n">
         <v>-0.3366600000000091</v>
@@ -26514,10 +26514,10 @@
         <v>0</v>
       </c>
       <c r="S356" t="n">
-        <v>60.56694325578018</v>
+        <v>77.55597423042136</v>
       </c>
       <c r="T356" t="n">
-        <v>60.56694325578018</v>
+        <v>77.55597423042136</v>
       </c>
     </row>
     <row r="357">
@@ -26576,10 +26576,10 @@
         <v>4.25</v>
       </c>
       <c r="O357" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P357" t="n">
-        <v>91.73148632588266</v>
+        <v>91.97723853188613</v>
       </c>
       <c r="Q357" t="n">
         <v>-2.541280000000015</v>
@@ -26588,10 +26588,10 @@
         <v>0</v>
       </c>
       <c r="S357" t="n">
-        <v>57.06961745037959</v>
+        <v>74.05700427926638</v>
       </c>
       <c r="T357" t="n">
-        <v>57.06961745037959</v>
+        <v>74.05700427926638</v>
       </c>
     </row>
     <row r="358">
@@ -26650,10 +26650,10 @@
         <v>4.5</v>
       </c>
       <c r="O358" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P358" t="n">
-        <v>91.25144660050927</v>
+        <v>91.49867759253665</v>
       </c>
       <c r="Q358" t="n">
         <v>-6.950520000000012</v>
@@ -26662,10 +26662,10 @@
         <v>0</v>
       </c>
       <c r="S358" t="n">
-        <v>53.70680909489487</v>
+        <v>70.68775348935247</v>
       </c>
       <c r="T358" t="n">
-        <v>53.70680909489487</v>
+        <v>70.68775348935247</v>
       </c>
     </row>
     <row r="359">
@@ -26724,10 +26724,10 @@
         <v>5.75</v>
       </c>
       <c r="O359" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P359" t="n">
-        <v>88.85124797364229</v>
+        <v>89.10587289578928</v>
       </c>
       <c r="Q359" t="n">
         <v>-1.438970000000012</v>
@@ -26736,10 +26736,10 @@
         <v>0</v>
       </c>
       <c r="S359" t="n">
-        <v>55.84677223509371</v>
+        <v>72.83756179924708</v>
       </c>
       <c r="T359" t="n">
-        <v>55.84677223509371</v>
+        <v>72.83756179924708</v>
       </c>
     </row>
     <row r="360">
@@ -26798,10 +26798,10 @@
         <v>6</v>
       </c>
       <c r="O360" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P360" t="n">
-        <v>88.37120824826889</v>
+        <v>88.62731195643981</v>
       </c>
       <c r="Q360" t="n">
         <v>5.174889999999976</v>
@@ -26810,10 +26810,10 @@
         <v>0</v>
       </c>
       <c r="S360" t="n">
-        <v>60.06556584665797</v>
+        <v>77.06673591311883</v>
       </c>
       <c r="T360" t="n">
-        <v>60.06556584665797</v>
+        <v>77.06673591311883</v>
       </c>
     </row>
     <row r="361">
@@ -26872,10 +26872,10 @@
         <v>9</v>
       </c>
       <c r="O361" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P361" t="n">
-        <v>82.61073154378813</v>
+        <v>82.88458068424612</v>
       </c>
       <c r="Q361" t="n">
         <v>-8.052830000000014</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="S361" t="n">
-        <v>47.00563266221759</v>
+        <v>63.99005608778034</v>
       </c>
       <c r="T361" t="n">
-        <v>47.00563266221759</v>
+        <v>63.99005608778034</v>
       </c>
     </row>
     <row r="362">
@@ -26946,10 +26946,10 @@
         <v>12</v>
       </c>
       <c r="O362" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P362" t="n">
-        <v>76.85025483930737</v>
+        <v>77.14184941205244</v>
       </c>
       <c r="Q362" t="n">
         <v>6.277199999999993</v>
@@ -26958,10 +26958,10 @@
         <v>0</v>
       </c>
       <c r="S362" t="n">
-        <v>52.89970439539973</v>
+        <v>69.909438521906</v>
       </c>
       <c r="T362" t="n">
-        <v>52.89970439539973</v>
+        <v>69.909438521906</v>
       </c>
     </row>
     <row r="363">
@@ -27020,10 +27020,10 @@
         <v>14</v>
       </c>
       <c r="O363" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P363" t="n">
-        <v>73.0099370363202</v>
+        <v>73.31336189725664</v>
       </c>
       <c r="Q363" t="n">
         <v>-4.745900000000006</v>
@@ -27032,10 +27032,10 @@
         <v>0</v>
       </c>
       <c r="S363" t="n">
-        <v>42.67676187902967</v>
+        <v>59.67196699092319</v>
       </c>
       <c r="T363" t="n">
-        <v>42.67676187902967</v>
+        <v>59.67196699092319</v>
       </c>
     </row>
     <row r="364">
@@ -27094,10 +27094,10 @@
         <v>18</v>
       </c>
       <c r="O364" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P364" t="n">
-        <v>65.32930143034585</v>
+        <v>65.65638686766505</v>
       </c>
       <c r="Q364" t="n">
         <v>-2.541280000000015</v>
@@ -27106,10 +27106,10 @@
         <v>0</v>
       </c>
       <c r="S364" t="n">
-        <v>38.91040117379737</v>
+        <v>55.91355871728603</v>
       </c>
       <c r="T364" t="n">
-        <v>38.91040117379737</v>
+        <v>55.91355871728603</v>
       </c>
     </row>
     <row r="365">
@@ -27168,10 +27168,10 @@
         <v>22.5</v>
       </c>
       <c r="O365" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P365" t="n">
-        <v>59.10083815279595</v>
+        <v>59.44948497631562</v>
       </c>
       <c r="Q365" t="n">
         <v>4.072579999999988</v>
@@ -27240,10 +27240,10 @@
         <v>0</v>
       </c>
       <c r="O366" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P366" t="n">
-        <v>98.98432291089227</v>
+        <v>100.1218907058739</v>
       </c>
       <c r="Q366" t="n">
         <v>-2.541280000000015</v>
@@ -27252,10 +27252,10 @@
         <v>0</v>
       </c>
       <c r="S366" t="n">
-        <v>62.05806172826819</v>
+        <v>79.67126232931588</v>
       </c>
       <c r="T366" t="n">
-        <v>62.05806172826819</v>
+        <v>79.67126232931588</v>
       </c>
     </row>
     <row r="367">
@@ -27314,10 +27314,10 @@
         <v>2</v>
       </c>
       <c r="O367" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P367" t="n">
-        <v>95.73201761283329</v>
+        <v>96.88062517946874</v>
       </c>
       <c r="Q367" t="n">
         <v>-1.438970000000012</v>
@@ -27326,10 +27326,10 @@
         <v>0</v>
       </c>
       <c r="S367" t="n">
-        <v>60.57931177762726</v>
+        <v>78.19684107395878</v>
       </c>
       <c r="T367" t="n">
-        <v>60.57931177762726</v>
+        <v>78.19684107395878</v>
       </c>
     </row>
     <row r="368">
@@ -27388,10 +27388,10 @@
         <v>2.25</v>
       </c>
       <c r="O368" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P368" t="n">
-        <v>95.32547945057591</v>
+        <v>96.47546698866809</v>
       </c>
       <c r="Q368" t="n">
         <v>1.867959999999982</v>
@@ -27400,10 +27400,10 @@
         <v>0</v>
       </c>
       <c r="S368" t="n">
-        <v>62.57417859932374</v>
+        <v>80.1970855768775</v>
       </c>
       <c r="T368" t="n">
-        <v>62.57417859932374</v>
+        <v>80.1970855768775</v>
       </c>
     </row>
     <row r="369">
@@ -27462,10 +27462,10 @@
         <v>3.5</v>
       </c>
       <c r="O369" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P369" t="n">
-        <v>93.29278863928906</v>
+        <v>94.44967603466488</v>
       </c>
       <c r="Q369" t="n">
         <v>-1.438970000000012</v>
@@ -27474,10 +27474,10 @@
         <v>0</v>
       </c>
       <c r="S369" t="n">
-        <v>58.90162916711789</v>
+        <v>76.52114326465701</v>
       </c>
       <c r="T369" t="n">
-        <v>58.90162916711789</v>
+        <v>76.52114326465701</v>
       </c>
     </row>
     <row r="370">
@@ -27536,10 +27536,10 @@
         <v>3.6</v>
       </c>
       <c r="O370" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P370" t="n">
-        <v>93.1301733743861</v>
+        <v>94.28761275834462</v>
       </c>
       <c r="Q370" t="n">
         <v>-1.438970000000012</v>
@@ -27548,10 +27548,10 @@
         <v>0</v>
       </c>
       <c r="S370" t="n">
-        <v>58.7897836597506</v>
+        <v>76.40943007737025</v>
       </c>
       <c r="T370" t="n">
-        <v>58.7897836597506</v>
+        <v>76.40943007737025</v>
       </c>
     </row>
     <row r="371">
@@ -27610,10 +27610,10 @@
         <v>6.6</v>
       </c>
       <c r="O371" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P371" t="n">
-        <v>88.25171542729763</v>
+        <v>89.42571446873691</v>
       </c>
       <c r="Q371" t="n">
         <v>-5.848210000000009</v>
@@ -27622,10 +27622,10 @@
         <v>0</v>
       </c>
       <c r="S371" t="n">
-        <v>52.40177765191223</v>
+        <v>70.0186644972525</v>
       </c>
       <c r="T371" t="n">
-        <v>52.40177765191223</v>
+        <v>70.0186644972525</v>
       </c>
     </row>
     <row r="372">
@@ -27684,10 +27684,10 @@
         <v>8.35</v>
       </c>
       <c r="O372" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P372" t="n">
-        <v>85.40594829149602</v>
+        <v>86.5896071331324</v>
       </c>
       <c r="Q372" t="n">
         <v>-1.438970000000012</v>
@@ -27696,10 +27696,10 @@
         <v>0</v>
       </c>
       <c r="S372" t="n">
-        <v>53.47712205980423</v>
+        <v>71.10305368124804</v>
       </c>
       <c r="T372" t="n">
-        <v>53.47712205980423</v>
+        <v>71.10305368124804</v>
       </c>
     </row>
     <row r="373">
@@ -27758,10 +27758,10 @@
         <v>8.6</v>
       </c>
       <c r="O373" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P373" t="n">
-        <v>84.99941012923864</v>
+        <v>86.18444894233177</v>
       </c>
       <c r="Q373" t="n">
         <v>-3.643590000000017</v>
@@ -27770,10 +27770,10 @@
         <v>0</v>
       </c>
       <c r="S373" t="n">
-        <v>51.68118789797619</v>
+        <v>69.30408573227396</v>
       </c>
       <c r="T373" t="n">
-        <v>51.68118789797619</v>
+        <v>69.30408573227396</v>
       </c>
     </row>
     <row r="374">
@@ -27832,10 +27832,10 @@
         <v>14.6</v>
       </c>
       <c r="O374" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P374" t="n">
-        <v>75.24249423506168</v>
+        <v>76.46065236311634</v>
       </c>
       <c r="Q374" t="n">
         <v>-3.643590000000017</v>
@@ -27844,10 +27844,10 @@
         <v>0</v>
       </c>
       <c r="S374" t="n">
-        <v>44.97045745593867</v>
+        <v>62.60129449506697</v>
       </c>
       <c r="T374" t="n">
-        <v>44.97045745593867</v>
+        <v>62.60129449506697</v>
       </c>
     </row>
     <row r="375">
@@ -27906,10 +27906,10 @@
         <v>19.1</v>
       </c>
       <c r="O375" t="n">
-        <v>0.001569290996552004</v>
+        <v>0.001879374052823693</v>
       </c>
       <c r="P375" t="n">
-        <v>67.92480731442896</v>
+        <v>69.16780492870475</v>
       </c>
       <c r="Q375" t="n">
         <v>-1.438970000000012</v>
@@ -27918,10 +27918,10 @@
         <v>0</v>
       </c>
       <c r="S375" t="n">
-        <v>41.45373001782033</v>
+        <v>59.09388604791886</v>
       </c>
       <c r="T375" t="n">
-        <v>41.45373001782033</v>
+        <v>59.09388604791886</v>
       </c>
     </row>
   </sheetData>
